--- a/docs/oc-regiones/seguro-colectivo-de-vida-con-adicional-de-salud/metropolitana.xlsx
+++ b/docs/oc-regiones/seguro-colectivo-de-vida-con-adicional-de-salud/metropolitana.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M142"/>
+  <dimension ref="A1:M143"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -573,7 +573,7 @@
         </is>
       </c>
       <c r="M2" s="2" t="n">
-        <v>484450.95</v>
+        <v>481726.08</v>
       </c>
     </row>
     <row r="3">
@@ -634,7 +634,7 @@
         </is>
       </c>
       <c r="M3" s="2" t="n">
-        <v>8134.41</v>
+        <v>8050.32</v>
       </c>
     </row>
     <row r="4">
@@ -695,7 +695,7 @@
         </is>
       </c>
       <c r="M4" s="2" t="n">
-        <v>9554.700000000001</v>
+        <v>9449.709999999999</v>
       </c>
     </row>
     <row r="5">
@@ -756,7 +756,7 @@
         </is>
       </c>
       <c r="M5" s="2" t="n">
-        <v>1721.57</v>
+        <v>1712.4</v>
       </c>
     </row>
     <row r="6">
@@ -817,7 +817,7 @@
         </is>
       </c>
       <c r="M6" s="2" t="n">
-        <v>7015.39</v>
+        <v>7049.15</v>
       </c>
     </row>
     <row r="7">
@@ -878,7 +878,7 @@
         </is>
       </c>
       <c r="M7" s="2" t="n">
-        <v>8952.15</v>
+        <v>9018.08</v>
       </c>
     </row>
     <row r="8">
@@ -943,7 +943,7 @@
         </is>
       </c>
       <c r="M8" s="2" t="n">
-        <v>111557.59</v>
+        <v>112379.21</v>
       </c>
     </row>
     <row r="9">
@@ -1004,7 +1004,7 @@
         </is>
       </c>
       <c r="M9" s="2" t="n">
-        <v>32064.2</v>
+        <v>32019.45</v>
       </c>
     </row>
     <row r="10">
@@ -1065,7 +1065,7 @@
         </is>
       </c>
       <c r="M10" s="2" t="n">
-        <v>6283.72</v>
+        <v>6274.95</v>
       </c>
     </row>
     <row r="11">
@@ -1126,7 +1126,7 @@
         </is>
       </c>
       <c r="M11" s="2" t="n">
-        <v>9554.700000000001</v>
+        <v>9605.530000000001</v>
       </c>
     </row>
     <row r="12">
@@ -1187,7 +1187,7 @@
         </is>
       </c>
       <c r="M12" s="2" t="n">
-        <v>9554.700000000001</v>
+        <v>9605.530000000001</v>
       </c>
     </row>
     <row r="13">
@@ -1248,7 +1248,7 @@
         </is>
       </c>
       <c r="M13" s="2" t="n">
-        <v>1157.21</v>
+        <v>1141.35</v>
       </c>
     </row>
     <row r="14">
@@ -1309,7 +1309,7 @@
         </is>
       </c>
       <c r="M14" s="2" t="n">
-        <v>1119.88</v>
+        <v>1104.53</v>
       </c>
     </row>
     <row r="15">
@@ -1370,7 +1370,7 @@
         </is>
       </c>
       <c r="M15" s="2" t="n">
-        <v>15091.44</v>
+        <v>14888</v>
       </c>
     </row>
     <row r="16">
@@ -1431,7 +1431,7 @@
         </is>
       </c>
       <c r="M16" s="2" t="n">
-        <v>567.47</v>
+        <v>561.39</v>
       </c>
     </row>
     <row r="17">
@@ -1492,7 +1492,7 @@
         </is>
       </c>
       <c r="M17" s="2" t="n">
-        <v>630.53</v>
+        <v>623.76</v>
       </c>
     </row>
     <row r="18">
@@ -1553,7 +1553,7 @@
         </is>
       </c>
       <c r="M18" s="2" t="n">
-        <v>8535.68</v>
+        <v>8444.09</v>
       </c>
     </row>
     <row r="19">
@@ -1614,7 +1614,7 @@
         </is>
       </c>
       <c r="M19" s="2" t="n">
-        <v>15179.44</v>
+        <v>15103.88</v>
       </c>
     </row>
     <row r="20">
@@ -1675,7 +1675,7 @@
         </is>
       </c>
       <c r="M20" s="2" t="n">
-        <v>1803.93</v>
+        <v>1781.82</v>
       </c>
     </row>
     <row r="21">
@@ -1736,7 +1736,7 @@
         </is>
       </c>
       <c r="M21" s="2" t="n">
-        <v>6467.76</v>
+        <v>6491.23</v>
       </c>
     </row>
     <row r="22">
@@ -1797,7 +1797,7 @@
         </is>
       </c>
       <c r="M22" s="2" t="n">
-        <v>9327.65</v>
+        <v>9315.32</v>
       </c>
     </row>
     <row r="23">
@@ -1858,7 +1858,7 @@
         </is>
       </c>
       <c r="M23" s="2" t="n">
-        <v>8315.690000000001</v>
+        <v>8304.700000000001</v>
       </c>
     </row>
     <row r="24">
@@ -1919,7 +1919,7 @@
         </is>
       </c>
       <c r="M24" s="2" t="n">
-        <v>32690.79</v>
+        <v>32738.51</v>
       </c>
     </row>
     <row r="25">
@@ -1984,7 +1984,7 @@
         </is>
       </c>
       <c r="M25" s="2" t="n">
-        <v>300954.1</v>
+        <v>303167.25</v>
       </c>
     </row>
     <row r="26">
@@ -2049,7 +2049,7 @@
         </is>
       </c>
       <c r="M26" s="2" t="n">
-        <v>494472.34</v>
+        <v>500977.05</v>
       </c>
     </row>
     <row r="27">
@@ -2110,7 +2110,7 @@
         </is>
       </c>
       <c r="M27" s="2" t="n">
-        <v>52006.07</v>
+        <v>52355.38</v>
       </c>
     </row>
     <row r="28">
@@ -2171,7 +2171,7 @@
         </is>
       </c>
       <c r="M28" s="2" t="n">
-        <v>52006.07</v>
+        <v>52355.38</v>
       </c>
     </row>
     <row r="29">
@@ -2232,7 +2232,7 @@
         </is>
       </c>
       <c r="M29" s="2" t="n">
-        <v>2771.9</v>
+        <v>2790.78</v>
       </c>
     </row>
     <row r="30">
@@ -2297,7 +2297,7 @@
         </is>
       </c>
       <c r="M30" s="2" t="n">
-        <v>5669438.88</v>
+        <v>5708070.46</v>
       </c>
     </row>
     <row r="31">
@@ -2358,7 +2358,7 @@
         </is>
       </c>
       <c r="M31" s="2" t="n">
-        <v>7446.4</v>
+        <v>7274.71</v>
       </c>
     </row>
     <row r="32">
@@ -2419,7 +2419,7 @@
         </is>
       </c>
       <c r="M32" s="2" t="n">
-        <v>65094.36</v>
+        <v>63593.52</v>
       </c>
     </row>
     <row r="33">
@@ -2480,7 +2480,7 @@
         </is>
       </c>
       <c r="M33" s="2" t="n">
-        <v>14794.17</v>
+        <v>14614.26</v>
       </c>
     </row>
     <row r="34">
@@ -2541,7 +2541,7 @@
         </is>
       </c>
       <c r="M34" s="2" t="n">
-        <v>1255.55</v>
+        <v>1239.87</v>
       </c>
     </row>
     <row r="35">
@@ -2602,7 +2602,7 @@
         </is>
       </c>
       <c r="M35" s="2" t="n">
-        <v>1725.99</v>
+        <v>1723.24</v>
       </c>
     </row>
     <row r="36">
@@ -2663,7 +2663,7 @@
         </is>
       </c>
       <c r="M36" s="2" t="n">
-        <v>5917.67</v>
+        <v>5919.55</v>
       </c>
     </row>
     <row r="37">
@@ -2724,7 +2724,7 @@
         </is>
       </c>
       <c r="M37" s="2" t="n">
-        <v>7939.54</v>
+        <v>7952.53</v>
       </c>
     </row>
     <row r="38">
@@ -2785,7 +2785,7 @@
         </is>
       </c>
       <c r="M38" s="2" t="n">
-        <v>46749.59</v>
+        <v>46826.08</v>
       </c>
     </row>
     <row r="39">
@@ -2846,7 +2846,7 @@
         </is>
       </c>
       <c r="M39" s="2" t="n">
-        <v>66573.78</v>
+        <v>66147.32000000001</v>
       </c>
     </row>
     <row r="40">
@@ -2911,7 +2911,7 @@
         </is>
       </c>
       <c r="M40" s="2" t="n">
-        <v>51187.84</v>
+        <v>50859.94</v>
       </c>
     </row>
     <row r="41">
@@ -2972,7 +2972,7 @@
         </is>
       </c>
       <c r="M41" s="2" t="n">
-        <v>44446.44</v>
+        <v>44161.73</v>
       </c>
     </row>
     <row r="42">
@@ -3033,7 +3033,7 @@
         </is>
       </c>
       <c r="M42" s="2" t="n">
-        <v>66869.66</v>
+        <v>66441.31</v>
       </c>
     </row>
     <row r="43">
@@ -3094,7 +3094,7 @@
         </is>
       </c>
       <c r="M43" s="2" t="n">
-        <v>72195.57000000001</v>
+        <v>72653.84</v>
       </c>
     </row>
     <row r="44">
@@ -3155,7 +3155,7 @@
         </is>
       </c>
       <c r="M44" s="2" t="n">
-        <v>10898.37</v>
+        <v>10967.55</v>
       </c>
     </row>
     <row r="45">
@@ -3216,7 +3216,7 @@
         </is>
       </c>
       <c r="M45" s="2" t="n">
-        <v>40240.15</v>
+        <v>40771.06</v>
       </c>
     </row>
     <row r="46">
@@ -3277,7 +3277,7 @@
         </is>
       </c>
       <c r="M46" s="2" t="n">
-        <v>9418.959999999999</v>
+        <v>9557.92</v>
       </c>
     </row>
     <row r="47">
@@ -3338,7 +3338,7 @@
         </is>
       </c>
       <c r="M47" s="2" t="n">
-        <v>10405.24</v>
+        <v>10558.75</v>
       </c>
     </row>
     <row r="48">
@@ -3399,7 +3399,7 @@
         </is>
       </c>
       <c r="M48" s="2" t="n">
-        <v>9369.639999999999</v>
+        <v>9592.43</v>
       </c>
     </row>
     <row r="49">
@@ -3460,7 +3460,7 @@
         </is>
       </c>
       <c r="M49" s="2" t="n">
-        <v>4586.19</v>
+        <v>4695.24</v>
       </c>
     </row>
     <row r="50">
@@ -3521,7 +3521,7 @@
         </is>
       </c>
       <c r="M50" s="2" t="n">
-        <v>77521.47</v>
+        <v>79768.07000000001</v>
       </c>
     </row>
     <row r="51">
@@ -3582,7 +3582,7 @@
         </is>
       </c>
       <c r="M51" s="2" t="n">
-        <v>36837.49</v>
+        <v>37905.05</v>
       </c>
     </row>
     <row r="52">
@@ -3643,7 +3643,7 @@
         </is>
       </c>
       <c r="M52" s="2" t="n">
-        <v>7051.89</v>
+        <v>7256.26</v>
       </c>
     </row>
     <row r="53">
@@ -3704,7 +3704,7 @@
         </is>
       </c>
       <c r="M53" s="2" t="n">
-        <v>60310.91</v>
+        <v>62058.74</v>
       </c>
     </row>
     <row r="54">
@@ -3765,7 +3765,7 @@
         </is>
       </c>
       <c r="M54" s="2" t="n">
-        <v>651.99</v>
+        <v>646.6799999999999</v>
       </c>
     </row>
     <row r="55">
@@ -3826,7 +3826,7 @@
         </is>
       </c>
       <c r="M55" s="2" t="n">
-        <v>32758.58</v>
+        <v>32901.72</v>
       </c>
     </row>
     <row r="56">
@@ -3887,7 +3887,7 @@
         </is>
       </c>
       <c r="M56" s="2" t="n">
-        <v>35461.09</v>
+        <v>35616.04</v>
       </c>
     </row>
     <row r="57">
@@ -3948,7 +3948,7 @@
         </is>
       </c>
       <c r="M57" s="2" t="n">
-        <v>29725.38</v>
+        <v>29574.68</v>
       </c>
     </row>
     <row r="58">
@@ -4009,7 +4009,7 @@
         </is>
       </c>
       <c r="M58" s="2" t="n">
-        <v>47317.95</v>
+        <v>47704.99</v>
       </c>
     </row>
     <row r="59">
@@ -4070,7 +4070,7 @@
         </is>
       </c>
       <c r="M59" s="2" t="n">
-        <v>48025.7</v>
+        <v>48311.88</v>
       </c>
     </row>
     <row r="60">
@@ -4131,7 +4131,7 @@
         </is>
       </c>
       <c r="M60" s="2" t="n">
-        <v>67943.72</v>
+        <v>68515.95</v>
       </c>
     </row>
     <row r="61">
@@ -4192,7 +4192,7 @@
         </is>
       </c>
       <c r="M61" s="2" t="n">
-        <v>1567.15</v>
+        <v>1565.68</v>
       </c>
     </row>
     <row r="62">
@@ -4253,7 +4253,7 @@
         </is>
       </c>
       <c r="M62" s="2" t="n">
-        <v>8189.65</v>
+        <v>8181.93</v>
       </c>
     </row>
     <row r="63">
@@ -4314,7 +4314,7 @@
         </is>
       </c>
       <c r="M63" s="2" t="n">
-        <v>7229.13</v>
+        <v>7221.2</v>
       </c>
     </row>
     <row r="64">
@@ -4375,7 +4375,7 @@
         </is>
       </c>
       <c r="M64" s="2" t="n">
-        <v>17440.91</v>
+        <v>17394.98</v>
       </c>
     </row>
     <row r="65">
@@ -4436,7 +4436,7 @@
         </is>
       </c>
       <c r="M65" s="2" t="n">
-        <v>10717.31</v>
+        <v>10689.09</v>
       </c>
     </row>
     <row r="66">
@@ -4497,7 +4497,7 @@
         </is>
       </c>
       <c r="M66" s="2" t="n">
-        <v>37813.92</v>
+        <v>37714.34</v>
       </c>
     </row>
     <row r="67">
@@ -4558,7 +4558,7 @@
         </is>
       </c>
       <c r="M67" s="2" t="n">
-        <v>1287.11</v>
+        <v>1295.55</v>
       </c>
     </row>
     <row r="68">
@@ -4619,7 +4619,7 @@
         </is>
       </c>
       <c r="M68" s="2" t="n">
-        <v>9706.25</v>
+        <v>9730.34</v>
       </c>
     </row>
     <row r="69">
@@ -4680,7 +4680,7 @@
         </is>
       </c>
       <c r="M69" s="2" t="n">
-        <v>16329.07</v>
+        <v>17036</v>
       </c>
     </row>
     <row r="70">
@@ -4741,7 +4741,7 @@
         </is>
       </c>
       <c r="M70" s="2" t="n">
-        <v>619.4</v>
+        <v>646.22</v>
       </c>
     </row>
     <row r="71">
@@ -4802,7 +4802,7 @@
         </is>
       </c>
       <c r="M71" s="2" t="n">
-        <v>10661.92</v>
+        <v>11123.51</v>
       </c>
     </row>
     <row r="72">
@@ -4867,7 +4867,7 @@
         </is>
       </c>
       <c r="M72" s="2" t="n">
-        <v>696818.85</v>
+        <v>716564.4</v>
       </c>
     </row>
     <row r="73">
@@ -4928,7 +4928,7 @@
         </is>
       </c>
       <c r="M73" s="2" t="n">
-        <v>1035505.11</v>
+        <v>1064847.91</v>
       </c>
     </row>
     <row r="74">
@@ -4993,7 +4993,7 @@
         </is>
       </c>
       <c r="M74" s="2" t="n">
-        <v>5386172.79</v>
+        <v>5472729.65</v>
       </c>
     </row>
     <row r="75">
@@ -5058,7 +5058,7 @@
         </is>
       </c>
       <c r="M75" s="2" t="n">
-        <v>316975.97</v>
+        <v>317672.53</v>
       </c>
     </row>
     <row r="76">
@@ -5119,7 +5119,7 @@
         </is>
       </c>
       <c r="M76" s="2" t="n">
-        <v>1248.69</v>
+        <v>1240.09</v>
       </c>
     </row>
     <row r="77">
@@ -5180,7 +5180,7 @@
         </is>
       </c>
       <c r="M77" s="2" t="n">
-        <v>296228.46</v>
+        <v>296262.25</v>
       </c>
     </row>
     <row r="78">
@@ -5241,7 +5241,7 @@
         </is>
       </c>
       <c r="M78" s="2" t="n">
-        <v>7828.35</v>
+        <v>7784.67</v>
       </c>
     </row>
     <row r="79">
@@ -5302,7 +5302,7 @@
         </is>
       </c>
       <c r="M79" s="2" t="n">
-        <v>10709.95</v>
+        <v>10643.09</v>
       </c>
     </row>
     <row r="80">
@@ -5363,7 +5363,7 @@
         </is>
       </c>
       <c r="M80" s="2" t="n">
-        <v>10181.65</v>
+        <v>10139.47</v>
       </c>
     </row>
     <row r="81">
@@ -5428,7 +5428,7 @@
         </is>
       </c>
       <c r="M81" s="2" t="n">
-        <v>727892.1</v>
+        <v>717480.3100000001</v>
       </c>
     </row>
     <row r="82">
@@ -5489,7 +5489,7 @@
         </is>
       </c>
       <c r="M82" s="2" t="n">
-        <v>192.11</v>
+        <v>189.36</v>
       </c>
     </row>
     <row r="83">
@@ -5550,7 +5550,7 @@
         </is>
       </c>
       <c r="M83" s="2" t="n">
-        <v>1222.78</v>
+        <v>1205.28</v>
       </c>
     </row>
     <row r="84">
@@ -5611,7 +5611,7 @@
         </is>
       </c>
       <c r="M84" s="2" t="n">
-        <v>58736.61</v>
+        <v>57482.4</v>
       </c>
     </row>
     <row r="85">
@@ -5672,7 +5672,7 @@
         </is>
       </c>
       <c r="M85" s="2" t="n">
-        <v>36116.05</v>
+        <v>35281.5</v>
       </c>
     </row>
     <row r="86">
@@ -5733,7 +5733,7 @@
         </is>
       </c>
       <c r="M86" s="2" t="n">
-        <v>9467.5</v>
+        <v>9257.09</v>
       </c>
     </row>
     <row r="87">
@@ -5794,7 +5794,7 @@
         </is>
       </c>
       <c r="M87" s="2" t="n">
-        <v>699.33</v>
+        <v>683.78</v>
       </c>
     </row>
     <row r="88">
@@ -5855,7 +5855,7 @@
         </is>
       </c>
       <c r="M88" s="2" t="n">
-        <v>77887.3</v>
+        <v>76156.3</v>
       </c>
     </row>
     <row r="89">
@@ -5916,7 +5916,7 @@
         </is>
       </c>
       <c r="M89" s="2" t="n">
-        <v>6978.62</v>
+        <v>6777.5</v>
       </c>
     </row>
     <row r="90">
@@ -5977,7 +5977,7 @@
         </is>
       </c>
       <c r="M90" s="2" t="n">
-        <v>1268.84</v>
+        <v>1242.65</v>
       </c>
     </row>
     <row r="91">
@@ -6042,7 +6042,7 @@
         </is>
       </c>
       <c r="M91" s="2" t="n">
-        <v>44895.23</v>
+        <v>44910.95</v>
       </c>
     </row>
     <row r="92">
@@ -6103,7 +6103,7 @@
         </is>
       </c>
       <c r="M92" s="2" t="n">
-        <v>22129.67</v>
+        <v>22072.83</v>
       </c>
     </row>
     <row r="93">
@@ -6164,7 +6164,7 @@
         </is>
       </c>
       <c r="M93" s="2" t="n">
-        <v>22129.67</v>
+        <v>22072.83</v>
       </c>
     </row>
     <row r="94">
@@ -6225,7 +6225,7 @@
         </is>
       </c>
       <c r="M94" s="2" t="n">
-        <v>7905.85</v>
+        <v>8109.27</v>
       </c>
     </row>
     <row r="95">
@@ -6286,7 +6286,7 @@
         </is>
       </c>
       <c r="M95" s="2" t="n">
-        <v>10882.75</v>
+        <v>11025.85</v>
       </c>
     </row>
     <row r="96">
@@ -6347,7 +6347,7 @@
         </is>
       </c>
       <c r="M96" s="2" t="n">
-        <v>7076.23</v>
+        <v>7154.89</v>
       </c>
     </row>
     <row r="97">
@@ -6408,7 +6408,7 @@
         </is>
       </c>
       <c r="M97" s="2" t="n">
-        <v>3199.19</v>
+        <v>3227.45</v>
       </c>
     </row>
     <row r="98">
@@ -6469,7 +6469,7 @@
         </is>
       </c>
       <c r="M98" s="2" t="n">
-        <v>36649.98</v>
+        <v>36973.69</v>
       </c>
     </row>
     <row r="99">
@@ -6530,7 +6530,7 @@
         </is>
       </c>
       <c r="M99" s="2" t="n">
-        <v>1159.67</v>
+        <v>1168.85</v>
       </c>
     </row>
     <row r="100">
@@ -6591,7 +6591,7 @@
         </is>
       </c>
       <c r="M100" s="2" t="n">
-        <v>35478.74</v>
+        <v>35697.47</v>
       </c>
     </row>
     <row r="101">
@@ -6652,7 +6652,7 @@
         </is>
       </c>
       <c r="M101" s="2" t="n">
-        <v>706.84</v>
+        <v>694.21</v>
       </c>
     </row>
     <row r="102">
@@ -6713,7 +6713,7 @@
         </is>
       </c>
       <c r="M102" s="2" t="n">
-        <v>9717.25</v>
+        <v>9595.75</v>
       </c>
     </row>
     <row r="103">
@@ -6774,7 +6774,7 @@
         </is>
       </c>
       <c r="M103" s="2" t="n">
-        <v>1282.48</v>
+        <v>1266.44</v>
       </c>
     </row>
     <row r="104">
@@ -6835,7 +6835,7 @@
         </is>
       </c>
       <c r="M104" s="2" t="n">
-        <v>31568.74</v>
+        <v>31632.24</v>
       </c>
     </row>
     <row r="105">
@@ -6896,7 +6896,7 @@
         </is>
       </c>
       <c r="M105" s="2" t="n">
-        <v>10309.17</v>
+        <v>10269.21</v>
       </c>
     </row>
     <row r="106">
@@ -6957,7 +6957,7 @@
         </is>
       </c>
       <c r="M106" s="2" t="n">
-        <v>359291.68</v>
+        <v>361779.55</v>
       </c>
     </row>
     <row r="107">
@@ -7018,7 +7018,7 @@
         </is>
       </c>
       <c r="M107" s="2" t="n">
-        <v>8040.16</v>
+        <v>8014.09</v>
       </c>
     </row>
     <row r="108">
@@ -7079,7 +7079,7 @@
         </is>
       </c>
       <c r="M108" s="2" t="n">
-        <v>1172.14</v>
+        <v>1161.2</v>
       </c>
     </row>
     <row r="109">
@@ -7140,7 +7140,7 @@
         </is>
       </c>
       <c r="M109" s="2" t="n">
-        <v>10309.17</v>
+        <v>10321.26</v>
       </c>
     </row>
     <row r="110">
@@ -7205,7 +7205,7 @@
         </is>
       </c>
       <c r="M110" s="2" t="n">
-        <v>158713.19</v>
+        <v>160141.93</v>
       </c>
     </row>
     <row r="111">
@@ -7266,7 +7266,7 @@
         </is>
       </c>
       <c r="M111" s="2" t="n">
-        <v>9421.290000000001</v>
+        <v>9494.969999999999</v>
       </c>
     </row>
     <row r="112">
@@ -7327,7 +7327,7 @@
         </is>
       </c>
       <c r="M112" s="2" t="n">
-        <v>7250.94</v>
+        <v>7328.32</v>
       </c>
     </row>
     <row r="113">
@@ -7388,7 +7388,7 @@
         </is>
       </c>
       <c r="M113" s="2" t="n">
-        <v>3509.62</v>
+        <v>3547.07</v>
       </c>
     </row>
     <row r="114">
@@ -7449,7 +7449,7 @@
         </is>
       </c>
       <c r="M114" s="2" t="n">
-        <v>709.34</v>
+        <v>717.09</v>
       </c>
     </row>
     <row r="115">
@@ -7510,7 +7510,7 @@
         </is>
       </c>
       <c r="M115" s="2" t="n">
-        <v>10840.59</v>
+        <v>10958.97</v>
       </c>
     </row>
     <row r="116">
@@ -7571,13 +7571,13 @@
         </is>
       </c>
       <c r="M116" s="2" t="n">
-        <v>37372.82</v>
+        <v>37700.6</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>1211992-116-CM26</t>
+          <t>692264-2-SE26</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
@@ -7597,17 +7597,17 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>65.192.585-1</t>
+          <t>60.910.047-8</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>CORPORACIÓN YUNUS</t>
+          <t>UNIVERSIDAD METROPOLITANA DE CIENCIAS DE LA EDUCACION</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
@@ -7625,20 +7625,24 @@
           <t>96.573.600-K</t>
         </is>
       </c>
-      <c r="K117" t="inlineStr"/>
+      <c r="K117" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Región de Tarapacá  </t>
+        </is>
+      </c>
       <c r="L117" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M117" s="2" t="n">
-        <v>1386.01</v>
+        <v>449847.9</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>692264-2-SE26</t>
+          <t>1211992-116-CM26</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
@@ -7658,17 +7662,17 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>60.910.047-8</t>
+          <t>65.192.585-1</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD METROPOLITANA DE CIENCIAS DE LA EDUCACION</t>
+          <t>CORPORACIÓN YUNUS</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
@@ -7686,18 +7690,14 @@
           <t>96.573.600-K</t>
         </is>
       </c>
-      <c r="K118" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Región de Tarapacá  </t>
-        </is>
-      </c>
+      <c r="K118" t="inlineStr"/>
       <c r="L118" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M118" s="2" t="n">
-        <v>443479.78</v>
+        <v>1405.91</v>
       </c>
     </row>
     <row r="119">
@@ -7762,7 +7762,7 @@
         </is>
       </c>
       <c r="M119" s="2" t="n">
-        <v>799431.89</v>
+        <v>805575.1800000001</v>
       </c>
     </row>
     <row r="120">
@@ -7823,7 +7823,7 @@
         </is>
       </c>
       <c r="M120" s="2" t="n">
-        <v>8019.07</v>
+        <v>8058.6</v>
       </c>
     </row>
     <row r="121">
@@ -7884,7 +7884,7 @@
         </is>
       </c>
       <c r="M121" s="2" t="n">
-        <v>7227.06</v>
+        <v>7338</v>
       </c>
     </row>
     <row r="122">
@@ -7949,7 +7949,7 @@
         </is>
       </c>
       <c r="M122" s="2" t="n">
-        <v>281162.42</v>
+        <v>286656.49</v>
       </c>
     </row>
     <row r="123">
@@ -8010,7 +8010,7 @@
         </is>
       </c>
       <c r="M123" s="2" t="n">
-        <v>51084.44</v>
+        <v>51470.7</v>
       </c>
     </row>
     <row r="124">
@@ -8071,7 +8071,7 @@
         </is>
       </c>
       <c r="M124" s="2" t="n">
-        <v>10395.09</v>
+        <v>10377.13</v>
       </c>
     </row>
     <row r="125">
@@ -8132,13 +8132,13 @@
         </is>
       </c>
       <c r="M125" s="2" t="n">
-        <v>314822.71</v>
+        <v>310935.41</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>1495206-5-CM26</t>
+          <t>1477-194-CM26</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
@@ -8163,12 +8163,12 @@
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>61.981.340-5</t>
+          <t>70.786.200-9</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>Servicio de Biodiversidad y Áreas Protegidas</t>
+          <t>Corporación de Asistencia Judicial RM</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
@@ -8193,13 +8193,13 @@
         </is>
       </c>
       <c r="M126" s="2" t="n">
-        <v>4036.47</v>
+        <v>36957.96</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>1186801-6-CM26</t>
+          <t>1495206-5-CM26</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
@@ -8224,12 +8224,12 @@
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>60.930.000-0</t>
+          <t>61.981.340-5</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>CONSEJO NACIONAL DE EDUCACION</t>
+          <t>Servicio de Biodiversidad y Áreas Protegidas</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
@@ -8254,13 +8254,13 @@
         </is>
       </c>
       <c r="M127" s="2" t="n">
-        <v>1218.29</v>
+        <v>3981.12</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>1477-194-CM26</t>
+          <t>1186801-6-CM26</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
@@ -8285,12 +8285,12 @@
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>70.786.200-9</t>
+          <t>60.930.000-0</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>Corporación de Asistencia Judicial RM</t>
+          <t>CONSEJO NACIONAL DE EDUCACION</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
@@ -8315,7 +8315,7 @@
         </is>
       </c>
       <c r="M128" s="2" t="n">
-        <v>37471.82</v>
+        <v>1201.58</v>
       </c>
     </row>
     <row r="129">
@@ -8376,7 +8376,7 @@
         </is>
       </c>
       <c r="M129" s="2" t="n">
-        <v>61479.53</v>
+        <v>60299.47</v>
       </c>
     </row>
     <row r="130">
@@ -8437,7 +8437,7 @@
         </is>
       </c>
       <c r="M130" s="2" t="n">
-        <v>689.64</v>
+        <v>695.87</v>
       </c>
     </row>
     <row r="131">
@@ -8498,7 +8498,7 @@
         </is>
       </c>
       <c r="M131" s="2" t="n">
-        <v>10587.58</v>
+        <v>10624.78</v>
       </c>
     </row>
     <row r="132">
@@ -8559,13 +8559,13 @@
         </is>
       </c>
       <c r="M132" s="2" t="n">
-        <v>9288.200000000001</v>
+        <v>9324.450000000001</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>550716-9-CM26</t>
+          <t>545927-3-SE26</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
@@ -8590,12 +8590,12 @@
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>65.961.370-0</t>
+          <t>61.212.000-5</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>Servicio de Bienestar del Personal del Gobierno Re</t>
+          <t>SUBSECRETARIA DE TRANSPORTES</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
@@ -8613,14 +8613,18 @@
           <t>96.573.600-K</t>
         </is>
       </c>
-      <c r="K133" t="inlineStr"/>
+      <c r="K133" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Región de Tarapacá  </t>
+        </is>
+      </c>
       <c r="L133" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M133" s="2" t="n">
-        <v>7026.3</v>
+        <v>581414.84</v>
       </c>
     </row>
     <row r="134">
@@ -8681,13 +8685,13 @@
         </is>
       </c>
       <c r="M134" s="2" t="n">
-        <v>1636.26</v>
+        <v>1647.34</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>545927-3-SE26</t>
+          <t>550716-9-CM26</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
@@ -8712,12 +8716,12 @@
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>61.212.000-5</t>
+          <t>65.961.370-0</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>SUBSECRETARIA DE TRANSPORTES</t>
+          <t>Servicio de Bienestar del Personal del Gobierno Re</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
@@ -8735,18 +8739,14 @@
           <t>96.573.600-K</t>
         </is>
       </c>
-      <c r="K135" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Región de Tarapacá  </t>
-        </is>
-      </c>
+      <c r="K135" t="inlineStr"/>
       <c r="L135" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M135" s="2" t="n">
-        <v>577504.36</v>
+        <v>7073.88</v>
       </c>
     </row>
     <row r="136">
@@ -8811,7 +8811,7 @@
         </is>
       </c>
       <c r="M136" s="2" t="n">
-        <v>154771.17</v>
+        <v>154472.86</v>
       </c>
     </row>
     <row r="137">
@@ -8876,7 +8876,7 @@
         </is>
       </c>
       <c r="M137" s="2" t="n">
-        <v>19346.4</v>
+        <v>19309.11</v>
       </c>
     </row>
     <row r="138">
@@ -8937,7 +8937,7 @@
         </is>
       </c>
       <c r="M138" s="2" t="n">
-        <v>1184.45</v>
+        <v>1177.97</v>
       </c>
     </row>
     <row r="139">
@@ -8998,7 +8998,7 @@
         </is>
       </c>
       <c r="M139" s="2" t="n">
-        <v>10491.33</v>
+        <v>10433.97</v>
       </c>
     </row>
     <row r="140">
@@ -9063,13 +9063,13 @@
         </is>
       </c>
       <c r="M140" s="2" t="n">
-        <v>1406029.91</v>
+        <v>1399224.97</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>2701-496-CM26</t>
+          <t>1477-242-CM26</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
@@ -9094,12 +9094,12 @@
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>69.071.800-6</t>
+          <t>70.786.200-9</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE TALAGANTE</t>
+          <t>Corporación de Asistencia Judicial RM</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
@@ -9124,13 +9124,13 @@
         </is>
       </c>
       <c r="M141" s="2" t="n">
-        <v>7796.31</v>
+        <v>36580.68</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>1477-242-CM26</t>
+          <t>2701-496-CM26</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
@@ -9155,12 +9155,12 @@
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>70.786.200-9</t>
+          <t>69.071.800-6</t>
         </is>
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>Corporación de Asistencia Judicial RM</t>
+          <t>I MUNICIPALIDAD DE TALAGANTE</t>
         </is>
       </c>
       <c r="H142" t="inlineStr">
@@ -9185,7 +9185,68 @@
         </is>
       </c>
       <c r="M142" s="2" t="n">
-        <v>36334.65</v>
+        <v>7849.1</v>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="inlineStr">
+        <is>
+          <t>4722-2-CM26</t>
+        </is>
+      </c>
+      <c r="B143" t="inlineStr">
+        <is>
+          <t>2239-12-LR23</t>
+        </is>
+      </c>
+      <c r="C143" t="inlineStr">
+        <is>
+          <t>ago-2026</t>
+        </is>
+      </c>
+      <c r="D143" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="E143" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F143" t="inlineStr">
+        <is>
+          <t>65.138.650-0</t>
+        </is>
+      </c>
+      <c r="G143" t="inlineStr">
+        <is>
+          <t>DEFENSORIA PENAL PUBLICA</t>
+        </is>
+      </c>
+      <c r="H143" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="I143" t="inlineStr">
+        <is>
+          <t>BCI SEGUROS VIDA S A</t>
+        </is>
+      </c>
+      <c r="J143" t="inlineStr">
+        <is>
+          <t>96.573.600-K</t>
+        </is>
+      </c>
+      <c r="K143" t="inlineStr"/>
+      <c r="L143" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M143" s="2" t="n">
+        <v>30370.94</v>
       </c>
     </row>
   </sheetData>

--- a/docs/oc-regiones/seguro-colectivo-de-vida-con-adicional-de-salud/metropolitana.xlsx
+++ b/docs/oc-regiones/seguro-colectivo-de-vida-con-adicional-de-salud/metropolitana.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M143"/>
+  <dimension ref="A1:M152"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -514,7 +514,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>559222-1-CM25</t>
+          <t>1114502-1-CM25</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -524,12 +524,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>nov-2025</t>
+          <t>ene-2025</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>2025-11-04</t>
+          <t>2025-01-09</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -539,12 +539,12 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>60.107.000-6</t>
+          <t>65.081.366-9</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE LA MUJER Y LA EQUIDAD DE GENERO</t>
+          <t>CONSEJO NACIONAL DE TELEVISION</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -562,24 +562,20 @@
           <t>96.573.600-K</t>
         </is>
       </c>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Región de Tarapacá  </t>
-        </is>
-      </c>
+      <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M2" s="2" t="n">
-        <v>481726.08</v>
+        <v>35351.76</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>1373053-12-CM25</t>
+          <t>1153625-4-CM25</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -589,12 +585,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>nov-2025</t>
+          <t>ene-2025</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2025-11-05</t>
+          <t>2025-01-27</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -604,12 +600,12 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>82.174.900-k</t>
+          <t>62.000.670-K</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>SERVICIO DE COOPERACION TECNICA</t>
+          <t>SUBSECRETARIA DE RELACIONES ECONOMICAS INTERNACIONALES</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -634,13 +630,13 @@
         </is>
       </c>
       <c r="M3" s="2" t="n">
-        <v>8050.32</v>
+        <v>50479.65</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2702-543-CM25</t>
+          <t>2702-108-CM25</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -650,12 +646,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>nov-2025</t>
+          <t>mar-2025</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2025-11-10</t>
+          <t>2025-03-10</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -695,13 +691,13 @@
         </is>
       </c>
       <c r="M4" s="2" t="n">
-        <v>9449.709999999999</v>
+        <v>9467.67</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>1211992-213-CM25</t>
+          <t>2702-186-CM25</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -711,27 +707,27 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>nov-2025</t>
+          <t>may-2025</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2025-11-11</t>
+          <t>2025-05-07</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>65.192.585-1</t>
+          <t>69.071.800-6</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>CORPORACIÓN YUNUS</t>
+          <t>I MUNICIPALIDAD DE TALAGANTE</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -756,13 +752,13 @@
         </is>
       </c>
       <c r="M5" s="2" t="n">
-        <v>1712.4</v>
+        <v>9601.809999999999</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2701-829-CM25</t>
+          <t>2702-233-CM25</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -772,12 +768,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>nov-2025</t>
+          <t>may-2025</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2025-11-20</t>
+          <t>2025-05-30</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -817,13 +813,13 @@
         </is>
       </c>
       <c r="M6" s="2" t="n">
-        <v>7049.15</v>
+        <v>9514.190000000001</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>670784-13-CM25</t>
+          <t>1157285-10-CM25</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -833,12 +829,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>nov-2025</t>
+          <t>jun-2025</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2025-11-21</t>
+          <t>2025-06-09</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -848,12 +844,12 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>60.818.000-1</t>
+          <t>62.000.860-5</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Superintendencia de Pensiones</t>
+          <t>SUBSECRETARIA PARA LAS FUERZAS ARMADAS</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -878,13 +874,13 @@
         </is>
       </c>
       <c r="M7" s="2" t="n">
-        <v>9018.08</v>
+        <v>45047.81</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>1169411-2-SE25</t>
+          <t>670784-6-CM25</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -894,12 +890,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>nov-2025</t>
+          <t>jun-2025</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2025-11-21</t>
+          <t>2025-06-19</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -909,12 +905,12 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>61.501.000-6</t>
+          <t>60.818.000-1</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>SUBSECRETARIA DEL TRABAJO</t>
+          <t>SUPERINTENDENCIA DE PENSIONES</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -932,24 +928,20 @@
           <t>96.573.600-K</t>
         </is>
       </c>
-      <c r="K8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Región de Tarapacá  </t>
-        </is>
-      </c>
+      <c r="K8" t="inlineStr"/>
       <c r="L8" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M8" s="2" t="n">
-        <v>112379.21</v>
+        <v>8663.24</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>1477-369-CM25</t>
+          <t>2702-326-CM25</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -959,12 +951,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>nov-2025</t>
+          <t>jul-2025</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2025-11-26</t>
+          <t>2025-07-21</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -974,12 +966,12 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>70.786.200-9</t>
+          <t>69.071.800-6</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Corporación de Asistencia Judicial RM</t>
+          <t>I MUNICIPALIDAD DE TALAGANTE</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -1004,13 +996,13 @@
         </is>
       </c>
       <c r="M9" s="2" t="n">
-        <v>32019.45</v>
+        <v>9243.610000000001</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>550716-15-CM25</t>
+          <t>2702-415-CM25</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1020,27 +1012,27 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>nov-2025</t>
+          <t>sep-2025</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2025-11-26</t>
+          <t>2025-09-02</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>65.961.370-0</t>
+          <t>69.071.800-6</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Servicio de Bienestar del Personal del Gobierno Re</t>
+          <t>I MUNICIPALIDAD DE TALAGANTE</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -1065,13 +1057,13 @@
         </is>
       </c>
       <c r="M10" s="2" t="n">
-        <v>6274.95</v>
+        <v>9178.57</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2702-582-CM25</t>
+          <t>559222-1-CM25</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1086,7 +1078,7 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2025-11-27</t>
+          <t>2025-11-04</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -1096,12 +1088,12 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>69.071.800-6</t>
+          <t>60.107.000-6</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE TALAGANTE</t>
+          <t>SERVICIO NACIONAL DE LA MUJER Y LA EQUIDAD DE GENERO</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -1119,20 +1111,24 @@
           <t>96.573.600-K</t>
         </is>
       </c>
-      <c r="K11" t="inlineStr"/>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Región de Tarapacá  </t>
+        </is>
+      </c>
       <c r="L11" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M11" s="2" t="n">
-        <v>9605.530000000001</v>
+        <v>481726.08</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2702-583-CM25</t>
+          <t>1373053-12-CM25</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1147,7 +1143,7 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2025-11-27</t>
+          <t>2025-11-05</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -1157,12 +1153,12 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>69.071.800-6</t>
+          <t>82.174.900-k</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE TALAGANTE</t>
+          <t>SERVICIO DE COOPERACION TECNICA</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -1187,13 +1183,13 @@
         </is>
       </c>
       <c r="M12" s="2" t="n">
-        <v>9605.530000000001</v>
+        <v>8050.32</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>1186801-14-CM25</t>
+          <t>2702-543-CM25</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1203,12 +1199,12 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>dic-2025</t>
+          <t>nov-2025</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2025-12-01</t>
+          <t>2025-11-10</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -1218,12 +1214,12 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>60.930.000-0</t>
+          <t>69.071.800-6</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>CONSEJO NACIONAL DE EDUCACION</t>
+          <t>I MUNICIPALIDAD DE TALAGANTE</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -1248,13 +1244,13 @@
         </is>
       </c>
       <c r="M13" s="2" t="n">
-        <v>1141.35</v>
+        <v>9449.709999999999</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>1186801-15-CM25</t>
+          <t>1211992-213-CM25</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1264,27 +1260,27 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>dic-2025</t>
+          <t>nov-2025</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2025-12-01</t>
+          <t>2025-11-11</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>60.930.000-0</t>
+          <t>65.192.585-1</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>CONSEJO NACIONAL DE EDUCACION</t>
+          <t>CORPORACIÓN YUNUS</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -1309,13 +1305,13 @@
         </is>
       </c>
       <c r="M14" s="2" t="n">
-        <v>1104.53</v>
+        <v>1712.4</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>3378-11858-CM25</t>
+          <t>2701-829-CM25</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1325,12 +1321,12 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>dic-2025</t>
+          <t>nov-2025</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2025-12-02</t>
+          <t>2025-11-20</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -1340,12 +1336,12 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>61.101.030-3</t>
+          <t>69.071.800-6</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>EJERCITO DE CHILE HOSPITAL MILITAR DE SANTIAGO</t>
+          <t>I MUNICIPALIDAD DE TALAGANTE</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -1370,13 +1366,13 @@
         </is>
       </c>
       <c r="M15" s="2" t="n">
-        <v>14888</v>
+        <v>7049.15</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>307-103-CM25</t>
+          <t>670784-13-CM25</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1386,27 +1382,27 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>dic-2025</t>
+          <t>nov-2025</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2025-12-03</t>
+          <t>2025-11-21</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>60.919.000-0</t>
+          <t>60.818.000-1</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Consejo de Rectores de las Universidades Chilenas</t>
+          <t>Superintendencia de Pensiones</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -1431,13 +1427,13 @@
         </is>
       </c>
       <c r="M16" s="2" t="n">
-        <v>561.39</v>
+        <v>9018.08</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>307-102-CM25</t>
+          <t>1169411-2-SE25</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1447,12 +1443,12 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>dic-2025</t>
+          <t>nov-2025</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2025-12-03</t>
+          <t>2025-11-21</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -1462,12 +1458,12 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>60.919.000-0</t>
+          <t>61.501.000-6</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Consejo de Rectores de las Universidades Chilenas</t>
+          <t>SUBSECRETARIA DEL TRABAJO</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -1485,20 +1481,24 @@
           <t>96.573.600-K</t>
         </is>
       </c>
-      <c r="K17" t="inlineStr"/>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Región de Tarapacá  </t>
+        </is>
+      </c>
       <c r="L17" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M17" s="2" t="n">
-        <v>623.76</v>
+        <v>112379.21</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>1373053-13-CM25</t>
+          <t>550716-15-CM25</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1508,27 +1508,27 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>dic-2025</t>
+          <t>nov-2025</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2025-12-03</t>
+          <t>2025-11-26</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>82.174.900-k</t>
+          <t>65.961.370-0</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>SERVICIO DE COOPERACION TECNICA</t>
+          <t>Servicio de Bienestar del Personal del Gobierno Re</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -1553,13 +1553,13 @@
         </is>
       </c>
       <c r="M18" s="2" t="n">
-        <v>8444.09</v>
+        <v>6274.95</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>3378-12106-CM25</t>
+          <t>1477-369-CM25</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1569,12 +1569,12 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>dic-2025</t>
+          <t>nov-2025</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>2025-12-09</t>
+          <t>2025-11-26</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -1584,12 +1584,12 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>61.101.030-3</t>
+          <t>70.786.200-9</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>EJERCITO DE CHILE HOSPITAL MILITAR DE SANTIAGO</t>
+          <t>Corporación de Asistencia Judicial RM</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -1614,13 +1614,13 @@
         </is>
       </c>
       <c r="M19" s="2" t="n">
-        <v>15103.88</v>
+        <v>32019.45</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>1211992-229-CM25</t>
+          <t>2702-583-CM25</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1630,27 +1630,27 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>dic-2025</t>
+          <t>nov-2025</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>2025-12-10</t>
+          <t>2025-11-27</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>65.192.585-1</t>
+          <t>69.071.800-6</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>CORPORACIÓN YUNUS</t>
+          <t>I MUNICIPALIDAD DE TALAGANTE</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -1675,13 +1675,13 @@
         </is>
       </c>
       <c r="M20" s="2" t="n">
-        <v>1781.82</v>
+        <v>9605.530000000001</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>550716-16-CM25</t>
+          <t>2702-582-CM25</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1691,27 +1691,27 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>dic-2025</t>
+          <t>nov-2025</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>2025-12-15</t>
+          <t>2025-11-27</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>65.961.370-0</t>
+          <t>69.071.800-6</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Servicio de Bienestar del Personal del Gobierno Re</t>
+          <t>I MUNICIPALIDAD DE TALAGANTE</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
@@ -1736,13 +1736,13 @@
         </is>
       </c>
       <c r="M21" s="2" t="n">
-        <v>6491.23</v>
+        <v>9605.530000000001</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>670784-16-CM25</t>
+          <t>1186801-15-CM25</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1757,7 +1757,7 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>2025-12-18</t>
+          <t>2025-12-01</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -1767,12 +1767,12 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>60.818.000-1</t>
+          <t>60.930.000-0</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Superintendencia de Pensiones</t>
+          <t>CONSEJO NACIONAL DE EDUCACION</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
@@ -1797,13 +1797,13 @@
         </is>
       </c>
       <c r="M22" s="2" t="n">
-        <v>9315.32</v>
+        <v>1104.53</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>1373053-14-CM25</t>
+          <t>1186801-14-CM25</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1818,7 +1818,7 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>2025-12-18</t>
+          <t>2025-12-01</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -1828,12 +1828,12 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>82.174.900-k</t>
+          <t>60.930.000-0</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>SERVICIO DE COOPERACION TECNICA</t>
+          <t>CONSEJO NACIONAL DE EDUCACION</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
@@ -1858,13 +1858,13 @@
         </is>
       </c>
       <c r="M23" s="2" t="n">
-        <v>8304.700000000001</v>
+        <v>1141.35</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>1477-416-CM25</t>
+          <t>3378-11858-CM25</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1879,7 +1879,7 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>2025-12-19</t>
+          <t>2025-12-02</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
@@ -1889,12 +1889,12 @@
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>70.786.200-9</t>
+          <t>61.101.030-3</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Corporación de Asistencia Judicial RM</t>
+          <t>EJERCITO DE CHILE HOSPITAL MILITAR DE SANTIAGO</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
@@ -1919,13 +1919,13 @@
         </is>
       </c>
       <c r="M24" s="2" t="n">
-        <v>32738.51</v>
+        <v>14888</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2341-693-CM25</t>
+          <t>307-103-CM25</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1940,22 +1940,22 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>2025-12-22</t>
+          <t>2025-12-03</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>69.072.700-5</t>
+          <t>60.919.000-0</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE SAN BERNARDO</t>
+          <t>Consejo de Rectores de las Universidades Chilenas</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
@@ -1973,24 +1973,20 @@
           <t>96.573.600-K</t>
         </is>
       </c>
-      <c r="K25" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Región de Tarapacá  </t>
-        </is>
-      </c>
+      <c r="K25" t="inlineStr"/>
       <c r="L25" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M25" s="2" t="n">
-        <v>303167.25</v>
+        <v>561.39</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>598002-22-SE25</t>
+          <t>1373053-13-CM25</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2005,22 +2001,22 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>2025-12-26</t>
+          <t>2025-12-03</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>60.810.001-6</t>
+          <t>82.174.900-k</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Servicio de Bienestar del Personal de la SVS</t>
+          <t>SERVICIO DE COOPERACION TECNICA</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
@@ -2038,24 +2034,20 @@
           <t>96.573.600-K</t>
         </is>
       </c>
-      <c r="K26" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Región de Tarapacá  </t>
-        </is>
-      </c>
+      <c r="K26" t="inlineStr"/>
       <c r="L26" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M26" s="2" t="n">
-        <v>500977.05</v>
+        <v>8444.09</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>1217436-22-CM25</t>
+          <t>307-102-CM25</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2070,7 +2062,7 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>2025-12-30</t>
+          <t>2025-12-03</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
@@ -2080,12 +2072,12 @@
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>61.221.000-4</t>
+          <t>60.919.000-0</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>SERVICIO DE BIENESTAR</t>
+          <t>Consejo de Rectores de las Universidades Chilenas</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
@@ -2110,13 +2102,13 @@
         </is>
       </c>
       <c r="M27" s="2" t="n">
-        <v>52355.38</v>
+        <v>623.76</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>1217436-21-CM25</t>
+          <t>3378-12106-CM25</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2131,7 +2123,7 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>2025-12-30</t>
+          <t>2025-12-09</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
@@ -2141,12 +2133,12 @@
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>61.221.000-4</t>
+          <t>61.101.030-3</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>SERVICIO DE BIENESTAR</t>
+          <t>EJERCITO DE CHILE HOSPITAL MILITAR DE SANTIAGO</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
@@ -2171,13 +2163,13 @@
         </is>
       </c>
       <c r="M28" s="2" t="n">
-        <v>52355.38</v>
+        <v>15103.88</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>4700-23-CM25</t>
+          <t>1211992-229-CM25</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2192,22 +2184,22 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>2025-12-31</t>
+          <t>2025-12-10</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>73.362.800-6</t>
+          <t>65.192.585-1</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>BIENESTAR DEL CONSEJO DE DEFENSA DEL ESTADO</t>
+          <t>CORPORACIÓN YUNUS</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
@@ -2232,13 +2224,13 @@
         </is>
       </c>
       <c r="M29" s="2" t="n">
-        <v>2790.78</v>
+        <v>1781.82</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>425-1046-SE25</t>
+          <t>550716-16-CM25</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -2253,22 +2245,22 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>2025-12-31</t>
+          <t>2025-12-15</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>60.301.001-9</t>
+          <t>65.961.370-0</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>CORP ADMINISTRATIVA DEL PODER JUDICIAL</t>
+          <t>Servicio de Bienestar del Personal del Gobierno Re</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
@@ -2286,24 +2278,20 @@
           <t>96.573.600-K</t>
         </is>
       </c>
-      <c r="K30" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Región de Tarapacá  </t>
-        </is>
-      </c>
+      <c r="K30" t="inlineStr"/>
       <c r="L30" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M30" s="2" t="n">
-        <v>5708070.46</v>
+        <v>6491.23</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2701-5-CM26</t>
+          <t>670784-16-CM25</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -2313,12 +2301,12 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>ene-2026</t>
+          <t>dic-2025</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>2026-01-06</t>
+          <t>2025-12-18</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
@@ -2328,12 +2316,12 @@
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>69.071.800-6</t>
+          <t>60.818.000-1</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE TALAGANTE</t>
+          <t>Superintendencia de Pensiones</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
@@ -2358,13 +2346,13 @@
         </is>
       </c>
       <c r="M31" s="2" t="n">
-        <v>7274.71</v>
+        <v>9315.32</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>574800-1-CM26</t>
+          <t>1373053-14-CM25</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -2374,12 +2362,12 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>ene-2026</t>
+          <t>dic-2025</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>2026-01-06</t>
+          <t>2025-12-18</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
@@ -2389,12 +2377,12 @@
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>60.601.000-1</t>
+          <t>82.174.900-k</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Subsecretaria de Relaciones Exteriores</t>
+          <t>SERVICIO DE COOPERACION TECNICA</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
@@ -2419,13 +2407,13 @@
         </is>
       </c>
       <c r="M32" s="2" t="n">
-        <v>63593.52</v>
+        <v>8304.700000000001</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>5780-1-CM26</t>
+          <t>1477-416-CM25</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -2435,12 +2423,12 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>ene-2026</t>
+          <t>dic-2025</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>2026-01-08</t>
+          <t>2025-12-19</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
@@ -2450,12 +2438,12 @@
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>60.819.000-7</t>
+          <t>70.786.200-9</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Superintendencia de Salud</t>
+          <t>Corporación de Asistencia Judicial RM</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
@@ -2480,13 +2468,13 @@
         </is>
       </c>
       <c r="M33" s="2" t="n">
-        <v>14614.26</v>
+        <v>32738.51</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>1186801-1-CM26</t>
+          <t>2341-693-CM25</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -2496,12 +2484,12 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>ene-2026</t>
+          <t>dic-2025</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>2026-01-12</t>
+          <t>2025-12-22</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
@@ -2511,12 +2499,12 @@
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>60.930.000-0</t>
+          <t>69.072.700-5</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>CONSEJO NACIONAL DE EDUCACION</t>
+          <t>I MUNICIPALIDAD DE SAN BERNARDO</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
@@ -2534,20 +2522,24 @@
           <t>96.573.600-K</t>
         </is>
       </c>
-      <c r="K34" t="inlineStr"/>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Región de Tarapacá  </t>
+        </is>
+      </c>
       <c r="L34" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M34" s="2" t="n">
-        <v>1239.87</v>
+        <v>303167.25</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>1211992-9-CM26</t>
+          <t>598002-22-SE25</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -2557,12 +2549,12 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>ene-2026</t>
+          <t>dic-2025</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>2026-01-13</t>
+          <t>2025-12-26</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
@@ -2572,12 +2564,12 @@
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>65.192.585-1</t>
+          <t>60.810.001-6</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>CORPORACIÓN YUNUS</t>
+          <t>Servicio de Bienestar del Personal de la SVS</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
@@ -2595,20 +2587,24 @@
           <t>96.573.600-K</t>
         </is>
       </c>
-      <c r="K35" t="inlineStr"/>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Región de Tarapacá  </t>
+        </is>
+      </c>
       <c r="L35" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M35" s="2" t="n">
-        <v>1723.24</v>
+        <v>500977.05</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>606-25-CM26</t>
+          <t>1217436-22-CM25</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -2618,12 +2614,12 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>ene-2026</t>
+          <t>dic-2025</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>2026-01-14</t>
+          <t>2025-12-30</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
@@ -2633,12 +2629,12 @@
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>60.513.000-3</t>
+          <t>61.221.000-4</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>SUBSECRETARIA DE TELECOMUNICACIONES</t>
+          <t>SERVICIO DE BIENESTAR</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
@@ -2663,13 +2659,13 @@
         </is>
       </c>
       <c r="M36" s="2" t="n">
-        <v>5919.55</v>
+        <v>52355.38</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2701-18-CM26</t>
+          <t>1217436-21-CM25</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -2679,12 +2675,12 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>ene-2026</t>
+          <t>dic-2025</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>2026-01-15</t>
+          <t>2025-12-30</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
@@ -2694,12 +2690,12 @@
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>69.071.800-6</t>
+          <t>61.221.000-4</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE TALAGANTE</t>
+          <t>SERVICIO DE BIENESTAR</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
@@ -2724,13 +2720,13 @@
         </is>
       </c>
       <c r="M37" s="2" t="n">
-        <v>7952.53</v>
+        <v>52355.38</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>1221275-1-CM26</t>
+          <t>4700-23-CM25</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -2740,27 +2736,27 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>ene-2026</t>
+          <t>dic-2025</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>2026-01-15</t>
+          <t>2025-12-31</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>60.108.000-1</t>
+          <t>73.362.800-6</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>AGENCIA CHILENA DE COOPERACION INTERNACIONAL PARA EL DESARROLLO</t>
+          <t>BIENESTAR DEL CONSEJO DE DEFENSA DEL ESTADO</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
@@ -2785,13 +2781,13 @@
         </is>
       </c>
       <c r="M38" s="2" t="n">
-        <v>46826.08</v>
+        <v>2790.78</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>786370-1-CM26</t>
+          <t>425-1046-SE25</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -2801,27 +2797,27 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>ene-2026</t>
+          <t>dic-2025</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>2026-01-21</t>
+          <t>2025-12-31</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>61.980.170-9</t>
+          <t>60.301.001-9</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL PARA LA PREVENCION Y REHABILITACION DEL CONSUMO DE D</t>
+          <t>CORP ADMINISTRATIVA DEL PODER JUDICIAL</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
@@ -2839,20 +2835,24 @@
           <t>96.573.600-K</t>
         </is>
       </c>
-      <c r="K39" t="inlineStr"/>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Región de Tarapacá  </t>
+        </is>
+      </c>
       <c r="L39" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M39" s="2" t="n">
-        <v>66147.32000000001</v>
+        <v>5708070.46</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>1157285-1-SE26</t>
+          <t>574800-1-CM26</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -2867,7 +2867,7 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>2026-01-21</t>
+          <t>2026-01-06</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
@@ -2877,12 +2877,12 @@
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>62.000.860-5</t>
+          <t>60.601.000-1</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Bienestar SSFFAA</t>
+          <t>Subsecretaria de Relaciones Exteriores</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
@@ -2900,24 +2900,20 @@
           <t>96.573.600-K</t>
         </is>
       </c>
-      <c r="K40" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Región de Tarapacá  </t>
-        </is>
-      </c>
+      <c r="K40" t="inlineStr"/>
       <c r="L40" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M40" s="2" t="n">
-        <v>50859.94</v>
+        <v>63593.52</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>1111089-31-CM26</t>
+          <t>2701-5-CM26</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -2932,7 +2928,7 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>2026-01-21</t>
+          <t>2026-01-06</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
@@ -2942,12 +2938,12 @@
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>60.915.000-9</t>
+          <t>69.071.800-6</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Agencia Nacional de Investigación y Desarrollo (ANID)</t>
+          <t>I MUNICIPALIDAD DE TALAGANTE</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
@@ -2972,13 +2968,13 @@
         </is>
       </c>
       <c r="M41" s="2" t="n">
-        <v>44161.73</v>
+        <v>7274.71</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>1153625-3-CM26</t>
+          <t>5780-1-CM26</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -2993,7 +2989,7 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>2026-01-21</t>
+          <t>2026-01-08</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
@@ -3003,12 +2999,12 @@
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>62.000.670-K</t>
+          <t>60.819.000-7</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>SUBSECRETARIA DE RELACIONES ECONOMICAS INTERNACIONALES</t>
+          <t>Superintendencia de Salud</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
@@ -3033,13 +3029,13 @@
         </is>
       </c>
       <c r="M42" s="2" t="n">
-        <v>66441.31</v>
+        <v>14614.26</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>785515-1-CM26</t>
+          <t>1186801-1-CM26</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -3054,7 +3050,7 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>2026-01-22</t>
+          <t>2026-01-12</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
@@ -3064,12 +3060,12 @@
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>65.074.471-3</t>
+          <t>60.930.000-0</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Servicio de Bienestar de los T.T.A.</t>
+          <t>CONSEJO NACIONAL DE EDUCACION</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
@@ -3094,13 +3090,13 @@
         </is>
       </c>
       <c r="M43" s="2" t="n">
-        <v>72653.84</v>
+        <v>1239.87</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2702-32-CM26</t>
+          <t>1211992-9-CM26</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -3115,22 +3111,22 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>2026-01-22</t>
+          <t>2026-01-13</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>69.071.800-6</t>
+          <t>65.192.585-1</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE TALAGANTE</t>
+          <t>CORPORACIÓN YUNUS</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
@@ -3155,13 +3151,13 @@
         </is>
       </c>
       <c r="M44" s="2" t="n">
-        <v>10967.55</v>
+        <v>1723.24</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>1273563-1-CM26</t>
+          <t>606-25-CM26</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -3176,7 +3172,7 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>2026-01-23</t>
+          <t>2026-01-14</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
@@ -3186,12 +3182,12 @@
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>62.000.740-4</t>
+          <t>60.513.000-3</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Servicio de Bienestar</t>
+          <t>SUBSECRETARIA DE TELECOMUNICACIONES</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
@@ -3216,13 +3212,13 @@
         </is>
       </c>
       <c r="M45" s="2" t="n">
-        <v>40771.06</v>
+        <v>5919.55</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>1373053-1-CM26</t>
+          <t>1221275-1-CM26</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -3237,22 +3233,22 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>2026-01-26</t>
+          <t>2026-01-15</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>82.174.900-k</t>
+          <t>60.108.000-1</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>SERVICIO DE COOPERACION TECNICA</t>
+          <t>AGENCIA CHILENA DE COOPERACION INTERNACIONAL PARA EL DESARROLLO</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
@@ -3277,13 +3273,13 @@
         </is>
       </c>
       <c r="M46" s="2" t="n">
-        <v>9557.92</v>
+        <v>46826.08</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>670784-1-CM26</t>
+          <t>2701-18-CM26</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -3298,7 +3294,7 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>2026-01-26</t>
+          <t>2026-01-15</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
@@ -3308,12 +3304,12 @@
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>60.818.000-1</t>
+          <t>69.071.800-6</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Superintendencia de Pensiones</t>
+          <t>I MUNICIPALIDAD DE TALAGANTE</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
@@ -3338,13 +3334,13 @@
         </is>
       </c>
       <c r="M47" s="2" t="n">
-        <v>10558.75</v>
+        <v>7952.53</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>543511-1-CM26</t>
+          <t>786370-1-CM26</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -3359,7 +3355,7 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>2026-01-27</t>
+          <t>2026-01-21</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
@@ -3369,12 +3365,12 @@
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>61.706.000-0</t>
+          <t>61.980.170-9</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>COMISIÓN CHILENA DEL COBRE - COCHILCO</t>
+          <t>SERVICIO NACIONAL PARA LA PREVENCION Y REHABILITACION DEL CONSUMO DE D</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
@@ -3399,13 +3395,13 @@
         </is>
       </c>
       <c r="M48" s="2" t="n">
-        <v>9592.43</v>
+        <v>66147.32000000001</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>626802-3-CM26</t>
+          <t>1157285-1-SE26</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -3420,7 +3416,7 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>2026-01-27</t>
+          <t>2026-01-21</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
@@ -3430,12 +3426,12 @@
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>65.034.169-4</t>
+          <t>62.000.860-5</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Consejo Resolutivo de Asignaciones Parlamentaria</t>
+          <t>Bienestar SSFFAA</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
@@ -3453,20 +3449,24 @@
           <t>96.573.600-K</t>
         </is>
       </c>
-      <c r="K49" t="inlineStr"/>
+      <c r="K49" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Región de Tarapacá  </t>
+        </is>
+      </c>
       <c r="L49" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M49" s="2" t="n">
-        <v>4695.24</v>
+        <v>50859.94</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>5134-2-CM26</t>
+          <t>1111089-31-CM26</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -3481,7 +3481,7 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>2026-01-30</t>
+          <t>2026-01-21</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
@@ -3491,12 +3491,12 @@
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>61.005.000-k</t>
+          <t>60.915.000-9</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Superintendencia de Insolvencia y Reemprendimiento</t>
+          <t>Agencia Nacional de Investigación y Desarrollo (ANID)</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
@@ -3521,13 +3521,13 @@
         </is>
       </c>
       <c r="M50" s="2" t="n">
-        <v>79768.07000000001</v>
+        <v>44161.73</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>1477-24-CM26</t>
+          <t>1153625-3-CM26</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -3542,7 +3542,7 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>2026-01-30</t>
+          <t>2026-01-21</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
@@ -3552,12 +3552,12 @@
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>70.786.200-9</t>
+          <t>62.000.670-K</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Corporación de Asistencia Judicial RM</t>
+          <t>SUBSECRETARIA DE RELACIONES ECONOMICAS INTERNACIONALES</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
@@ -3582,13 +3582,13 @@
         </is>
       </c>
       <c r="M51" s="2" t="n">
-        <v>37905.05</v>
+        <v>66441.31</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>550716-1-CM26</t>
+          <t>2702-32-CM26</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -3603,22 +3603,22 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>2026-01-30</t>
+          <t>2026-01-22</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>65.961.370-0</t>
+          <t>69.071.800-6</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Servicio de Bienestar del Personal del Gobierno Re</t>
+          <t>I MUNICIPALIDAD DE TALAGANTE</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
@@ -3643,13 +3643,13 @@
         </is>
       </c>
       <c r="M52" s="2" t="n">
-        <v>7256.26</v>
+        <v>10967.55</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>772003-2-CM26</t>
+          <t>785515-1-CM26</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -3664,7 +3664,7 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>2026-01-30</t>
+          <t>2026-01-22</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
@@ -3674,12 +3674,12 @@
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>61.979.930-5</t>
+          <t>65.074.471-3</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>SUBSECRETARIA DEL MEDIO AMBIENTE</t>
+          <t>Servicio de Bienestar de los T.T.A.</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
@@ -3704,13 +3704,13 @@
         </is>
       </c>
       <c r="M53" s="2" t="n">
-        <v>62058.74</v>
+        <v>72653.84</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>307-11-CM26</t>
+          <t>1273563-1-CM26</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -3720,12 +3720,12 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>feb-2026</t>
+          <t>ene-2026</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>2026-02-03</t>
+          <t>2026-01-23</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
@@ -3735,12 +3735,12 @@
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>60.919.000-0</t>
+          <t>62.000.740-4</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Consejo de Rectores de las Universidades Chilenas</t>
+          <t>Servicio de Bienestar</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
@@ -3765,13 +3765,13 @@
         </is>
       </c>
       <c r="M54" s="2" t="n">
-        <v>646.6799999999999</v>
+        <v>40771.06</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>606591-5-CM26</t>
+          <t>670784-1-CM26</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -3781,27 +3781,27 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>feb-2026</t>
+          <t>ene-2026</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>2026-02-05</t>
+          <t>2026-01-26</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>60.718.000-8</t>
+          <t>60.818.000-1</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>COMISION NACIONAL DE RIEGO</t>
+          <t>Superintendencia de Pensiones</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
@@ -3826,13 +3826,13 @@
         </is>
       </c>
       <c r="M55" s="2" t="n">
-        <v>32901.72</v>
+        <v>10558.75</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>606591-4-CM26</t>
+          <t>1373053-1-CM26</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -3842,27 +3842,27 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>feb-2026</t>
+          <t>ene-2026</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>2026-02-05</t>
+          <t>2026-01-26</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>60.718.000-8</t>
+          <t>82.174.900-k</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>COMISION NACIONAL DE RIEGO</t>
+          <t>SERVICIO DE COOPERACION TECNICA</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
@@ -3887,13 +3887,13 @@
         </is>
       </c>
       <c r="M56" s="2" t="n">
-        <v>35616.04</v>
+        <v>9557.92</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>931071-1-CM26</t>
+          <t>543511-1-CM26</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -3903,27 +3903,27 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>feb-2026</t>
+          <t>ene-2026</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>2026-02-06</t>
+          <t>2026-01-27</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>61.980.750-2</t>
+          <t>61.706.000-0</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Servicio de bienestar UAF</t>
+          <t>COMISIÓN CHILENA DEL COBRE - COCHILCO</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
@@ -3948,13 +3948,13 @@
         </is>
       </c>
       <c r="M57" s="2" t="n">
-        <v>29574.68</v>
+        <v>9592.43</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>1114502-2-CM26</t>
+          <t>626802-3-CM26</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -3964,12 +3964,12 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>feb-2026</t>
+          <t>ene-2026</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>2026-02-10</t>
+          <t>2026-01-27</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
@@ -3979,12 +3979,12 @@
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>65.081.366-9</t>
+          <t>65.034.169-4</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Servicio de bienestar del personal del CNTV</t>
+          <t>Consejo Resolutivo de Asignaciones Parlamentaria</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
@@ -4009,13 +4009,13 @@
         </is>
       </c>
       <c r="M58" s="2" t="n">
-        <v>47704.99</v>
+        <v>4695.24</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>543511-2-CM26</t>
+          <t>772003-2-CM26</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -4025,27 +4025,27 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>feb-2026</t>
+          <t>ene-2026</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>2026-02-12</t>
+          <t>2026-01-30</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>61.706.000-0</t>
+          <t>61.979.930-5</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>COMISIÓN CHILENA DEL COBRE - COCHILCO</t>
+          <t>SUBSECRETARIA DEL MEDIO AMBIENTE</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
@@ -4070,13 +4070,13 @@
         </is>
       </c>
       <c r="M59" s="2" t="n">
-        <v>48311.88</v>
+        <v>62058.74</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>609685-1-CM26</t>
+          <t>550716-1-CM26</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -4086,27 +4086,27 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>feb-2026</t>
+          <t>ene-2026</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>2026-02-13</t>
+          <t>2026-01-30</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>53.314.782-8</t>
+          <t>65.961.370-0</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Servicio de Bienestar Dirección de Compras y Contratación Pública</t>
+          <t>Servicio de Bienestar del Personal del Gobierno Re</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
@@ -4131,13 +4131,13 @@
         </is>
       </c>
       <c r="M60" s="2" t="n">
-        <v>68515.95</v>
+        <v>7256.26</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>1211992-22-CM26</t>
+          <t>1477-24-CM26</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -4147,27 +4147,27 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>feb-2026</t>
+          <t>ene-2026</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>2026-02-17</t>
+          <t>2026-01-30</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>65.192.585-1</t>
+          <t>70.786.200-9</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>CORPORACIÓN YUNUS</t>
+          <t>Corporación de Asistencia Judicial RM</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
@@ -4192,13 +4192,13 @@
         </is>
       </c>
       <c r="M61" s="2" t="n">
-        <v>1565.68</v>
+        <v>37905.05</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>2701-85-CM26</t>
+          <t>5134-2-CM26</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -4208,12 +4208,12 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>feb-2026</t>
+          <t>ene-2026</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>2026-02-17</t>
+          <t>2026-01-30</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
@@ -4223,12 +4223,12 @@
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>69.071.800-6</t>
+          <t>61.005.000-k</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE TALAGANTE</t>
+          <t>Superintendencia de Insolvencia y Reemprendimiento</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
@@ -4253,13 +4253,13 @@
         </is>
       </c>
       <c r="M62" s="2" t="n">
-        <v>8181.93</v>
+        <v>79768.07000000001</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>550716-2-CM26</t>
+          <t>307-11-CM26</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -4274,22 +4274,22 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>2026-02-19</t>
+          <t>2026-02-03</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>65.961.370-0</t>
+          <t>60.919.000-0</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Servicio de Bienestar del Personal del Gobierno Re</t>
+          <t>Consejo de Rectores de las Universidades Chilenas</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
@@ -4314,13 +4314,13 @@
         </is>
       </c>
       <c r="M63" s="2" t="n">
-        <v>7221.2</v>
+        <v>646.6799999999999</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>3378-1718-CM26</t>
+          <t>606591-4-CM26</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -4335,7 +4335,7 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>2026-02-25</t>
+          <t>2026-02-05</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
@@ -4345,12 +4345,12 @@
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>61.101.030-3</t>
+          <t>60.718.000-8</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>EJERCITO DE CHILE HOSPITAL MILITAR DE SANTIAGO</t>
+          <t>COMISION NACIONAL DE RIEGO</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
@@ -4375,13 +4375,13 @@
         </is>
       </c>
       <c r="M64" s="2" t="n">
-        <v>17394.98</v>
+        <v>35616.04</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>670784-2-CM26</t>
+          <t>606591-5-CM26</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -4396,7 +4396,7 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>2026-02-25</t>
+          <t>2026-02-05</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
@@ -4406,12 +4406,12 @@
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>60.818.000-1</t>
+          <t>60.718.000-8</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Superintendencia de Pensiones</t>
+          <t>COMISION NACIONAL DE RIEGO</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
@@ -4436,13 +4436,13 @@
         </is>
       </c>
       <c r="M65" s="2" t="n">
-        <v>10689.09</v>
+        <v>32901.72</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>1477-47-CM26</t>
+          <t>931071-1-CM26</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -4457,7 +4457,7 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>2026-02-25</t>
+          <t>2026-02-06</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
@@ -4467,12 +4467,12 @@
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>70.786.200-9</t>
+          <t>61.980.750-2</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Corporación de Asistencia Judicial RM</t>
+          <t>Servicio de bienestar UAF</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
@@ -4497,13 +4497,13 @@
         </is>
       </c>
       <c r="M66" s="2" t="n">
-        <v>37714.34</v>
+        <v>29574.68</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>1186801-2-CM26</t>
+          <t>1114502-2-CM26</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -4518,7 +4518,7 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>2026-02-26</t>
+          <t>2026-02-10</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
@@ -4528,12 +4528,12 @@
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>60.930.000-0</t>
+          <t>65.081.366-9</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>CONSEJO NACIONAL DE EDUCACION</t>
+          <t>Servicio de bienestar del personal del CNTV</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
@@ -4558,13 +4558,13 @@
         </is>
       </c>
       <c r="M67" s="2" t="n">
-        <v>1295.55</v>
+        <v>47704.99</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>1373053-2-CM26</t>
+          <t>543511-2-CM26</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -4579,22 +4579,22 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>2026-02-27</t>
+          <t>2026-02-12</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>82.174.900-k</t>
+          <t>61.706.000-0</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>SERVICIO DE COOPERACION TECNICA</t>
+          <t>COMISIÓN CHILENA DEL COBRE - COCHILCO</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
@@ -4619,13 +4619,13 @@
         </is>
       </c>
       <c r="M68" s="2" t="n">
-        <v>9730.34</v>
+        <v>48311.88</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>3378-1719-CM26</t>
+          <t>609685-1-CM26</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -4635,27 +4635,27 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>mar-2026</t>
+          <t>feb-2026</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-02-13</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>61.101.030-3</t>
+          <t>53.314.782-8</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>EJERCITO DE CHILE HOSPITAL MILITAR DE SANTIAGO</t>
+          <t>Servicio de Bienestar Dirección de Compras y Contratación Pública</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
@@ -4680,13 +4680,13 @@
         </is>
       </c>
       <c r="M69" s="2" t="n">
-        <v>17036</v>
+        <v>68515.95</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>307-14-CM26</t>
+          <t>1211992-22-CM26</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -4696,27 +4696,27 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>mar-2026</t>
+          <t>feb-2026</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-02-17</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>60.919.000-0</t>
+          <t>65.192.585-1</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Consejo de Rectores de las Universidades Chilenas</t>
+          <t>CORPORACIÓN YUNUS</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
@@ -4741,13 +4741,13 @@
         </is>
       </c>
       <c r="M70" s="2" t="n">
-        <v>646.22</v>
+        <v>1565.68</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>2702-83-CM26</t>
+          <t>2701-85-CM26</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -4757,12 +4757,12 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>mar-2026</t>
+          <t>feb-2026</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-02-17</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
@@ -4802,13 +4802,13 @@
         </is>
       </c>
       <c r="M71" s="2" t="n">
-        <v>11123.51</v>
+        <v>8181.93</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>574800-3-SE26</t>
+          <t>550716-2-CM26</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -4818,27 +4818,27 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>mar-2026</t>
+          <t>feb-2026</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2026-02-19</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>60.601.000-1</t>
+          <t>65.961.370-0</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Subsecretaria de Relaciones Exteriores</t>
+          <t>Servicio de Bienestar del Personal del Gobierno Re</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
@@ -4856,24 +4856,20 @@
           <t>96.573.600-K</t>
         </is>
       </c>
-      <c r="K72" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Región de Tarapacá  </t>
-        </is>
-      </c>
+      <c r="K72" t="inlineStr"/>
       <c r="L72" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M72" s="2" t="n">
-        <v>716564.4</v>
+        <v>7221.2</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>575437-3-CM26</t>
+          <t>3378-1718-CM26</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -4883,27 +4879,27 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>mar-2026</t>
+          <t>feb-2026</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2026-02-25</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>60.805.312-3</t>
+          <t>61.101.030-3</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Bienestar</t>
+          <t>EJERCITO DE CHILE HOSPITAL MILITAR DE SANTIAGO</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
@@ -4928,13 +4924,13 @@
         </is>
       </c>
       <c r="M73" s="2" t="n">
-        <v>1064847.91</v>
+        <v>17394.98</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>593951-78-SE26</t>
+          <t>670784-2-CM26</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -4944,27 +4940,27 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>mar-2026</t>
+          <t>feb-2026</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-02-25</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>70.574.900-0</t>
+          <t>60.818.000-1</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>FUNDACION EDUCACIONAL PARA EL DESAROLLO INTEGRAL DE LA NIÑEZ</t>
+          <t>Superintendencia de Pensiones</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
@@ -4982,24 +4978,20 @@
           <t>96.573.600-K</t>
         </is>
       </c>
-      <c r="K74" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Región de Tarapacá  </t>
-        </is>
-      </c>
+      <c r="K74" t="inlineStr"/>
       <c r="L74" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M74" s="2" t="n">
-        <v>5472729.65</v>
+        <v>10689.09</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>2413-18-SE26</t>
+          <t>1477-47-CM26</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -5009,27 +5001,27 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>mar-2026</t>
+          <t>feb-2026</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-02-25</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>69.254.100-6</t>
+          <t>70.786.200-9</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE LO PRADO</t>
+          <t>Corporación de Asistencia Judicial RM</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
@@ -5047,24 +5039,20 @@
           <t>96.573.600-K</t>
         </is>
       </c>
-      <c r="K75" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Región de Tarapacá  </t>
-        </is>
-      </c>
+      <c r="K75" t="inlineStr"/>
       <c r="L75" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M75" s="2" t="n">
-        <v>317672.53</v>
+        <v>37714.34</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>1211992-29-CM26</t>
+          <t>1186801-2-CM26</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -5074,27 +5062,27 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>mar-2026</t>
+          <t>feb-2026</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-02-26</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>65.192.585-1</t>
+          <t>60.930.000-0</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>CORPORACIÓN YUNUS</t>
+          <t>CONSEJO NACIONAL DE EDUCACION</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
@@ -5119,13 +5107,13 @@
         </is>
       </c>
       <c r="M76" s="2" t="n">
-        <v>1240.09</v>
+        <v>1295.55</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>2403-118-CM26</t>
+          <t>1373053-2-CM26</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -5135,27 +5123,27 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>mar-2026</t>
+          <t>feb-2026</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>2026-03-13</t>
+          <t>2026-02-27</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>69.254.000-k</t>
+          <t>82.174.900-k</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE PENALOLEN</t>
+          <t>SERVICIO DE COOPERACION TECNICA</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
@@ -5180,13 +5168,13 @@
         </is>
       </c>
       <c r="M77" s="2" t="n">
-        <v>296262.25</v>
+        <v>9730.34</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>2701-151-CM26</t>
+          <t>3378-1719-CM26</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -5201,22 +5189,22 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2026-03-02</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>69.071.800-6</t>
+          <t>61.101.030-3</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE TALAGANTE</t>
+          <t>EJERCITO DE CHILE HOSPITAL MILITAR DE SANTIAGO</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
@@ -5241,13 +5229,13 @@
         </is>
       </c>
       <c r="M78" s="2" t="n">
-        <v>7784.67</v>
+        <v>17036</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>2702-134-CM26</t>
+          <t>307-14-CM26</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -5262,7 +5250,7 @@
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-02</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
@@ -5272,12 +5260,12 @@
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>69.071.800-6</t>
+          <t>60.919.000-0</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE TALAGANTE</t>
+          <t>Consejo de Rectores de las Universidades Chilenas</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
@@ -5302,13 +5290,13 @@
         </is>
       </c>
       <c r="M79" s="2" t="n">
-        <v>10643.09</v>
+        <v>646.22</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>670784-3-CM26</t>
+          <t>2702-83-CM26</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -5323,7 +5311,7 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2026-03-02</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
@@ -5333,12 +5321,12 @@
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>60.818.000-1</t>
+          <t>69.071.800-6</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Superintendencia de Pensiones</t>
+          <t>I MUNICIPALIDAD DE TALAGANTE</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
@@ -5363,13 +5351,13 @@
         </is>
       </c>
       <c r="M80" s="2" t="n">
-        <v>10139.47</v>
+        <v>11123.51</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>1149280-4-SE26</t>
+          <t>575437-3-CM26</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -5384,7 +5372,7 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>2026-03-27</t>
+          <t>2026-03-03</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
@@ -5394,12 +5382,12 @@
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>60.400.000-9</t>
+          <t>60.805.312-3</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>CONTRALORIA GENERAL DE LA REPUBLICA</t>
+          <t>Bienestar</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
@@ -5417,24 +5405,20 @@
           <t>96.573.600-K</t>
         </is>
       </c>
-      <c r="K81" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Región de Tarapacá  </t>
-        </is>
-      </c>
+      <c r="K81" t="inlineStr"/>
       <c r="L81" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M81" s="2" t="n">
-        <v>717480.3100000001</v>
+        <v>1064847.91</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>1211992-40-CM26</t>
+          <t>574800-3-SE26</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -5449,22 +5433,22 @@
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>2026-03-27</t>
+          <t>2026-03-03</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>65.192.585-1</t>
+          <t>60.601.000-1</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>CORPORACIÓN YUNUS</t>
+          <t>Subsecretaria de Relaciones Exteriores</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
@@ -5482,20 +5466,24 @@
           <t>96.573.600-K</t>
         </is>
       </c>
-      <c r="K82" t="inlineStr"/>
+      <c r="K82" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Región de Tarapacá  </t>
+        </is>
+      </c>
       <c r="L82" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M82" s="2" t="n">
-        <v>189.36</v>
+        <v>716564.4</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>1186801-3-CM26</t>
+          <t>593951-78-SE26</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -5510,7 +5498,7 @@
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>2026-03-27</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
@@ -5520,12 +5508,12 @@
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>60.930.000-0</t>
+          <t>70.574.900-0</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>CONSEJO NACIONAL DE EDUCACION</t>
+          <t>FUNDACION EDUCACIONAL PARA EL DESAROLLO INTEGRAL DE LA NIÑEZ</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
@@ -5543,20 +5531,24 @@
           <t>96.573.600-K</t>
         </is>
       </c>
-      <c r="K83" t="inlineStr"/>
+      <c r="K83" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Región de Tarapacá  </t>
+        </is>
+      </c>
       <c r="L83" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M83" s="2" t="n">
-        <v>1205.28</v>
+        <v>5472729.65</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>772003-3-CM26</t>
+          <t>2413-18-SE26</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -5571,22 +5563,22 @@
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-03-06</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>61.979.930-5</t>
+          <t>69.254.100-6</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>SUBSECRETARIA DEL MEDIO AMBIENTE</t>
+          <t>I MUNICIPALIDAD DE LO PRADO</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
@@ -5604,20 +5596,24 @@
           <t>96.573.600-K</t>
         </is>
       </c>
-      <c r="K84" t="inlineStr"/>
+      <c r="K84" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Región de Tarapacá  </t>
+        </is>
+      </c>
       <c r="L84" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M84" s="2" t="n">
-        <v>57482.4</v>
+        <v>317672.53</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>1477-81-CM26</t>
+          <t>1211992-29-CM26</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -5632,22 +5628,22 @@
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>70.786.200-9</t>
+          <t>65.192.585-1</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Corporación de Asistencia Judicial RM</t>
+          <t>CORPORACIÓN YUNUS</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
@@ -5672,13 +5668,13 @@
         </is>
       </c>
       <c r="M85" s="2" t="n">
-        <v>35281.5</v>
+        <v>1240.09</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>1373053-3-CM26</t>
+          <t>2403-118-CM26</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -5688,27 +5684,27 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>abr-2026</t>
+          <t>mar-2026</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>2026-04-02</t>
+          <t>2026-03-13</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>82.174.900-k</t>
+          <t>69.254.000-k</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>SERVICIO DE COOPERACION TECNICA</t>
+          <t>I MUNICIPALIDAD DE PENALOLEN</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
@@ -5733,13 +5729,13 @@
         </is>
       </c>
       <c r="M86" s="2" t="n">
-        <v>9257.09</v>
+        <v>296262.25</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>307-30-CM26</t>
+          <t>2701-151-CM26</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -5749,12 +5745,12 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>abr-2026</t>
+          <t>mar-2026</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>2026-04-02</t>
+          <t>2026-03-24</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
@@ -5764,12 +5760,12 @@
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>60.919.000-0</t>
+          <t>69.071.800-6</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Consejo de Rectores de las Universidades Chilenas</t>
+          <t>I MUNICIPALIDAD DE TALAGANTE</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
@@ -5794,13 +5790,13 @@
         </is>
       </c>
       <c r="M87" s="2" t="n">
-        <v>683.78</v>
+        <v>7784.67</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>603663-54-CM26</t>
+          <t>2702-134-CM26</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -5810,12 +5806,12 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>abr-2026</t>
+          <t>mar-2026</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>2026-04-02</t>
+          <t>2026-03-25</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
@@ -5825,12 +5821,12 @@
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>65.028.707-K</t>
+          <t>69.071.800-6</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>INSTITUTO NACIONAL DE DERECHOS HUMANOS</t>
+          <t>I MUNICIPALIDAD DE TALAGANTE</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
@@ -5855,13 +5851,13 @@
         </is>
       </c>
       <c r="M88" s="2" t="n">
-        <v>76156.3</v>
+        <v>10643.09</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>550716-3-CM26</t>
+          <t>670784-3-CM26</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -5871,27 +5867,27 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>abr-2026</t>
+          <t>mar-2026</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>2026-04-06</t>
+          <t>2026-03-26</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>65.961.370-0</t>
+          <t>60.818.000-1</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Servicio de Bienestar del Personal del Gobierno Re</t>
+          <t>Superintendencia de Pensiones</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
@@ -5916,13 +5912,13 @@
         </is>
       </c>
       <c r="M89" s="2" t="n">
-        <v>6777.5</v>
+        <v>10139.47</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>1211992-43-CM26</t>
+          <t>1149280-4-SE26</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -5932,27 +5928,27 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>abr-2026</t>
+          <t>mar-2026</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>2026-04-07</t>
+          <t>2026-03-27</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>65.192.585-1</t>
+          <t>60.400.000-9</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>CORPORACIÓN YUNUS</t>
+          <t>CONTRALORIA GENERAL DE LA REPUBLICA</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
@@ -5970,20 +5966,24 @@
           <t>96.573.600-K</t>
         </is>
       </c>
-      <c r="K90" t="inlineStr"/>
+      <c r="K90" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Región de Tarapacá  </t>
+        </is>
+      </c>
       <c r="L90" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M90" s="2" t="n">
-        <v>1242.65</v>
+        <v>717480.3100000001</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>2490-79-CM26</t>
+          <t>1211992-40-CM26</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -5993,27 +5993,27 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>abr-2026</t>
+          <t>mar-2026</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>2026-04-09</t>
+          <t>2026-03-27</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>69.070.300-9</t>
+          <t>65.192.585-1</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE PROVIDENCIA</t>
+          <t>CORPORACIÓN YUNUS</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
@@ -6031,24 +6031,20 @@
           <t>96.573.600-K</t>
         </is>
       </c>
-      <c r="K91" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Región de Tarapacá  </t>
-        </is>
-      </c>
+      <c r="K91" t="inlineStr"/>
       <c r="L91" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M91" s="2" t="n">
-        <v>44910.95</v>
+        <v>189.36</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>5482-80-CM26</t>
+          <t>1186801-3-CM26</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -6058,12 +6054,12 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>abr-2026</t>
+          <t>mar-2026</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-03-27</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
@@ -6073,12 +6069,12 @@
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>69.070.500-1</t>
+          <t>60.930.000-0</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE NUNOA</t>
+          <t>CONSEJO NACIONAL DE EDUCACION</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
@@ -6103,13 +6099,13 @@
         </is>
       </c>
       <c r="M92" s="2" t="n">
-        <v>22072.83</v>
+        <v>1205.28</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>5482-81-CM26</t>
+          <t>772003-3-CM26</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -6119,12 +6115,12 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>abr-2026</t>
+          <t>mar-2026</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-03-30</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
@@ -6134,12 +6130,12 @@
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>69.070.500-1</t>
+          <t>61.979.930-5</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE NUNOA</t>
+          <t>SUBSECRETARIA DEL MEDIO AMBIENTE</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
@@ -6164,13 +6160,13 @@
         </is>
       </c>
       <c r="M93" s="2" t="n">
-        <v>22072.83</v>
+        <v>57482.4</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>2701-207-CM26</t>
+          <t>1477-81-CM26</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -6180,12 +6176,12 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>abr-2026</t>
+          <t>mar-2026</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
@@ -6195,12 +6191,12 @@
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>69.071.800-6</t>
+          <t>70.786.200-9</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE TALAGANTE</t>
+          <t>Corporación de Asistencia Judicial RM</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
@@ -6225,13 +6221,13 @@
         </is>
       </c>
       <c r="M94" s="2" t="n">
-        <v>8109.27</v>
+        <v>35281.5</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>2702-184-CM26</t>
+          <t>603663-54-CM26</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -6246,7 +6242,7 @@
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-04-02</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
@@ -6256,12 +6252,12 @@
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>69.071.800-6</t>
+          <t>65.028.707-K</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE TALAGANTE</t>
+          <t>INSTITUTO NACIONAL DE DERECHOS HUMANOS</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
@@ -6286,13 +6282,13 @@
         </is>
       </c>
       <c r="M95" s="2" t="n">
-        <v>11025.85</v>
+        <v>76156.3</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>550716-4-CM26</t>
+          <t>307-30-CM26</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -6307,22 +6303,22 @@
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-02</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>65.961.370-0</t>
+          <t>60.919.000-0</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Servicio de Bienestar del Personal del Gobierno Re</t>
+          <t>Consejo de Rectores de las Universidades Chilenas</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
@@ -6347,13 +6343,13 @@
         </is>
       </c>
       <c r="M96" s="2" t="n">
-        <v>7154.89</v>
+        <v>683.78</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>1495206-1-CM26</t>
+          <t>1373053-3-CM26</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -6368,7 +6364,7 @@
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-02</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
@@ -6378,12 +6374,12 @@
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>61.981.340-5</t>
+          <t>82.174.900-k</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Servicio de Biodiversidad y Áreas Protegidas</t>
+          <t>SERVICIO DE COOPERACION TECNICA</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
@@ -6408,13 +6404,13 @@
         </is>
       </c>
       <c r="M97" s="2" t="n">
-        <v>3227.45</v>
+        <v>9257.09</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>1477-108-CM26</t>
+          <t>550716-3-CM26</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -6429,22 +6425,22 @@
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-06</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>70.786.200-9</t>
+          <t>65.961.370-0</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Corporación de Asistencia Judicial RM</t>
+          <t>Servicio de Bienestar del Personal del Gobierno Re</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
@@ -6469,13 +6465,13 @@
         </is>
       </c>
       <c r="M98" s="2" t="n">
-        <v>36973.69</v>
+        <v>6777.5</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>1186801-4-CM26</t>
+          <t>1211992-43-CM26</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -6490,22 +6486,22 @@
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-07</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>60.930.000-0</t>
+          <t>65.192.585-1</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>CONSEJO NACIONAL DE EDUCACION</t>
+          <t>CORPORACIÓN YUNUS</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
@@ -6530,13 +6526,13 @@
         </is>
       </c>
       <c r="M99" s="2" t="n">
-        <v>1168.85</v>
+        <v>1242.65</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>772003-4-CM26</t>
+          <t>2490-79-CM26</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -6551,7 +6547,7 @@
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>2026-04-29</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
@@ -6561,12 +6557,12 @@
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>61.979.930-5</t>
+          <t>69.070.300-9</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>SUBSECRETARIA DEL MEDIO AMBIENTE</t>
+          <t>I MUNICIPALIDAD DE PROVIDENCIA</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
@@ -6584,20 +6580,24 @@
           <t>96.573.600-K</t>
         </is>
       </c>
-      <c r="K100" t="inlineStr"/>
+      <c r="K100" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Región de Tarapacá  </t>
+        </is>
+      </c>
       <c r="L100" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M100" s="2" t="n">
-        <v>35697.47</v>
+        <v>44910.95</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>307-44-CM26</t>
+          <t>5482-80-CM26</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -6607,12 +6607,12 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>may-2026</t>
+          <t>abr-2026</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>2026-05-05</t>
+          <t>2026-04-14</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
@@ -6622,12 +6622,12 @@
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>60.919.000-0</t>
+          <t>69.070.500-1</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Consejo de Rectores de las Universidades Chilenas</t>
+          <t>I MUNICIPALIDAD DE NUNOA</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
@@ -6652,13 +6652,13 @@
         </is>
       </c>
       <c r="M101" s="2" t="n">
-        <v>694.21</v>
+        <v>22072.83</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>1373053-5-CM26</t>
+          <t>5482-81-CM26</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -6668,12 +6668,12 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>may-2026</t>
+          <t>abr-2026</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2026-04-14</t>
         </is>
       </c>
       <c r="E102" t="inlineStr">
@@ -6683,12 +6683,12 @@
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>82.174.900-k</t>
+          <t>69.070.500-1</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>SERVICIO DE COOPERACION TECNICA</t>
+          <t>I MUNICIPALIDAD DE NUNOA</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
@@ -6713,13 +6713,13 @@
         </is>
       </c>
       <c r="M102" s="2" t="n">
-        <v>9595.75</v>
+        <v>22072.83</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>1211992-69-CM26</t>
+          <t>2701-207-CM26</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -6729,27 +6729,27 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>may-2026</t>
+          <t>abr-2026</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2026-04-20</t>
         </is>
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>65.192.585-1</t>
+          <t>69.071.800-6</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>CORPORACIÓN YUNUS</t>
+          <t>I MUNICIPALIDAD DE TALAGANTE</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
@@ -6774,13 +6774,13 @@
         </is>
       </c>
       <c r="M103" s="2" t="n">
-        <v>1266.44</v>
+        <v>8109.27</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>606591-6-CM26</t>
+          <t>2702-184-CM26</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -6790,27 +6790,27 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>may-2026</t>
+          <t>abr-2026</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>2026-05-12</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>60.718.000-8</t>
+          <t>69.071.800-6</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>COMISION NACIONAL DE RIEGO</t>
+          <t>I MUNICIPALIDAD DE TALAGANTE</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
@@ -6835,13 +6835,13 @@
         </is>
       </c>
       <c r="M104" s="2" t="n">
-        <v>31632.24</v>
+        <v>11025.85</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>670784-6-CM26</t>
+          <t>550716-4-CM26</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -6851,27 +6851,27 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>may-2026</t>
+          <t>abr-2026</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-04-23</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>60.818.000-1</t>
+          <t>65.961.370-0</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Superintendencia de Pensiones</t>
+          <t>Servicio de Bienestar del Personal del Gobierno Re</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
@@ -6896,13 +6896,13 @@
         </is>
       </c>
       <c r="M105" s="2" t="n">
-        <v>10269.21</v>
+        <v>7154.89</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>2667-214-CM26</t>
+          <t>1495206-1-CM26</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
@@ -6912,12 +6912,12 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>may-2026</t>
+          <t>abr-2026</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>2026-05-15</t>
+          <t>2026-04-24</t>
         </is>
       </c>
       <c r="E106" t="inlineStr">
@@ -6927,12 +6927,12 @@
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>69.255.600-3</t>
+          <t>61.981.340-5</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE VITACURA</t>
+          <t>Servicio de Biodiversidad y Áreas Protegidas</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
@@ -6957,13 +6957,13 @@
         </is>
       </c>
       <c r="M106" s="2" t="n">
-        <v>361779.55</v>
+        <v>3227.45</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>2701-300-CM26</t>
+          <t>1477-108-CM26</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
@@ -6973,12 +6973,12 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>may-2026</t>
+          <t>abr-2026</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
+          <t>2026-04-24</t>
         </is>
       </c>
       <c r="E107" t="inlineStr">
@@ -6988,12 +6988,12 @@
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>69.071.800-6</t>
+          <t>70.786.200-9</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE TALAGANTE</t>
+          <t>Corporación de Asistencia Judicial RM</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
@@ -7018,13 +7018,13 @@
         </is>
       </c>
       <c r="M107" s="2" t="n">
-        <v>8014.09</v>
+        <v>36973.69</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>1186801-5-CM26</t>
+          <t>1186801-4-CM26</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -7034,12 +7034,12 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>may-2026</t>
+          <t>abr-2026</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2026-04-28</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
@@ -7079,13 +7079,13 @@
         </is>
       </c>
       <c r="M108" s="2" t="n">
-        <v>1161.2</v>
+        <v>1168.85</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>670784-7-CM26</t>
+          <t>772003-4-CM26</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
@@ -7095,12 +7095,12 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>may-2026</t>
+          <t>abr-2026</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>2026-05-25</t>
+          <t>2026-04-29</t>
         </is>
       </c>
       <c r="E109" t="inlineStr">
@@ -7110,12 +7110,12 @@
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>60.818.000-1</t>
+          <t>61.979.930-5</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Superintendencia de Pensiones</t>
+          <t>SUBSECRETARIA DEL MEDIO AMBIENTE</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
@@ -7140,13 +7140,13 @@
         </is>
       </c>
       <c r="M109" s="2" t="n">
-        <v>10321.26</v>
+        <v>35697.47</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>1111089-91-CM26</t>
+          <t>307-44-CM26</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
@@ -7161,7 +7161,7 @@
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>2026-05-26</t>
+          <t>2026-05-05</t>
         </is>
       </c>
       <c r="E110" t="inlineStr">
@@ -7171,12 +7171,12 @@
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>60.915.000-9</t>
+          <t>60.919.000-0</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>Agencia Nacional de Investigación y Desarrollo (ANID)</t>
+          <t>Consejo de Rectores de las Universidades Chilenas</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
@@ -7194,24 +7194,20 @@
           <t>96.573.600-K</t>
         </is>
       </c>
-      <c r="K110" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Región de Tarapacá  </t>
-        </is>
-      </c>
+      <c r="K110" t="inlineStr"/>
       <c r="L110" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M110" s="2" t="n">
-        <v>160141.93</v>
+        <v>694.21</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>1373053-6-CM26</t>
+          <t>1373053-5-CM26</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
@@ -7226,7 +7222,7 @@
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>2026-05-27</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="E111" t="inlineStr">
@@ -7266,13 +7262,13 @@
         </is>
       </c>
       <c r="M111" s="2" t="n">
-        <v>9494.969999999999</v>
+        <v>9595.75</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>550716-6-CM26</t>
+          <t>1211992-69-CM26</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
@@ -7287,7 +7283,7 @@
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>2026-05-29</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="E112" t="inlineStr">
@@ -7297,12 +7293,12 @@
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>65.961.370-0</t>
+          <t>65.192.585-1</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>Servicio de Bienestar del Personal del Gobierno Re</t>
+          <t>CORPORACIÓN YUNUS</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
@@ -7327,13 +7323,13 @@
         </is>
       </c>
       <c r="M112" s="2" t="n">
-        <v>7328.32</v>
+        <v>1266.44</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>1495206-3-CM26</t>
+          <t>606591-6-CM26</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
@@ -7348,22 +7344,22 @@
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>2026-05-29</t>
+          <t>2026-05-12</t>
         </is>
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>61.981.340-5</t>
+          <t>60.718.000-8</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>Servicio de Biodiversidad y Áreas Protegidas</t>
+          <t>COMISION NACIONAL DE RIEGO</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
@@ -7388,13 +7384,13 @@
         </is>
       </c>
       <c r="M113" s="2" t="n">
-        <v>3547.07</v>
+        <v>31632.24</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>307-48-CM26</t>
+          <t>670784-6-CM26</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
@@ -7404,12 +7400,12 @@
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>jun-2026</t>
+          <t>may-2026</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="E114" t="inlineStr">
@@ -7419,12 +7415,12 @@
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>60.919.000-0</t>
+          <t>60.818.000-1</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>Consejo de Rectores de las Universidades Chilenas</t>
+          <t>Superintendencia de Pensiones</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
@@ -7449,13 +7445,13 @@
         </is>
       </c>
       <c r="M114" s="2" t="n">
-        <v>717.09</v>
+        <v>10269.21</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>2702-247-CM26</t>
+          <t>2667-214-CM26</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
@@ -7465,12 +7461,12 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>jun-2026</t>
+          <t>may-2026</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="E115" t="inlineStr">
@@ -7480,12 +7476,12 @@
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>69.071.800-6</t>
+          <t>69.255.600-3</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE TALAGANTE</t>
+          <t>I MUNICIPALIDAD DE VITACURA</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
@@ -7510,13 +7506,13 @@
         </is>
       </c>
       <c r="M115" s="2" t="n">
-        <v>10958.97</v>
+        <v>361779.55</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>1477-163-CM26</t>
+          <t>2701-300-CM26</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
@@ -7526,12 +7522,12 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>jun-2026</t>
+          <t>may-2026</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-05-19</t>
         </is>
       </c>
       <c r="E116" t="inlineStr">
@@ -7541,12 +7537,12 @@
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>70.786.200-9</t>
+          <t>69.071.800-6</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Corporación de Asistencia Judicial RM</t>
+          <t>I MUNICIPALIDAD DE TALAGANTE</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
@@ -7571,13 +7567,13 @@
         </is>
       </c>
       <c r="M116" s="2" t="n">
-        <v>37700.6</v>
+        <v>8014.09</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>692264-2-SE26</t>
+          <t>1186801-5-CM26</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
@@ -7587,12 +7583,12 @@
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>jun-2026</t>
+          <t>may-2026</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>2026-06-03</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="E117" t="inlineStr">
@@ -7602,12 +7598,12 @@
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>60.910.047-8</t>
+          <t>60.930.000-0</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD METROPOLITANA DE CIENCIAS DE LA EDUCACION</t>
+          <t>CONSEJO NACIONAL DE EDUCACION</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
@@ -7625,24 +7621,20 @@
           <t>96.573.600-K</t>
         </is>
       </c>
-      <c r="K117" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Región de Tarapacá  </t>
-        </is>
-      </c>
+      <c r="K117" t="inlineStr"/>
       <c r="L117" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M117" s="2" t="n">
-        <v>449847.9</v>
+        <v>1161.2</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>1211992-116-CM26</t>
+          <t>670784-7-CM26</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
@@ -7652,27 +7644,27 @@
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>jun-2026</t>
+          <t>may-2026</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>2026-06-03</t>
+          <t>2026-05-25</t>
         </is>
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>65.192.585-1</t>
+          <t>60.818.000-1</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>CORPORACIÓN YUNUS</t>
+          <t>Superintendencia de Pensiones</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
@@ -7697,13 +7689,13 @@
         </is>
       </c>
       <c r="M118" s="2" t="n">
-        <v>1405.91</v>
+        <v>10321.26</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>1515286-3-SE26</t>
+          <t>1111089-91-CM26</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
@@ -7713,12 +7705,12 @@
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>jun-2026</t>
+          <t>may-2026</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>2026-06-05</t>
+          <t>2026-05-26</t>
         </is>
       </c>
       <c r="E119" t="inlineStr">
@@ -7728,12 +7720,12 @@
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>53.337.014-4</t>
+          <t>60.915.000-9</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t xml:space="preserve">Fondo de Bienestar de la Corporación de Fomento </t>
+          <t>Agencia Nacional de Investigación y Desarrollo (ANID)</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
@@ -7762,13 +7754,13 @@
         </is>
       </c>
       <c r="M119" s="2" t="n">
-        <v>805575.1800000001</v>
+        <v>160141.93</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>2701-376-CM26</t>
+          <t>1373053-6-CM26</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
@@ -7778,12 +7770,12 @@
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>jun-2026</t>
+          <t>may-2026</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-05-27</t>
         </is>
       </c>
       <c r="E120" t="inlineStr">
@@ -7793,12 +7785,12 @@
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>69.071.800-6</t>
+          <t>82.174.900-k</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE TALAGANTE</t>
+          <t>SERVICIO DE COOPERACION TECNICA</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
@@ -7823,13 +7815,13 @@
         </is>
       </c>
       <c r="M120" s="2" t="n">
-        <v>8058.6</v>
+        <v>9494.969999999999</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>550716-8-CM26</t>
+          <t>550716-6-CM26</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
@@ -7839,17 +7831,17 @@
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>jun-2026</t>
+          <t>may-2026</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-05-29</t>
         </is>
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
@@ -7884,13 +7876,13 @@
         </is>
       </c>
       <c r="M121" s="2" t="n">
-        <v>7338</v>
+        <v>7328.32</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>1342-4-SE26</t>
+          <t>1495206-3-CM26</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
@@ -7900,12 +7892,12 @@
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>jun-2026</t>
+          <t>may-2026</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-05-29</t>
         </is>
       </c>
       <c r="E122" t="inlineStr">
@@ -7915,12 +7907,12 @@
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>60.109.000-7</t>
+          <t>61.981.340-5</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>FONDO DE SOLIDARIDAD E INVERSION SOCIAL</t>
+          <t>Servicio de Biodiversidad y Áreas Protegidas</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
@@ -7938,24 +7930,20 @@
           <t>96.573.600-K</t>
         </is>
       </c>
-      <c r="K122" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Región de Tarapacá  </t>
-        </is>
-      </c>
+      <c r="K122" t="inlineStr"/>
       <c r="L122" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M122" s="2" t="n">
-        <v>286656.49</v>
+        <v>3547.07</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>1157285-8-CM26</t>
+          <t>2702-247-CM26</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
@@ -7970,7 +7958,7 @@
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="E123" t="inlineStr">
@@ -7980,12 +7968,12 @@
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>62.000.860-5</t>
+          <t>69.071.800-6</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>Bienestar SSFFAA</t>
+          <t>I MUNICIPALIDAD DE TALAGANTE</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
@@ -8010,13 +7998,13 @@
         </is>
       </c>
       <c r="M123" s="2" t="n">
-        <v>51470.7</v>
+        <v>10958.97</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>670784-8-CM26</t>
+          <t>307-48-CM26</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
@@ -8031,7 +8019,7 @@
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="E124" t="inlineStr">
@@ -8041,12 +8029,12 @@
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>60.818.000-1</t>
+          <t>60.919.000-0</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>Superintendencia de Pensiones</t>
+          <t>Consejo de Rectores de las Universidades Chilenas</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
@@ -8071,13 +8059,13 @@
         </is>
       </c>
       <c r="M124" s="2" t="n">
-        <v>10377.13</v>
+        <v>717.09</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>4700-10-CM26</t>
+          <t>1477-163-CM26</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
@@ -8092,7 +8080,7 @@
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-02</t>
         </is>
       </c>
       <c r="E125" t="inlineStr">
@@ -8102,12 +8090,12 @@
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>73.362.800-6</t>
+          <t>70.786.200-9</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>BIENESTAR DEL CONSEJO DE DEFENSA DEL ESTADO</t>
+          <t>Corporación de Asistencia Judicial RM</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
@@ -8132,13 +8120,13 @@
         </is>
       </c>
       <c r="M125" s="2" t="n">
-        <v>310935.41</v>
+        <v>37700.6</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>1477-194-CM26</t>
+          <t>1211992-116-CM26</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
@@ -8153,22 +8141,22 @@
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-03</t>
         </is>
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>70.786.200-9</t>
+          <t>65.192.585-1</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>Corporación de Asistencia Judicial RM</t>
+          <t>CORPORACIÓN YUNUS</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
@@ -8193,13 +8181,13 @@
         </is>
       </c>
       <c r="M126" s="2" t="n">
-        <v>36957.96</v>
+        <v>1405.91</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>1495206-5-CM26</t>
+          <t>692264-2-SE26</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
@@ -8214,7 +8202,7 @@
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-03</t>
         </is>
       </c>
       <c r="E127" t="inlineStr">
@@ -8224,12 +8212,12 @@
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>61.981.340-5</t>
+          <t>60.910.047-8</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>Servicio de Biodiversidad y Áreas Protegidas</t>
+          <t>UNIVERSIDAD METROPOLITANA DE CIENCIAS DE LA EDUCACION</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
@@ -8247,20 +8235,24 @@
           <t>96.573.600-K</t>
         </is>
       </c>
-      <c r="K127" t="inlineStr"/>
+      <c r="K127" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Región de Tarapacá  </t>
+        </is>
+      </c>
       <c r="L127" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M127" s="2" t="n">
-        <v>3981.12</v>
+        <v>449847.9</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>1186801-6-CM26</t>
+          <t>1515286-3-SE26</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
@@ -8275,7 +8267,7 @@
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-05</t>
         </is>
       </c>
       <c r="E128" t="inlineStr">
@@ -8285,12 +8277,12 @@
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>60.930.000-0</t>
+          <t>53.337.014-4</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>CONSEJO NACIONAL DE EDUCACION</t>
+          <t xml:space="preserve">Fondo de Bienestar de la Corporación de Fomento </t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
@@ -8308,20 +8300,24 @@
           <t>96.573.600-K</t>
         </is>
       </c>
-      <c r="K128" t="inlineStr"/>
+      <c r="K128" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Región de Tarapacá  </t>
+        </is>
+      </c>
       <c r="L128" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M128" s="2" t="n">
-        <v>1201.58</v>
+        <v>805575.1800000001</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>1216062-700-CM26</t>
+          <t>2701-376-CM26</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
@@ -8336,7 +8332,7 @@
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="E129" t="inlineStr">
@@ -8346,12 +8342,12 @@
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>71.265.200-4</t>
+          <t>69.071.800-6</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>Corporación Municipal de Lo Prado</t>
+          <t>I MUNICIPALIDAD DE TALAGANTE</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
@@ -8376,13 +8372,13 @@
         </is>
       </c>
       <c r="M129" s="2" t="n">
-        <v>60299.47</v>
+        <v>8058.6</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>307-54-CM26</t>
+          <t>550716-8-CM26</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
@@ -8392,12 +8388,12 @@
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>jul-2026</t>
+          <t>jun-2026</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="E130" t="inlineStr">
@@ -8407,12 +8403,12 @@
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>60.919.000-0</t>
+          <t>65.961.370-0</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>Consejo de Rectores de las Universidades Chilenas</t>
+          <t>Servicio de Bienestar del Personal del Gobierno Re</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
@@ -8437,13 +8433,13 @@
         </is>
       </c>
       <c r="M130" s="2" t="n">
-        <v>695.87</v>
+        <v>7338</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>2702-311-CM26</t>
+          <t>1342-4-SE26</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
@@ -8453,12 +8449,12 @@
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>jul-2026</t>
+          <t>jun-2026</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="E131" t="inlineStr">
@@ -8468,12 +8464,12 @@
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>69.071.800-6</t>
+          <t>60.109.000-7</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE TALAGANTE</t>
+          <t>FONDO DE SOLIDARIDAD E INVERSION SOCIAL</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
@@ -8491,20 +8487,24 @@
           <t>96.573.600-K</t>
         </is>
       </c>
-      <c r="K131" t="inlineStr"/>
+      <c r="K131" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Región de Tarapacá  </t>
+        </is>
+      </c>
       <c r="L131" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M131" s="2" t="n">
-        <v>10624.78</v>
+        <v>286656.49</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>1373053-8-CM26</t>
+          <t>1157285-8-CM26</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
@@ -8514,12 +8514,12 @@
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>jul-2026</t>
+          <t>jun-2026</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="E132" t="inlineStr">
@@ -8529,12 +8529,12 @@
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>82.174.900-k</t>
+          <t>62.000.860-5</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>SERVICIO DE COOPERACION TECNICA</t>
+          <t>Bienestar SSFFAA</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
@@ -8559,13 +8559,13 @@
         </is>
       </c>
       <c r="M132" s="2" t="n">
-        <v>9324.450000000001</v>
+        <v>51470.7</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>545927-3-SE26</t>
+          <t>670784-8-CM26</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
@@ -8575,12 +8575,12 @@
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>jul-2026</t>
+          <t>jun-2026</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="E133" t="inlineStr">
@@ -8590,12 +8590,12 @@
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>61.212.000-5</t>
+          <t>60.818.000-1</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>SUBSECRETARIA DE TRANSPORTES</t>
+          <t>Superintendencia de Pensiones</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
@@ -8613,24 +8613,20 @@
           <t>96.573.600-K</t>
         </is>
       </c>
-      <c r="K133" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Región de Tarapacá  </t>
-        </is>
-      </c>
+      <c r="K133" t="inlineStr"/>
       <c r="L133" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M133" s="2" t="n">
-        <v>581414.84</v>
+        <v>10377.13</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>1211992-149-CM26</t>
+          <t>4700-10-CM26</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
@@ -8640,12 +8636,12 @@
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>jul-2026</t>
+          <t>jun-2026</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="E134" t="inlineStr">
@@ -8655,12 +8651,12 @@
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>65.192.585-1</t>
+          <t>73.362.800-6</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>CORPORACIÓN YUNUS</t>
+          <t>BIENESTAR DEL CONSEJO DE DEFENSA DEL ESTADO</t>
         </is>
       </c>
       <c r="H134" t="inlineStr">
@@ -8685,13 +8681,13 @@
         </is>
       </c>
       <c r="M134" s="2" t="n">
-        <v>1647.34</v>
+        <v>310935.41</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>550716-9-CM26</t>
+          <t>1495206-5-CM26</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
@@ -8701,12 +8697,12 @@
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>jul-2026</t>
+          <t>jun-2026</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="E135" t="inlineStr">
@@ -8716,12 +8712,12 @@
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>65.961.370-0</t>
+          <t>61.981.340-5</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>Servicio de Bienestar del Personal del Gobierno Re</t>
+          <t>Servicio de Biodiversidad y Áreas Protegidas</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
@@ -8746,13 +8742,13 @@
         </is>
       </c>
       <c r="M135" s="2" t="n">
-        <v>7073.88</v>
+        <v>3981.12</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>772003-6-SE26</t>
+          <t>1186801-6-CM26</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
@@ -8762,12 +8758,12 @@
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>jul-2026</t>
+          <t>jun-2026</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="E136" t="inlineStr">
@@ -8777,12 +8773,12 @@
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>61.979.930-5</t>
+          <t>60.930.000-0</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>SUBSECRETARIA DEL MEDIO AMBIENTE</t>
+          <t>CONSEJO NACIONAL DE EDUCACION</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
@@ -8800,24 +8796,20 @@
           <t>96.573.600-K</t>
         </is>
       </c>
-      <c r="K136" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Región de Tarapacá  </t>
-        </is>
-      </c>
+      <c r="K136" t="inlineStr"/>
       <c r="L136" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M136" s="2" t="n">
-        <v>154472.86</v>
+        <v>1201.58</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>772003-7-SE26</t>
+          <t>1477-194-CM26</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
@@ -8827,12 +8819,12 @@
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>jul-2026</t>
+          <t>jun-2026</t>
         </is>
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="E137" t="inlineStr">
@@ -8842,12 +8834,12 @@
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>61.979.930-5</t>
+          <t>70.786.200-9</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>SUBSECRETARIA DEL MEDIO AMBIENTE</t>
+          <t>Corporación de Asistencia Judicial RM</t>
         </is>
       </c>
       <c r="H137" t="inlineStr">
@@ -8865,24 +8857,20 @@
           <t>96.573.600-K</t>
         </is>
       </c>
-      <c r="K137" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Región de Tarapacá  </t>
-        </is>
-      </c>
+      <c r="K137" t="inlineStr"/>
       <c r="L137" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M137" s="2" t="n">
-        <v>19309.11</v>
+        <v>36957.96</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>1186801-7-CM26</t>
+          <t>1216062-700-CM26</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
@@ -8892,12 +8880,12 @@
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>jul-2026</t>
+          <t>jun-2026</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="E138" t="inlineStr">
@@ -8907,12 +8895,12 @@
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>60.930.000-0</t>
+          <t>71.265.200-4</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>CONSEJO NACIONAL DE EDUCACION</t>
+          <t>Corporación Municipal de Lo Prado</t>
         </is>
       </c>
       <c r="H138" t="inlineStr">
@@ -8937,13 +8925,13 @@
         </is>
       </c>
       <c r="M138" s="2" t="n">
-        <v>1177.97</v>
+        <v>60299.47</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>2702-361-CM26</t>
+          <t>307-54-CM26</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
@@ -8958,7 +8946,7 @@
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="E139" t="inlineStr">
@@ -8968,12 +8956,12 @@
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>69.071.800-6</t>
+          <t>60.919.000-0</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE TALAGANTE</t>
+          <t>Consejo de Rectores de las Universidades Chilenas</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
@@ -8998,13 +8986,13 @@
         </is>
       </c>
       <c r="M139" s="2" t="n">
-        <v>10433.97</v>
+        <v>695.87</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>1211839-502-SE26</t>
+          <t>2702-311-CM26</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
@@ -9019,7 +9007,7 @@
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="E140" t="inlineStr">
@@ -9029,12 +9017,12 @@
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>70.856.400-1</t>
+          <t>69.071.800-6</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>CORP MUNIC EDUC SALUD Y ATENCION</t>
+          <t>I MUNICIPALIDAD DE TALAGANTE</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
@@ -9052,24 +9040,20 @@
           <t>96.573.600-K</t>
         </is>
       </c>
-      <c r="K140" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Región de Tarapacá  </t>
-        </is>
-      </c>
+      <c r="K140" t="inlineStr"/>
       <c r="L140" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M140" s="2" t="n">
-        <v>1399224.97</v>
+        <v>10624.78</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>1477-242-CM26</t>
+          <t>1373053-8-CM26</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
@@ -9084,7 +9068,7 @@
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="E141" t="inlineStr">
@@ -9094,12 +9078,12 @@
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>70.786.200-9</t>
+          <t>82.174.900-k</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>Corporación de Asistencia Judicial RM</t>
+          <t>SERVICIO DE COOPERACION TECNICA</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
@@ -9124,13 +9108,13 @@
         </is>
       </c>
       <c r="M141" s="2" t="n">
-        <v>36580.68</v>
+        <v>9324.450000000001</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>2701-496-CM26</t>
+          <t>550716-9-CM26</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
@@ -9145,7 +9129,7 @@
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="E142" t="inlineStr">
@@ -9155,12 +9139,12 @@
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>69.071.800-6</t>
+          <t>65.961.370-0</t>
         </is>
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE TALAGANTE</t>
+          <t>Servicio de Bienestar del Personal del Gobierno Re</t>
         </is>
       </c>
       <c r="H142" t="inlineStr">
@@ -9185,13 +9169,13 @@
         </is>
       </c>
       <c r="M142" s="2" t="n">
-        <v>7849.1</v>
+        <v>7073.88</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>4722-2-CM26</t>
+          <t>1211992-149-CM26</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
@@ -9201,12 +9185,12 @@
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>ago-2026</t>
+          <t>jul-2026</t>
         </is>
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="E143" t="inlineStr">
@@ -9216,12 +9200,12 @@
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>65.138.650-0</t>
+          <t>65.192.585-1</t>
         </is>
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>DEFENSORIA PENAL PUBLICA</t>
+          <t>CORPORACIÓN YUNUS</t>
         </is>
       </c>
       <c r="H143" t="inlineStr">
@@ -9246,6 +9230,571 @@
         </is>
       </c>
       <c r="M143" s="2" t="n">
+        <v>1647.34</v>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="inlineStr">
+        <is>
+          <t>545927-3-SE26</t>
+        </is>
+      </c>
+      <c r="B144" t="inlineStr">
+        <is>
+          <t>2239-12-LR23</t>
+        </is>
+      </c>
+      <c r="C144" t="inlineStr">
+        <is>
+          <t>jul-2026</t>
+        </is>
+      </c>
+      <c r="D144" t="inlineStr">
+        <is>
+          <t>2026-07-15</t>
+        </is>
+      </c>
+      <c r="E144" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F144" t="inlineStr">
+        <is>
+          <t>61.212.000-5</t>
+        </is>
+      </c>
+      <c r="G144" t="inlineStr">
+        <is>
+          <t>SUBSECRETARIA DE TRANSPORTES</t>
+        </is>
+      </c>
+      <c r="H144" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="I144" t="inlineStr">
+        <is>
+          <t>BCI SEGUROS VIDA S A</t>
+        </is>
+      </c>
+      <c r="J144" t="inlineStr">
+        <is>
+          <t>96.573.600-K</t>
+        </is>
+      </c>
+      <c r="K144" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Región de Tarapacá  </t>
+        </is>
+      </c>
+      <c r="L144" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M144" s="2" t="n">
+        <v>581414.84</v>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" t="inlineStr">
+        <is>
+          <t>772003-6-SE26</t>
+        </is>
+      </c>
+      <c r="B145" t="inlineStr">
+        <is>
+          <t>2239-12-LR23</t>
+        </is>
+      </c>
+      <c r="C145" t="inlineStr">
+        <is>
+          <t>jul-2026</t>
+        </is>
+      </c>
+      <c r="D145" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="E145" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F145" t="inlineStr">
+        <is>
+          <t>61.979.930-5</t>
+        </is>
+      </c>
+      <c r="G145" t="inlineStr">
+        <is>
+          <t>SUBSECRETARIA DEL MEDIO AMBIENTE</t>
+        </is>
+      </c>
+      <c r="H145" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="I145" t="inlineStr">
+        <is>
+          <t>BCI SEGUROS VIDA S A</t>
+        </is>
+      </c>
+      <c r="J145" t="inlineStr">
+        <is>
+          <t>96.573.600-K</t>
+        </is>
+      </c>
+      <c r="K145" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Región de Tarapacá  </t>
+        </is>
+      </c>
+      <c r="L145" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M145" s="2" t="n">
+        <v>154472.86</v>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" t="inlineStr">
+        <is>
+          <t>772003-7-SE26</t>
+        </is>
+      </c>
+      <c r="B146" t="inlineStr">
+        <is>
+          <t>2239-12-LR23</t>
+        </is>
+      </c>
+      <c r="C146" t="inlineStr">
+        <is>
+          <t>jul-2026</t>
+        </is>
+      </c>
+      <c r="D146" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="E146" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F146" t="inlineStr">
+        <is>
+          <t>61.979.930-5</t>
+        </is>
+      </c>
+      <c r="G146" t="inlineStr">
+        <is>
+          <t>SUBSECRETARIA DEL MEDIO AMBIENTE</t>
+        </is>
+      </c>
+      <c r="H146" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="I146" t="inlineStr">
+        <is>
+          <t>BCI SEGUROS VIDA S A</t>
+        </is>
+      </c>
+      <c r="J146" t="inlineStr">
+        <is>
+          <t>96.573.600-K</t>
+        </is>
+      </c>
+      <c r="K146" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Región de Tarapacá  </t>
+        </is>
+      </c>
+      <c r="L146" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M146" s="2" t="n">
+        <v>19309.11</v>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" t="inlineStr">
+        <is>
+          <t>1186801-7-CM26</t>
+        </is>
+      </c>
+      <c r="B147" t="inlineStr">
+        <is>
+          <t>2239-12-LR23</t>
+        </is>
+      </c>
+      <c r="C147" t="inlineStr">
+        <is>
+          <t>jul-2026</t>
+        </is>
+      </c>
+      <c r="D147" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="E147" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F147" t="inlineStr">
+        <is>
+          <t>60.930.000-0</t>
+        </is>
+      </c>
+      <c r="G147" t="inlineStr">
+        <is>
+          <t>CONSEJO NACIONAL DE EDUCACION</t>
+        </is>
+      </c>
+      <c r="H147" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="I147" t="inlineStr">
+        <is>
+          <t>BCI SEGUROS VIDA S A</t>
+        </is>
+      </c>
+      <c r="J147" t="inlineStr">
+        <is>
+          <t>96.573.600-K</t>
+        </is>
+      </c>
+      <c r="K147" t="inlineStr"/>
+      <c r="L147" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M147" s="2" t="n">
+        <v>1177.97</v>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" t="inlineStr">
+        <is>
+          <t>2702-361-CM26</t>
+        </is>
+      </c>
+      <c r="B148" t="inlineStr">
+        <is>
+          <t>2239-12-LR23</t>
+        </is>
+      </c>
+      <c r="C148" t="inlineStr">
+        <is>
+          <t>jul-2026</t>
+        </is>
+      </c>
+      <c r="D148" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="E148" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F148" t="inlineStr">
+        <is>
+          <t>69.071.800-6</t>
+        </is>
+      </c>
+      <c r="G148" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE TALAGANTE</t>
+        </is>
+      </c>
+      <c r="H148" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="I148" t="inlineStr">
+        <is>
+          <t>BCI SEGUROS VIDA S A</t>
+        </is>
+      </c>
+      <c r="J148" t="inlineStr">
+        <is>
+          <t>96.573.600-K</t>
+        </is>
+      </c>
+      <c r="K148" t="inlineStr"/>
+      <c r="L148" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M148" s="2" t="n">
+        <v>10433.97</v>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" t="inlineStr">
+        <is>
+          <t>1211839-502-SE26</t>
+        </is>
+      </c>
+      <c r="B149" t="inlineStr">
+        <is>
+          <t>2239-12-LR23</t>
+        </is>
+      </c>
+      <c r="C149" t="inlineStr">
+        <is>
+          <t>jul-2026</t>
+        </is>
+      </c>
+      <c r="D149" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="E149" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F149" t="inlineStr">
+        <is>
+          <t>70.856.400-1</t>
+        </is>
+      </c>
+      <c r="G149" t="inlineStr">
+        <is>
+          <t>CORP MUNIC EDUC SALUD Y ATENCION</t>
+        </is>
+      </c>
+      <c r="H149" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="I149" t="inlineStr">
+        <is>
+          <t>BCI SEGUROS VIDA S A</t>
+        </is>
+      </c>
+      <c r="J149" t="inlineStr">
+        <is>
+          <t>96.573.600-K</t>
+        </is>
+      </c>
+      <c r="K149" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Región de Tarapacá  </t>
+        </is>
+      </c>
+      <c r="L149" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M149" s="2" t="n">
+        <v>1399224.97</v>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" t="inlineStr">
+        <is>
+          <t>2701-496-CM26</t>
+        </is>
+      </c>
+      <c r="B150" t="inlineStr">
+        <is>
+          <t>2239-12-LR23</t>
+        </is>
+      </c>
+      <c r="C150" t="inlineStr">
+        <is>
+          <t>jul-2026</t>
+        </is>
+      </c>
+      <c r="D150" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="E150" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F150" t="inlineStr">
+        <is>
+          <t>69.071.800-6</t>
+        </is>
+      </c>
+      <c r="G150" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE TALAGANTE</t>
+        </is>
+      </c>
+      <c r="H150" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="I150" t="inlineStr">
+        <is>
+          <t>BCI SEGUROS VIDA S A</t>
+        </is>
+      </c>
+      <c r="J150" t="inlineStr">
+        <is>
+          <t>96.573.600-K</t>
+        </is>
+      </c>
+      <c r="K150" t="inlineStr"/>
+      <c r="L150" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M150" s="2" t="n">
+        <v>7849.1</v>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" t="inlineStr">
+        <is>
+          <t>1477-242-CM26</t>
+        </is>
+      </c>
+      <c r="B151" t="inlineStr">
+        <is>
+          <t>2239-12-LR23</t>
+        </is>
+      </c>
+      <c r="C151" t="inlineStr">
+        <is>
+          <t>jul-2026</t>
+        </is>
+      </c>
+      <c r="D151" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="E151" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F151" t="inlineStr">
+        <is>
+          <t>70.786.200-9</t>
+        </is>
+      </c>
+      <c r="G151" t="inlineStr">
+        <is>
+          <t>Corporación de Asistencia Judicial RM</t>
+        </is>
+      </c>
+      <c r="H151" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="I151" t="inlineStr">
+        <is>
+          <t>BCI SEGUROS VIDA S A</t>
+        </is>
+      </c>
+      <c r="J151" t="inlineStr">
+        <is>
+          <t>96.573.600-K</t>
+        </is>
+      </c>
+      <c r="K151" t="inlineStr"/>
+      <c r="L151" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M151" s="2" t="n">
+        <v>36580.68</v>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" t="inlineStr">
+        <is>
+          <t>4722-2-CM26</t>
+        </is>
+      </c>
+      <c r="B152" t="inlineStr">
+        <is>
+          <t>2239-12-LR23</t>
+        </is>
+      </c>
+      <c r="C152" t="inlineStr">
+        <is>
+          <t>ago-2026</t>
+        </is>
+      </c>
+      <c r="D152" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="E152" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F152" t="inlineStr">
+        <is>
+          <t>65.138.650-0</t>
+        </is>
+      </c>
+      <c r="G152" t="inlineStr">
+        <is>
+          <t>DEFENSORIA PENAL PUBLICA</t>
+        </is>
+      </c>
+      <c r="H152" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="I152" t="inlineStr">
+        <is>
+          <t>BCI SEGUROS VIDA S A</t>
+        </is>
+      </c>
+      <c r="J152" t="inlineStr">
+        <is>
+          <t>96.573.600-K</t>
+        </is>
+      </c>
+      <c r="K152" t="inlineStr"/>
+      <c r="L152" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M152" s="2" t="n">
         <v>30370.94</v>
       </c>
     </row>

--- a/docs/oc-regiones/seguro-colectivo-de-vida-con-adicional-de-salud/metropolitana.xlsx
+++ b/docs/oc-regiones/seguro-colectivo-de-vida-con-adicional-de-salud/metropolitana.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M310"/>
+  <dimension ref="A1:M312"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -3634,7 +3634,7 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>307-21-CM25</t>
+          <t>553925-2-CM25</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -3659,12 +3659,12 @@
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>60.919.000-0</t>
+          <t>60.701.000-5</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Consejo de Rectores de las Universidades Chilenas</t>
+          <t>SUBSECRETARIA DE ECONOMIA Y EMPRESAS DE MENOR TAMANO</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
@@ -3693,13 +3693,13 @@
         </is>
       </c>
       <c r="M50" s="2" t="n">
-        <v>538.7</v>
+        <v>22512.79</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>553925-2-CM25</t>
+          <t>307-21-CM25</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -3724,12 +3724,12 @@
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>60.701.000-5</t>
+          <t>60.919.000-0</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>SUBSECRETARIA DE ECONOMIA Y EMPRESAS DE MENOR TAMANO</t>
+          <t>Consejo de Rectores de las Universidades Chilenas</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
@@ -3758,7 +3758,7 @@
         </is>
       </c>
       <c r="M51" s="2" t="n">
-        <v>22512.79</v>
+        <v>538.7</v>
       </c>
     </row>
     <row r="52">
@@ -4674,7 +4674,7 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>2701-360-CM25</t>
+          <t>1186801-5-CM25</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -4699,12 +4699,12 @@
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>69.071.800-6</t>
+          <t>60.930.000-0</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE TALAGANTE</t>
+          <t>CONSEJO NACIONAL DE EDUCACION</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
@@ -4733,13 +4733,13 @@
         </is>
       </c>
       <c r="M66" s="2" t="n">
-        <v>6907.56</v>
+        <v>1072.05</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>1186801-5-CM25</t>
+          <t>2701-360-CM25</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -4764,12 +4764,12 @@
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>60.930.000-0</t>
+          <t>69.071.800-6</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>CONSEJO NACIONAL DE EDUCACION</t>
+          <t>I MUNICIPALIDAD DE TALAGANTE</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
@@ -4798,7 +4798,7 @@
         </is>
       </c>
       <c r="M67" s="2" t="n">
-        <v>1072.05</v>
+        <v>6907.56</v>
       </c>
     </row>
     <row r="68">
@@ -4999,7 +4999,7 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>4722-1-CM25</t>
+          <t>2702-233-CM25</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -5024,12 +5024,12 @@
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>65.138.650-0</t>
+          <t>69.071.800-6</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>DEFENSORIA PENAL PUBLICA</t>
+          <t>I MUNICIPALIDAD DE TALAGANTE</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
@@ -5058,13 +5058,13 @@
         </is>
       </c>
       <c r="M71" s="2" t="n">
-        <v>26827.43</v>
+        <v>9514.190000000001</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>307-40-CM25</t>
+          <t>3378-4820-CM25</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -5084,17 +5084,17 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>60.919.000-0</t>
+          <t>61.101.030-3</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Consejo de Rectores de las Universidades Chilenas</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
@@ -5123,13 +5123,13 @@
         </is>
       </c>
       <c r="M72" s="2" t="n">
-        <v>608.6799999999999</v>
+        <v>15545.51</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>3378-4820-CM25</t>
+          <t>4722-1-CM25</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -5149,17 +5149,17 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>61.101.030-3</t>
+          <t>65.138.650-0</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>DIVISION LOGISTICA DEL EJERCITO</t>
+          <t>DEFENSORIA PENAL PUBLICA</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
@@ -5188,13 +5188,13 @@
         </is>
       </c>
       <c r="M73" s="2" t="n">
-        <v>15545.51</v>
+        <v>26827.43</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>2702-233-CM25</t>
+          <t>307-40-CM25</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -5219,12 +5219,12 @@
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>69.071.800-6</t>
+          <t>60.919.000-0</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE TALAGANTE</t>
+          <t>Consejo de Rectores de las Universidades Chilenas</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
@@ -5253,7 +5253,7 @@
         </is>
       </c>
       <c r="M74" s="2" t="n">
-        <v>9514.190000000001</v>
+        <v>608.6799999999999</v>
       </c>
     </row>
     <row r="75">
@@ -5779,7 +5779,7 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>2403-438-CM25</t>
+          <t>670784-6-CM25</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -5804,12 +5804,12 @@
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>69.254.000-k</t>
+          <t>60.818.000-1</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE PENALOLEN</t>
+          <t>SUPERINTENDENCIA DE PENSIONES</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
@@ -5838,13 +5838,13 @@
         </is>
       </c>
       <c r="M83" s="2" t="n">
-        <v>266236.19</v>
+        <v>8663.24</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>670784-6-CM25</t>
+          <t>2403-438-CM25</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -5869,12 +5869,12 @@
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>60.818.000-1</t>
+          <t>69.254.000-k</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>SUPERINTENDENCIA DE PENSIONES</t>
+          <t>I MUNICIPALIDAD DE PENALOLEN</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
@@ -5903,7 +5903,7 @@
         </is>
       </c>
       <c r="M84" s="2" t="n">
-        <v>8663.24</v>
+        <v>266236.19</v>
       </c>
     </row>
     <row r="85">
@@ -6429,7 +6429,7 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>3378-6239-CM25</t>
+          <t>670784-7-CM25</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -6449,17 +6449,17 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>61.101.030-3</t>
+          <t>60.818.000-1</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>DIVISION LOGISTICA DEL EJERCITO</t>
+          <t>SUPERINTENDENCIA DE PENSIONES</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
@@ -6488,13 +6488,13 @@
         </is>
       </c>
       <c r="M93" s="2" t="n">
-        <v>14929.94</v>
+        <v>8454.799999999999</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>670784-7-CM25</t>
+          <t>3378-6239-CM25</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -6514,17 +6514,17 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>60.818.000-1</t>
+          <t>61.101.030-3</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>SUPERINTENDENCIA DE PENSIONES</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
@@ -6553,7 +6553,7 @@
         </is>
       </c>
       <c r="M94" s="2" t="n">
-        <v>8454.799999999999</v>
+        <v>14929.94</v>
       </c>
     </row>
     <row r="95">
@@ -7079,7 +7079,7 @@
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>1373053-9-CM25</t>
+          <t>2702-382-CM25</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -7104,12 +7104,12 @@
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>82.174.900-k</t>
+          <t>69.071.800-6</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>SERVICIO DE COOPERACION TECNICA</t>
+          <t>I MUNICIPALIDAD DE TALAGANTE</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
@@ -7138,13 +7138,13 @@
         </is>
       </c>
       <c r="M103" s="2" t="n">
-        <v>7776.79</v>
+        <v>9183.23</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>2702-382-CM25</t>
+          <t>1373053-9-CM25</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -7169,12 +7169,12 @@
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>69.071.800-6</t>
+          <t>82.174.900-k</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE TALAGANTE</t>
+          <t>SERVICIO DE COOPERACION TECNICA</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
@@ -7203,7 +7203,7 @@
         </is>
       </c>
       <c r="M104" s="2" t="n">
-        <v>9183.23</v>
+        <v>7776.79</v>
       </c>
     </row>
     <row r="105">
@@ -7859,7 +7859,7 @@
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>2701-636-CM25</t>
+          <t>550716-13-CM25</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
@@ -7879,17 +7879,17 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>69.071.800-6</t>
+          <t>65.961.370-0</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE TALAGANTE</t>
+          <t>GOBIERNO REGIONAL REGION METROPOLITANA</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
@@ -7918,13 +7918,13 @@
         </is>
       </c>
       <c r="M115" s="2" t="n">
-        <v>6875.85</v>
+        <v>6074.37</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>550716-13-CM25</t>
+          <t>2701-636-CM25</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
@@ -7944,17 +7944,17 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>65.961.370-0</t>
+          <t>69.071.800-6</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>GOBIERNO REGIONAL REGION METROPOLITANA</t>
+          <t>I MUNICIPALIDAD DE TALAGANTE</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
@@ -7983,7 +7983,7 @@
         </is>
       </c>
       <c r="M116" s="2" t="n">
-        <v>6074.37</v>
+        <v>6875.85</v>
       </c>
     </row>
     <row r="117">
@@ -9809,7 +9809,7 @@
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>1186801-14-CM25</t>
+          <t>1186801-15-CM25</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
@@ -9868,13 +9868,13 @@
         </is>
       </c>
       <c r="M145" s="2" t="n">
-        <v>1141.35</v>
+        <v>1104.53</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>1186801-15-CM25</t>
+          <t>1186801-14-CM25</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
@@ -9933,7 +9933,7 @@
         </is>
       </c>
       <c r="M146" s="2" t="n">
-        <v>1104.53</v>
+        <v>1141.35</v>
       </c>
     </row>
     <row r="147">
@@ -14814,7 +14814,7 @@
     <row r="222">
       <c r="A222" t="inlineStr">
         <is>
-          <t>4973-40-SE26</t>
+          <t>1211992-43-CM26</t>
         </is>
       </c>
       <c r="B222" t="inlineStr">
@@ -14834,17 +14834,17 @@
       </c>
       <c r="E222" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F222" t="inlineStr">
         <is>
-          <t>61.202.016-7</t>
+          <t>65.192.585-1</t>
         </is>
       </c>
       <c r="G222" t="inlineStr">
         <is>
-          <t>MINISTERIO DE OBRAS PUBLICAS DIREC CION GRAL DE OO PP DCYF</t>
+          <t>CORPORACIÓN YUNUS</t>
         </is>
       </c>
       <c r="H222" t="inlineStr">
@@ -14873,13 +14873,13 @@
         </is>
       </c>
       <c r="M222" s="2" t="n">
-        <v>1573308.56</v>
+        <v>1242.65</v>
       </c>
     </row>
     <row r="223">
       <c r="A223" t="inlineStr">
         <is>
-          <t>1211992-43-CM26</t>
+          <t>4973-40-SE26</t>
         </is>
       </c>
       <c r="B223" t="inlineStr">
@@ -14899,17 +14899,17 @@
       </c>
       <c r="E223" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F223" t="inlineStr">
         <is>
-          <t>65.192.585-1</t>
+          <t>61.202.016-7</t>
         </is>
       </c>
       <c r="G223" t="inlineStr">
         <is>
-          <t>CORPORACIÓN YUNUS</t>
+          <t>MINISTERIO DE OBRAS PUBLICAS DIREC CION GRAL DE OO PP DCYF</t>
         </is>
       </c>
       <c r="H223" t="inlineStr">
@@ -14938,7 +14938,7 @@
         </is>
       </c>
       <c r="M223" s="2" t="n">
-        <v>1242.65</v>
+        <v>1573308.56</v>
       </c>
     </row>
     <row r="224">
@@ -15659,7 +15659,7 @@
     <row r="235">
       <c r="A235" t="inlineStr">
         <is>
-          <t>1211992-69-CM26</t>
+          <t>1373053-5-CM26</t>
         </is>
       </c>
       <c r="B235" t="inlineStr">
@@ -15679,17 +15679,17 @@
       </c>
       <c r="E235" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F235" t="inlineStr">
         <is>
-          <t>65.192.585-1</t>
+          <t>82.174.900-k</t>
         </is>
       </c>
       <c r="G235" t="inlineStr">
         <is>
-          <t>CORPORACIÓN YUNUS</t>
+          <t>SERVICIO DE COOPERACION TECNICA</t>
         </is>
       </c>
       <c r="H235" t="inlineStr">
@@ -15718,13 +15718,13 @@
         </is>
       </c>
       <c r="M235" s="2" t="n">
-        <v>1266.44</v>
+        <v>9595.75</v>
       </c>
     </row>
     <row r="236">
       <c r="A236" t="inlineStr">
         <is>
-          <t>1373053-5-CM26</t>
+          <t>1211992-69-CM26</t>
         </is>
       </c>
       <c r="B236" t="inlineStr">
@@ -15744,17 +15744,17 @@
       </c>
       <c r="E236" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F236" t="inlineStr">
         <is>
-          <t>82.174.900-k</t>
+          <t>65.192.585-1</t>
         </is>
       </c>
       <c r="G236" t="inlineStr">
         <is>
-          <t>SERVICIO DE COOPERACION TECNICA</t>
+          <t>CORPORACIÓN YUNUS</t>
         </is>
       </c>
       <c r="H236" t="inlineStr">
@@ -15783,7 +15783,7 @@
         </is>
       </c>
       <c r="M236" s="2" t="n">
-        <v>9595.75</v>
+        <v>1266.44</v>
       </c>
     </row>
     <row r="237">
@@ -16439,7 +16439,7 @@
     <row r="247">
       <c r="A247" t="inlineStr">
         <is>
-          <t>1495206-3-CM26</t>
+          <t>550716-6-CM26</t>
         </is>
       </c>
       <c r="B247" t="inlineStr">
@@ -16459,17 +16459,17 @@
       </c>
       <c r="E247" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F247" t="inlineStr">
         <is>
-          <t>61.981.340-5</t>
+          <t>65.961.370-0</t>
         </is>
       </c>
       <c r="G247" t="inlineStr">
         <is>
-          <t>SERVICIO DE BIODIVERSIDAD Y ÁREAS PROTEGIDAS</t>
+          <t>GOBIERNO REGIONAL REGION METROPOLITANA</t>
         </is>
       </c>
       <c r="H247" t="inlineStr">
@@ -16498,13 +16498,13 @@
         </is>
       </c>
       <c r="M247" s="2" t="n">
-        <v>3547.07</v>
+        <v>7328.32</v>
       </c>
     </row>
     <row r="248">
       <c r="A248" t="inlineStr">
         <is>
-          <t>550716-6-CM26</t>
+          <t>1495206-3-CM26</t>
         </is>
       </c>
       <c r="B248" t="inlineStr">
@@ -16524,17 +16524,17 @@
       </c>
       <c r="E248" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F248" t="inlineStr">
         <is>
-          <t>65.961.370-0</t>
+          <t>61.981.340-5</t>
         </is>
       </c>
       <c r="G248" t="inlineStr">
         <is>
-          <t>GOBIERNO REGIONAL REGION METROPOLITANA</t>
+          <t>SERVICIO DE BIODIVERSIDAD Y ÁREAS PROTEGIDAS</t>
         </is>
       </c>
       <c r="H248" t="inlineStr">
@@ -16563,13 +16563,13 @@
         </is>
       </c>
       <c r="M248" s="2" t="n">
-        <v>7328.32</v>
+        <v>3547.07</v>
       </c>
     </row>
     <row r="249">
       <c r="A249" t="inlineStr">
         <is>
-          <t>307-48-CM26</t>
+          <t>2702-247-CM26</t>
         </is>
       </c>
       <c r="B249" t="inlineStr">
@@ -16594,12 +16594,12 @@
       </c>
       <c r="F249" t="inlineStr">
         <is>
-          <t>60.919.000-0</t>
+          <t>69.071.800-6</t>
         </is>
       </c>
       <c r="G249" t="inlineStr">
         <is>
-          <t>Consejo de Rectores de las Universidades Chilenas</t>
+          <t>I MUNICIPALIDAD DE TALAGANTE</t>
         </is>
       </c>
       <c r="H249" t="inlineStr">
@@ -16628,13 +16628,13 @@
         </is>
       </c>
       <c r="M249" s="2" t="n">
-        <v>717.09</v>
+        <v>10958.97</v>
       </c>
     </row>
     <row r="250">
       <c r="A250" t="inlineStr">
         <is>
-          <t>2702-247-CM26</t>
+          <t>307-48-CM26</t>
         </is>
       </c>
       <c r="B250" t="inlineStr">
@@ -16659,12 +16659,12 @@
       </c>
       <c r="F250" t="inlineStr">
         <is>
-          <t>69.071.800-6</t>
+          <t>60.919.000-0</t>
         </is>
       </c>
       <c r="G250" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE TALAGANTE</t>
+          <t>Consejo de Rectores de las Universidades Chilenas</t>
         </is>
       </c>
       <c r="H250" t="inlineStr">
@@ -16693,7 +16693,7 @@
         </is>
       </c>
       <c r="M250" s="2" t="n">
-        <v>10958.97</v>
+        <v>717.09</v>
       </c>
     </row>
     <row r="251">
@@ -17414,7 +17414,7 @@
     <row r="262">
       <c r="A262" t="inlineStr">
         <is>
-          <t>1495206-5-CM26</t>
+          <t>1186801-6-CM26</t>
         </is>
       </c>
       <c r="B262" t="inlineStr">
@@ -17439,12 +17439,12 @@
       </c>
       <c r="F262" t="inlineStr">
         <is>
-          <t>61.981.340-5</t>
+          <t>60.930.000-0</t>
         </is>
       </c>
       <c r="G262" t="inlineStr">
         <is>
-          <t>SERVICIO DE BIODIVERSIDAD Y ÁREAS PROTEGIDAS</t>
+          <t>CONSEJO NACIONAL DE EDUCACION</t>
         </is>
       </c>
       <c r="H262" t="inlineStr">
@@ -17473,13 +17473,13 @@
         </is>
       </c>
       <c r="M262" s="2" t="n">
-        <v>3981.12</v>
+        <v>1201.58</v>
       </c>
     </row>
     <row r="263">
       <c r="A263" t="inlineStr">
         <is>
-          <t>1186801-6-CM26</t>
+          <t>1495206-5-CM26</t>
         </is>
       </c>
       <c r="B263" t="inlineStr">
@@ -17504,12 +17504,12 @@
       </c>
       <c r="F263" t="inlineStr">
         <is>
-          <t>60.930.000-0</t>
+          <t>61.981.340-5</t>
         </is>
       </c>
       <c r="G263" t="inlineStr">
         <is>
-          <t>CONSEJO NACIONAL DE EDUCACION</t>
+          <t>SERVICIO DE BIODIVERSIDAD Y ÁREAS PROTEGIDAS</t>
         </is>
       </c>
       <c r="H263" t="inlineStr">
@@ -17538,7 +17538,7 @@
         </is>
       </c>
       <c r="M263" s="2" t="n">
-        <v>1201.58</v>
+        <v>3981.12</v>
       </c>
     </row>
     <row r="264">
@@ -18129,7 +18129,7 @@
     <row r="273">
       <c r="A273" t="inlineStr">
         <is>
-          <t>2702-361-CM26</t>
+          <t>1186801-7-CM26</t>
         </is>
       </c>
       <c r="B273" t="inlineStr">
@@ -18154,12 +18154,12 @@
       </c>
       <c r="F273" t="inlineStr">
         <is>
-          <t>69.071.800-6</t>
+          <t>60.930.000-0</t>
         </is>
       </c>
       <c r="G273" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE TALAGANTE</t>
+          <t>CONSEJO NACIONAL DE EDUCACION</t>
         </is>
       </c>
       <c r="H273" t="inlineStr">
@@ -18188,13 +18188,13 @@
         </is>
       </c>
       <c r="M273" s="2" t="n">
-        <v>10433.97</v>
+        <v>1177.97</v>
       </c>
     </row>
     <row r="274">
       <c r="A274" t="inlineStr">
         <is>
-          <t>1186801-7-CM26</t>
+          <t>2702-361-CM26</t>
         </is>
       </c>
       <c r="B274" t="inlineStr">
@@ -18219,12 +18219,12 @@
       </c>
       <c r="F274" t="inlineStr">
         <is>
-          <t>60.930.000-0</t>
+          <t>69.071.800-6</t>
         </is>
       </c>
       <c r="G274" t="inlineStr">
         <is>
-          <t>CONSEJO NACIONAL DE EDUCACION</t>
+          <t>I MUNICIPALIDAD DE TALAGANTE</t>
         </is>
       </c>
       <c r="H274" t="inlineStr">
@@ -18253,7 +18253,7 @@
         </is>
       </c>
       <c r="M274" s="2" t="n">
-        <v>1177.97</v>
+        <v>10433.97</v>
       </c>
     </row>
     <row r="275">
@@ -18714,7 +18714,7 @@
     <row r="282">
       <c r="A282" t="inlineStr">
         <is>
-          <t>1373053-9-CM26</t>
+          <t>846677-2-SE26</t>
         </is>
       </c>
       <c r="B282" t="inlineStr">
@@ -18729,22 +18729,22 @@
       </c>
       <c r="D282" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="E282" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F282" t="inlineStr">
         <is>
-          <t>82.174.900-k</t>
+          <t>61.979.950-k</t>
         </is>
       </c>
       <c r="G282" t="inlineStr">
         <is>
-          <t>SERVICIO DE COOPERACION TECNICA</t>
+          <t>Superintendencia del Medio Ambiente</t>
         </is>
       </c>
       <c r="H282" t="inlineStr">
@@ -18773,13 +18773,13 @@
         </is>
       </c>
       <c r="M282" s="2" t="n">
-        <v>9583.110000000001</v>
+        <v>104140.14</v>
       </c>
     </row>
     <row r="283">
       <c r="A283" t="inlineStr">
         <is>
-          <t>3378-4239-CM26</t>
+          <t>1373053-9-CM26</t>
         </is>
       </c>
       <c r="B283" t="inlineStr">
@@ -18794,7 +18794,7 @@
       </c>
       <c r="D283" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="E283" t="inlineStr">
@@ -18804,12 +18804,12 @@
       </c>
       <c r="F283" t="inlineStr">
         <is>
-          <t>61.101.030-3</t>
+          <t>82.174.900-k</t>
         </is>
       </c>
       <c r="G283" t="inlineStr">
         <is>
-          <t>DIVISION LOGISTICA DEL EJERCITO</t>
+          <t>SERVICIO DE COOPERACION TECNICA</t>
         </is>
       </c>
       <c r="H283" t="inlineStr">
@@ -18838,13 +18838,13 @@
         </is>
       </c>
       <c r="M283" s="2" t="n">
-        <v>16186.82</v>
+        <v>9583.110000000001</v>
       </c>
     </row>
     <row r="284">
       <c r="A284" t="inlineStr">
         <is>
-          <t>2701-560-CM26</t>
+          <t>3378-4239-CM26</t>
         </is>
       </c>
       <c r="B284" t="inlineStr">
@@ -18859,7 +18859,7 @@
       </c>
       <c r="D284" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="E284" t="inlineStr">
@@ -18869,12 +18869,12 @@
       </c>
       <c r="F284" t="inlineStr">
         <is>
-          <t>69.071.800-6</t>
+          <t>61.101.030-3</t>
         </is>
       </c>
       <c r="G284" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE TALAGANTE</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H284" t="inlineStr">
@@ -18903,13 +18903,13 @@
         </is>
       </c>
       <c r="M284" s="2" t="n">
-        <v>7874.28</v>
+        <v>16186.82</v>
       </c>
     </row>
     <row r="285">
       <c r="A285" t="inlineStr">
         <is>
-          <t>1500781-64-CM26</t>
+          <t>2701-560-CM26</t>
         </is>
       </c>
       <c r="B285" t="inlineStr">
@@ -18934,12 +18934,12 @@
       </c>
       <c r="F285" t="inlineStr">
         <is>
-          <t>65.260.064-6</t>
+          <t>69.071.800-6</t>
         </is>
       </c>
       <c r="G285" t="inlineStr">
         <is>
-          <t>CORPORACION MUNICIPAL DE DEPORTES, CULTURA, RECREACION Y FOMENTO DE HU</t>
+          <t>I MUNICIPALIDAD DE TALAGANTE</t>
         </is>
       </c>
       <c r="H285" t="inlineStr">
@@ -18968,13 +18968,13 @@
         </is>
       </c>
       <c r="M285" s="2" t="n">
-        <v>46630.5</v>
+        <v>7874.28</v>
       </c>
     </row>
     <row r="286">
       <c r="A286" t="inlineStr">
         <is>
-          <t>307-82-CM26</t>
+          <t>1500781-64-CM26</t>
         </is>
       </c>
       <c r="B286" t="inlineStr">
@@ -18989,7 +18989,7 @@
       </c>
       <c r="D286" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="E286" t="inlineStr">
@@ -18999,12 +18999,12 @@
       </c>
       <c r="F286" t="inlineStr">
         <is>
-          <t>60.919.000-0</t>
+          <t>65.260.064-6</t>
         </is>
       </c>
       <c r="G286" t="inlineStr">
         <is>
-          <t>Consejo de Rectores de las Universidades Chilenas</t>
+          <t>CORPORACION MUNICIPAL DE DEPORTES, CULTURA, RECREACION Y FOMENTO DE HU</t>
         </is>
       </c>
       <c r="H286" t="inlineStr">
@@ -19033,13 +19033,13 @@
         </is>
       </c>
       <c r="M286" s="2" t="n">
-        <v>699.64</v>
+        <v>46630.5</v>
       </c>
     </row>
     <row r="287">
       <c r="A287" t="inlineStr">
         <is>
-          <t>550716-10-CM26</t>
+          <t>307-82-CM26</t>
         </is>
       </c>
       <c r="B287" t="inlineStr">
@@ -19059,17 +19059,17 @@
       </c>
       <c r="E287" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F287" t="inlineStr">
         <is>
-          <t>65.961.370-0</t>
+          <t>60.919.000-0</t>
         </is>
       </c>
       <c r="G287" t="inlineStr">
         <is>
-          <t>GOBIERNO REGIONAL REGION METROPOLITANA</t>
+          <t>Consejo de Rectores de las Universidades Chilenas</t>
         </is>
       </c>
       <c r="H287" t="inlineStr">
@@ -19098,13 +19098,13 @@
         </is>
       </c>
       <c r="M287" s="2" t="n">
-        <v>7128.25</v>
+        <v>699.64</v>
       </c>
     </row>
     <row r="288">
       <c r="A288" t="inlineStr">
         <is>
-          <t>670784-10-CM26</t>
+          <t>550716-10-CM26</t>
         </is>
       </c>
       <c r="B288" t="inlineStr">
@@ -19119,7 +19119,7 @@
       </c>
       <c r="D288" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="E288" t="inlineStr">
@@ -19129,12 +19129,12 @@
       </c>
       <c r="F288" t="inlineStr">
         <is>
-          <t>60.818.000-1</t>
+          <t>65.961.370-0</t>
         </is>
       </c>
       <c r="G288" t="inlineStr">
         <is>
-          <t>SUPERINTENDENCIA DE PENSIONES</t>
+          <t>GOBIERNO REGIONAL REGION METROPOLITANA</t>
         </is>
       </c>
       <c r="H288" t="inlineStr">
@@ -19163,13 +19163,13 @@
         </is>
       </c>
       <c r="M288" s="2" t="n">
-        <v>10292.87</v>
+        <v>7128.25</v>
       </c>
     </row>
     <row r="289">
       <c r="A289" t="inlineStr">
         <is>
-          <t>1477-270-CM26</t>
+          <t>670784-10-CM26</t>
         </is>
       </c>
       <c r="B289" t="inlineStr">
@@ -19189,17 +19189,17 @@
       </c>
       <c r="E289" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F289" t="inlineStr">
         <is>
-          <t>70.786.200-9</t>
+          <t>60.818.000-1</t>
         </is>
       </c>
       <c r="G289" t="inlineStr">
         <is>
-          <t>Corporación de Asistencia Judicial RM</t>
+          <t>SUPERINTENDENCIA DE PENSIONES</t>
         </is>
       </c>
       <c r="H289" t="inlineStr">
@@ -19228,13 +19228,13 @@
         </is>
       </c>
       <c r="M289" s="2" t="n">
-        <v>37103.35</v>
+        <v>10292.87</v>
       </c>
     </row>
     <row r="290">
       <c r="A290" t="inlineStr">
         <is>
-          <t>606591-7-CM26</t>
+          <t>1477-270-CM26</t>
         </is>
       </c>
       <c r="B290" t="inlineStr">
@@ -19254,17 +19254,17 @@
       </c>
       <c r="E290" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F290" t="inlineStr">
         <is>
-          <t>60.718.000-8</t>
+          <t>70.786.200-9</t>
         </is>
       </c>
       <c r="G290" t="inlineStr">
         <is>
-          <t>COMISION NACIONAL DE RIEGO</t>
+          <t>Corporación de Asistencia Judicial RM</t>
         </is>
       </c>
       <c r="H290" t="inlineStr">
@@ -19293,13 +19293,13 @@
         </is>
       </c>
       <c r="M290" s="2" t="n">
-        <v>31368.75</v>
+        <v>37103.35</v>
       </c>
     </row>
     <row r="291">
       <c r="A291" t="inlineStr">
         <is>
-          <t>1186801-8-CM26</t>
+          <t>606591-7-CM26</t>
         </is>
       </c>
       <c r="B291" t="inlineStr">
@@ -19314,22 +19314,22 @@
       </c>
       <c r="D291" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="E291" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F291" t="inlineStr">
         <is>
-          <t>60.930.000-0</t>
+          <t>60.718.000-8</t>
         </is>
       </c>
       <c r="G291" t="inlineStr">
         <is>
-          <t>CONSEJO NACIONAL DE EDUCACION</t>
+          <t>COMISION NACIONAL DE RIEGO</t>
         </is>
       </c>
       <c r="H291" t="inlineStr">
@@ -19358,13 +19358,13 @@
         </is>
       </c>
       <c r="M291" s="2" t="n">
-        <v>1201.42</v>
+        <v>31368.75</v>
       </c>
     </row>
     <row r="292">
       <c r="A292" t="inlineStr">
         <is>
-          <t>1373053-10-CM26</t>
+          <t>1186801-8-CM26</t>
         </is>
       </c>
       <c r="B292" t="inlineStr">
@@ -19379,7 +19379,7 @@
       </c>
       <c r="D292" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="E292" t="inlineStr">
@@ -19389,12 +19389,12 @@
       </c>
       <c r="F292" t="inlineStr">
         <is>
-          <t>82.174.900-k</t>
+          <t>60.930.000-0</t>
         </is>
       </c>
       <c r="G292" t="inlineStr">
         <is>
-          <t>SERVICIO DE COOPERACION TECNICA</t>
+          <t>CONSEJO NACIONAL DE EDUCACION</t>
         </is>
       </c>
       <c r="H292" t="inlineStr">
@@ -19423,13 +19423,13 @@
         </is>
       </c>
       <c r="M292" s="2" t="n">
-        <v>9602.950000000001</v>
+        <v>1201.42</v>
       </c>
     </row>
     <row r="293">
       <c r="A293" t="inlineStr">
         <is>
-          <t>1211992-189-CM26</t>
+          <t>1373053-10-CM26</t>
         </is>
       </c>
       <c r="B293" t="inlineStr">
@@ -19439,12 +19439,12 @@
       </c>
       <c r="C293" t="inlineStr">
         <is>
-          <t>sep-2026</t>
+          <t>ago-2026</t>
         </is>
       </c>
       <c r="D293" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="E293" t="inlineStr">
@@ -19454,12 +19454,12 @@
       </c>
       <c r="F293" t="inlineStr">
         <is>
-          <t>65.192.585-1</t>
+          <t>82.174.900-k</t>
         </is>
       </c>
       <c r="G293" t="inlineStr">
         <is>
-          <t>CORPORACIÓN YUNUS</t>
+          <t>SERVICIO DE COOPERACION TECNICA</t>
         </is>
       </c>
       <c r="H293" t="inlineStr">
@@ -19488,13 +19488,13 @@
         </is>
       </c>
       <c r="M293" s="2" t="n">
-        <v>1633.34</v>
+        <v>9602.950000000001</v>
       </c>
     </row>
     <row r="294">
       <c r="A294" t="inlineStr">
         <is>
-          <t>307-88-CM26</t>
+          <t>1211992-189-CM26</t>
         </is>
       </c>
       <c r="B294" t="inlineStr">
@@ -19509,7 +19509,7 @@
       </c>
       <c r="D294" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="E294" t="inlineStr">
@@ -19519,12 +19519,12 @@
       </c>
       <c r="F294" t="inlineStr">
         <is>
-          <t>60.919.000-0</t>
+          <t>65.192.585-1</t>
         </is>
       </c>
       <c r="G294" t="inlineStr">
         <is>
-          <t>Consejo de Rectores de las Universidades Chilenas</t>
+          <t>CORPORACIÓN YUNUS</t>
         </is>
       </c>
       <c r="H294" t="inlineStr">
@@ -19553,13 +19553,13 @@
         </is>
       </c>
       <c r="M294" s="2" t="n">
-        <v>685.88</v>
+        <v>1633.34</v>
       </c>
     </row>
     <row r="295">
       <c r="A295" t="inlineStr">
         <is>
-          <t>4722-3-CM26</t>
+          <t>307-88-CM26</t>
         </is>
       </c>
       <c r="B295" t="inlineStr">
@@ -19574,7 +19574,7 @@
       </c>
       <c r="D295" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="E295" t="inlineStr">
@@ -19584,12 +19584,12 @@
       </c>
       <c r="F295" t="inlineStr">
         <is>
-          <t>65.138.650-0</t>
+          <t>60.919.000-0</t>
         </is>
       </c>
       <c r="G295" t="inlineStr">
         <is>
-          <t>DEFENSORIA PENAL PUBLICA</t>
+          <t>Consejo de Rectores de las Universidades Chilenas</t>
         </is>
       </c>
       <c r="H295" t="inlineStr">
@@ -19618,13 +19618,13 @@
         </is>
       </c>
       <c r="M295" s="2" t="n">
-        <v>30024.39</v>
+        <v>685.88</v>
       </c>
     </row>
     <row r="296">
       <c r="A296" t="inlineStr">
         <is>
-          <t>786370-3-CM26</t>
+          <t>4722-3-CM26</t>
         </is>
       </c>
       <c r="B296" t="inlineStr">
@@ -19639,22 +19639,22 @@
       </c>
       <c r="D296" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="E296" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F296" t="inlineStr">
         <is>
-          <t>61.980.170-9</t>
+          <t>65.138.650-0</t>
         </is>
       </c>
       <c r="G296" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL PARA LA PREVENCION Y REHABILITACION DEL CONSUMO DE D</t>
+          <t>DEFENSORIA PENAL PUBLICA</t>
         </is>
       </c>
       <c r="H296" t="inlineStr">
@@ -19683,13 +19683,13 @@
         </is>
       </c>
       <c r="M296" s="2" t="n">
-        <v>90796.42999999999</v>
+        <v>30024.39</v>
       </c>
     </row>
     <row r="297">
       <c r="A297" t="inlineStr">
         <is>
-          <t>2702-443-CM26</t>
+          <t>786370-3-CM26</t>
         </is>
       </c>
       <c r="B297" t="inlineStr">
@@ -19704,22 +19704,22 @@
       </c>
       <c r="D297" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="E297" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F297" t="inlineStr">
         <is>
-          <t>69.071.800-6</t>
+          <t>61.980.170-9</t>
         </is>
       </c>
       <c r="G297" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE TALAGANTE</t>
+          <t>SERVICIO NACIONAL PARA LA PREVENCION Y REHABILITACION DEL CONSUMO DE D</t>
         </is>
       </c>
       <c r="H297" t="inlineStr">
@@ -19748,7 +19748,7 @@
         </is>
       </c>
       <c r="M297" s="2" t="n">
-        <v>10270.43</v>
+        <v>90796.42999999999</v>
       </c>
     </row>
     <row r="298">
@@ -19819,7 +19819,7 @@
     <row r="299">
       <c r="A299" t="inlineStr">
         <is>
-          <t>550716-12-CM26</t>
+          <t>2702-443-CM26</t>
         </is>
       </c>
       <c r="B299" t="inlineStr">
@@ -19834,7 +19834,7 @@
       </c>
       <c r="D299" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="E299" t="inlineStr">
@@ -19844,12 +19844,12 @@
       </c>
       <c r="F299" t="inlineStr">
         <is>
-          <t>65.961.370-0</t>
+          <t>69.071.800-6</t>
         </is>
       </c>
       <c r="G299" t="inlineStr">
         <is>
-          <t>GOBIERNO REGIONAL REGION METROPOLITANA</t>
+          <t>I MUNICIPALIDAD DE TALAGANTE</t>
         </is>
       </c>
       <c r="H299" t="inlineStr">
@@ -19878,13 +19878,13 @@
         </is>
       </c>
       <c r="M299" s="2" t="n">
-        <v>6943.58</v>
+        <v>10270.43</v>
       </c>
     </row>
     <row r="300">
       <c r="A300" t="inlineStr">
         <is>
-          <t>2702-464-CM26</t>
+          <t>550716-12-CM26</t>
         </is>
       </c>
       <c r="B300" t="inlineStr">
@@ -19899,7 +19899,7 @@
       </c>
       <c r="D300" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="E300" t="inlineStr">
@@ -19909,12 +19909,12 @@
       </c>
       <c r="F300" t="inlineStr">
         <is>
-          <t>69.071.800-6</t>
+          <t>65.961.370-0</t>
         </is>
       </c>
       <c r="G300" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE TALAGANTE</t>
+          <t>GOBIERNO REGIONAL REGION METROPOLITANA</t>
         </is>
       </c>
       <c r="H300" t="inlineStr">
@@ -19943,13 +19943,13 @@
         </is>
       </c>
       <c r="M300" s="2" t="n">
-        <v>10413.64</v>
+        <v>6943.58</v>
       </c>
     </row>
     <row r="301">
       <c r="A301" t="inlineStr">
         <is>
-          <t>1186801-10-CM26</t>
+          <t>558338-4-SE26</t>
         </is>
       </c>
       <c r="B301" t="inlineStr">
@@ -19964,7 +19964,7 @@
       </c>
       <c r="D301" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="E301" t="inlineStr">
@@ -19974,12 +19974,12 @@
       </c>
       <c r="F301" t="inlineStr">
         <is>
-          <t>60.930.000-0</t>
+          <t>61.702.000-9</t>
         </is>
       </c>
       <c r="G301" t="inlineStr">
         <is>
-          <t>CONSEJO NACIONAL DE EDUCACION</t>
+          <t>SERVICIO NACIONAL DE GEOLOGIA Y MINERIA</t>
         </is>
       </c>
       <c r="H301" t="inlineStr">
@@ -20008,13 +20008,13 @@
         </is>
       </c>
       <c r="M301" s="2" t="n">
-        <v>4681.22</v>
+        <v>306084.36</v>
       </c>
     </row>
     <row r="302">
       <c r="A302" t="inlineStr">
         <is>
-          <t>2701-676-CM26</t>
+          <t>2702-464-CM26</t>
         </is>
       </c>
       <c r="B302" t="inlineStr">
@@ -20029,7 +20029,7 @@
       </c>
       <c r="D302" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="E302" t="inlineStr">
@@ -20073,13 +20073,13 @@
         </is>
       </c>
       <c r="M302" s="2" t="n">
-        <v>7594.58</v>
+        <v>10413.64</v>
       </c>
     </row>
     <row r="303">
       <c r="A303" t="inlineStr">
         <is>
-          <t>307-95-CM26</t>
+          <t>1186801-10-CM26</t>
         </is>
       </c>
       <c r="B303" t="inlineStr">
@@ -20094,7 +20094,7 @@
       </c>
       <c r="D303" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="E303" t="inlineStr">
@@ -20104,12 +20104,12 @@
       </c>
       <c r="F303" t="inlineStr">
         <is>
-          <t>60.919.000-0</t>
+          <t>60.930.000-0</t>
         </is>
       </c>
       <c r="G303" t="inlineStr">
         <is>
-          <t>Consejo de Rectores de las Universidades Chilenas</t>
+          <t>CONSEJO NACIONAL DE EDUCACION</t>
         </is>
       </c>
       <c r="H303" t="inlineStr">
@@ -20138,13 +20138,13 @@
         </is>
       </c>
       <c r="M303" s="2" t="n">
-        <v>667.67</v>
+        <v>4681.22</v>
       </c>
     </row>
     <row r="304">
       <c r="A304" t="inlineStr">
         <is>
-          <t>307-96-CM26</t>
+          <t>307-95-CM26</t>
         </is>
       </c>
       <c r="B304" t="inlineStr">
@@ -20209,7 +20209,7 @@
     <row r="305">
       <c r="A305" t="inlineStr">
         <is>
-          <t>307-97-CM26</t>
+          <t>307-96-CM26</t>
         </is>
       </c>
       <c r="B305" t="inlineStr">
@@ -20274,7 +20274,7 @@
     <row r="306">
       <c r="A306" t="inlineStr">
         <is>
-          <t>307-98-CM26</t>
+          <t>307-97-CM26</t>
         </is>
       </c>
       <c r="B306" t="inlineStr">
@@ -20339,7 +20339,7 @@
     <row r="307">
       <c r="A307" t="inlineStr">
         <is>
-          <t>2701-675-CM26</t>
+          <t>307-98-CM26</t>
         </is>
       </c>
       <c r="B307" t="inlineStr">
@@ -20364,12 +20364,12 @@
       </c>
       <c r="F307" t="inlineStr">
         <is>
-          <t>69.071.800-6</t>
+          <t>60.919.000-0</t>
         </is>
       </c>
       <c r="G307" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE TALAGANTE</t>
+          <t>Consejo de Rectores de las Universidades Chilenas</t>
         </is>
       </c>
       <c r="H307" t="inlineStr">
@@ -20398,13 +20398,13 @@
         </is>
       </c>
       <c r="M307" s="2" t="n">
-        <v>7594.58</v>
+        <v>667.67</v>
       </c>
     </row>
     <row r="308">
       <c r="A308" t="inlineStr">
         <is>
-          <t>2701-677-CM26</t>
+          <t>2701-675-CM26</t>
         </is>
       </c>
       <c r="B308" t="inlineStr">
@@ -20469,7 +20469,7 @@
     <row r="309">
       <c r="A309" t="inlineStr">
         <is>
-          <t>1477-295-CM26</t>
+          <t>2701-676-CM26</t>
         </is>
       </c>
       <c r="B309" t="inlineStr">
@@ -20484,7 +20484,7 @@
       </c>
       <c r="D309" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="E309" t="inlineStr">
@@ -20494,12 +20494,12 @@
       </c>
       <c r="F309" t="inlineStr">
         <is>
-          <t>70.786.200-9</t>
+          <t>69.071.800-6</t>
         </is>
       </c>
       <c r="G309" t="inlineStr">
         <is>
-          <t>Corporación de Asistencia Judicial RM</t>
+          <t>I MUNICIPALIDAD DE TALAGANTE</t>
         </is>
       </c>
       <c r="H309" t="inlineStr">
@@ -20528,71 +20528,201 @@
         </is>
       </c>
       <c r="M309" s="2" t="n">
-        <v>35397.27</v>
+        <v>7594.58</v>
       </c>
     </row>
     <row r="310">
       <c r="A310" t="inlineStr">
         <is>
+          <t>2701-677-CM26</t>
+        </is>
+      </c>
+      <c r="B310" t="inlineStr">
+        <is>
+          <t>2239-12-LR23</t>
+        </is>
+      </c>
+      <c r="C310" t="inlineStr">
+        <is>
+          <t>sep-2026</t>
+        </is>
+      </c>
+      <c r="D310" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="E310" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F310" t="inlineStr">
+        <is>
+          <t>69.071.800-6</t>
+        </is>
+      </c>
+      <c r="G310" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE TALAGANTE</t>
+        </is>
+      </c>
+      <c r="H310" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="I310" t="inlineStr">
+        <is>
+          <t>BCI SEGUROS VIDA S A</t>
+        </is>
+      </c>
+      <c r="J310" t="inlineStr">
+        <is>
+          <t>96.573.600-K</t>
+        </is>
+      </c>
+      <c r="K310" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
+      <c r="L310" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M310" s="2" t="n">
+        <v>7594.58</v>
+      </c>
+    </row>
+    <row r="311">
+      <c r="A311" t="inlineStr">
+        <is>
+          <t>1477-295-CM26</t>
+        </is>
+      </c>
+      <c r="B311" t="inlineStr">
+        <is>
+          <t>2239-12-LR23</t>
+        </is>
+      </c>
+      <c r="C311" t="inlineStr">
+        <is>
+          <t>sep-2026</t>
+        </is>
+      </c>
+      <c r="D311" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="E311" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F311" t="inlineStr">
+        <is>
+          <t>70.786.200-9</t>
+        </is>
+      </c>
+      <c r="G311" t="inlineStr">
+        <is>
+          <t>Corporación de Asistencia Judicial RM</t>
+        </is>
+      </c>
+      <c r="H311" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="I311" t="inlineStr">
+        <is>
+          <t>BCI SEGUROS VIDA S A</t>
+        </is>
+      </c>
+      <c r="J311" t="inlineStr">
+        <is>
+          <t>96.573.600-K</t>
+        </is>
+      </c>
+      <c r="K311" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
+      <c r="L311" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M311" s="2" t="n">
+        <v>35397.27</v>
+      </c>
+    </row>
+    <row r="312">
+      <c r="A312" t="inlineStr">
+        <is>
           <t>1495206-6-CM26</t>
         </is>
       </c>
-      <c r="B310" t="inlineStr">
-        <is>
-          <t>2239-12-LR23</t>
-        </is>
-      </c>
-      <c r="C310" t="inlineStr">
+      <c r="B312" t="inlineStr">
+        <is>
+          <t>2239-12-LR23</t>
+        </is>
+      </c>
+      <c r="C312" t="inlineStr">
         <is>
           <t>sep-2026</t>
         </is>
       </c>
-      <c r="D310" t="inlineStr">
+      <c r="D312" t="inlineStr">
         <is>
           <t>2026-09-30</t>
         </is>
       </c>
-      <c r="E310" t="inlineStr">
-        <is>
-          <t>Aceptada</t>
-        </is>
-      </c>
-      <c r="F310" t="inlineStr">
+      <c r="E312" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F312" t="inlineStr">
         <is>
           <t>61.981.340-5</t>
         </is>
       </c>
-      <c r="G310" t="inlineStr">
+      <c r="G312" t="inlineStr">
         <is>
           <t>SERVICIO DE BIODIVERSIDAD Y ÁREAS PROTEGIDAS</t>
         </is>
       </c>
-      <c r="H310" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
-      <c r="I310" t="inlineStr">
-        <is>
-          <t>BCI SEGUROS VIDA S A</t>
-        </is>
-      </c>
-      <c r="J310" t="inlineStr">
-        <is>
-          <t>96.573.600-K</t>
-        </is>
-      </c>
-      <c r="K310" t="inlineStr">
-        <is>
-          <t>Tarapacá</t>
-        </is>
-      </c>
-      <c r="L310" t="inlineStr">
-        <is>
-          <t>USD</t>
-        </is>
-      </c>
-      <c r="M310" s="2" t="n">
+      <c r="H312" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="I312" t="inlineStr">
+        <is>
+          <t>BCI SEGUROS VIDA S A</t>
+        </is>
+      </c>
+      <c r="J312" t="inlineStr">
+        <is>
+          <t>96.573.600-K</t>
+        </is>
+      </c>
+      <c r="K312" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
+      <c r="L312" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M312" s="2" t="n">
         <v>20926.2</v>
       </c>
     </row>

--- a/docs/oc-regiones/seguro-colectivo-de-vida-con-adicional-de-salud/metropolitana.xlsx
+++ b/docs/oc-regiones/seguro-colectivo-de-vida-con-adicional-de-salud/metropolitana.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M312"/>
+  <dimension ref="A1:M323"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -1164,7 +1164,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2702-27-CM25</t>
+          <t>543511-2-CM25</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1184,17 +1184,17 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>69.071.800-6</t>
+          <t>61.706.000-0</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE TALAGANTE</t>
+          <t>Comisión Chilena del Cobre - COCHILCO</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -1223,13 +1223,13 @@
         </is>
       </c>
       <c r="M12" s="2" t="n">
-        <v>8899.790000000001</v>
+        <v>7370.75</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>543511-2-CM25</t>
+          <t>2702-27-CM25</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1249,17 +1249,17 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>61.706.000-0</t>
+          <t>69.071.800-6</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Comisión Chilena del Cobre - COCHILCO</t>
+          <t>I MUNICIPALIDAD DE TALAGANTE</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -1288,7 +1288,7 @@
         </is>
       </c>
       <c r="M13" s="2" t="n">
-        <v>7370.75</v>
+        <v>8899.790000000001</v>
       </c>
     </row>
     <row r="14">
@@ -2464,7 +2464,7 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>550716-2-CM25</t>
+          <t>670784-2-CM25</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -2489,12 +2489,12 @@
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>65.961.370-0</t>
+          <t>60.818.000-1</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>GOBIERNO REGIONAL REGION METROPOLITANA</t>
+          <t>SUPERINTENDENCIA DE PENSIONES</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
@@ -2523,13 +2523,13 @@
         </is>
       </c>
       <c r="M32" s="2" t="n">
-        <v>5906.62</v>
+        <v>8527.16</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>670784-2-CM25</t>
+          <t>550716-2-CM25</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -2554,12 +2554,12 @@
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>60.818.000-1</t>
+          <t>65.961.370-0</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>SUPERINTENDENCIA DE PENSIONES</t>
+          <t>GOBIERNO REGIONAL REGION METROPOLITANA</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
@@ -2588,7 +2588,7 @@
         </is>
       </c>
       <c r="M33" s="2" t="n">
-        <v>8527.16</v>
+        <v>5906.62</v>
       </c>
     </row>
     <row r="34">
@@ -2789,7 +2789,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>307-15-CM25</t>
+          <t>1477-76-CM25</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -2814,12 +2814,12 @@
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>60.919.000-0</t>
+          <t>70.786.200-9</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Consejo de Rectores de las Universidades Chilenas</t>
+          <t>Corporación de Asistencia Judicial RM</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
@@ -2848,13 +2848,13 @@
         </is>
       </c>
       <c r="M37" s="2" t="n">
-        <v>531.36</v>
+        <v>29292.08</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>1477-76-CM25</t>
+          <t>307-15-CM25</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -2879,12 +2879,12 @@
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>70.786.200-9</t>
+          <t>60.919.000-0</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Corporación de Asistencia Judicial RM</t>
+          <t>Consejo de Rectores de las Universidades Chilenas</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
@@ -2913,7 +2913,7 @@
         </is>
       </c>
       <c r="M38" s="2" t="n">
-        <v>29292.08</v>
+        <v>531.36</v>
       </c>
     </row>
     <row r="39">
@@ -3244,7 +3244,7 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2701-191-CM25</t>
+          <t>2702-123-CM25</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -3303,13 +3303,13 @@
         </is>
       </c>
       <c r="M44" s="2" t="n">
-        <v>6964.44</v>
+        <v>9570.76</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2702-123-CM25</t>
+          <t>2701-191-CM25</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -3368,7 +3368,7 @@
         </is>
       </c>
       <c r="M45" s="2" t="n">
-        <v>9570.76</v>
+        <v>6964.44</v>
       </c>
     </row>
     <row r="46">
@@ -3634,7 +3634,7 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>553925-2-CM25</t>
+          <t>307-21-CM25</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -3659,12 +3659,12 @@
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>60.701.000-5</t>
+          <t>60.919.000-0</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>SUBSECRETARIA DE ECONOMIA Y EMPRESAS DE MENOR TAMANO</t>
+          <t>Consejo de Rectores de las Universidades Chilenas</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
@@ -3693,13 +3693,13 @@
         </is>
       </c>
       <c r="M50" s="2" t="n">
-        <v>22512.79</v>
+        <v>538.7</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>307-21-CM25</t>
+          <t>553925-2-CM25</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -3724,12 +3724,12 @@
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>60.919.000-0</t>
+          <t>60.701.000-5</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Consejo de Rectores de las Universidades Chilenas</t>
+          <t>SUBSECRETARIA DE ECONOMIA Y EMPRESAS DE MENOR TAMANO</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
@@ -3758,13 +3758,13 @@
         </is>
       </c>
       <c r="M51" s="2" t="n">
-        <v>538.7</v>
+        <v>22512.79</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>1211992-69-CM25</t>
+          <t>5482-61-SE25</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -3784,17 +3784,17 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>65.192.585-1</t>
+          <t>69.070.500-1</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>CORPORACIÓN YUNUS</t>
+          <t>I MUNICIPALIDAD DE NUNOA</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
@@ -3823,13 +3823,13 @@
         </is>
       </c>
       <c r="M52" s="2" t="n">
-        <v>2039.37</v>
+        <v>232885.44</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>5482-61-SE25</t>
+          <t>1211992-69-CM25</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -3849,17 +3849,17 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>69.070.500-1</t>
+          <t>65.192.585-1</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE NUNOA</t>
+          <t>CORPORACIÓN YUNUS</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
@@ -3888,7 +3888,7 @@
         </is>
       </c>
       <c r="M53" s="2" t="n">
-        <v>232885.44</v>
+        <v>2039.37</v>
       </c>
     </row>
     <row r="54">
@@ -4089,7 +4089,7 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>670784-4-CM25</t>
+          <t>2701-291-CM25</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -4114,12 +4114,12 @@
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>60.818.000-1</t>
+          <t>69.071.800-6</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>SUPERINTENDENCIA DE PENSIONES</t>
+          <t>I MUNICIPALIDAD DE TALAGANTE</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
@@ -4148,13 +4148,13 @@
         </is>
       </c>
       <c r="M57" s="2" t="n">
-        <v>8556.65</v>
+        <v>6803.58</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>2701-291-CM25</t>
+          <t>670784-4-CM25</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -4179,12 +4179,12 @@
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>69.071.800-6</t>
+          <t>60.818.000-1</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE TALAGANTE</t>
+          <t>SUPERINTENDENCIA DE PENSIONES</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
@@ -4213,7 +4213,7 @@
         </is>
       </c>
       <c r="M58" s="2" t="n">
-        <v>6803.58</v>
+        <v>8556.65</v>
       </c>
     </row>
     <row r="59">
@@ -5064,7 +5064,7 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>3378-4820-CM25</t>
+          <t>4722-1-CM25</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -5084,17 +5084,17 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>61.101.030-3</t>
+          <t>65.138.650-0</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>DIVISION LOGISTICA DEL EJERCITO</t>
+          <t>DEFENSORIA PENAL PUBLICA</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
@@ -5123,13 +5123,13 @@
         </is>
       </c>
       <c r="M72" s="2" t="n">
-        <v>15545.51</v>
+        <v>26827.43</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>4722-1-CM25</t>
+          <t>307-40-CM25</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -5154,12 +5154,12 @@
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>65.138.650-0</t>
+          <t>60.919.000-0</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>DEFENSORIA PENAL PUBLICA</t>
+          <t>Consejo de Rectores de las Universidades Chilenas</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
@@ -5188,13 +5188,13 @@
         </is>
       </c>
       <c r="M73" s="2" t="n">
-        <v>26827.43</v>
+        <v>608.6799999999999</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>307-40-CM25</t>
+          <t>3378-4820-CM25</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -5214,17 +5214,17 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>60.919.000-0</t>
+          <t>61.101.030-3</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Consejo de Rectores de las Universidades Chilenas</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
@@ -5253,7 +5253,7 @@
         </is>
       </c>
       <c r="M74" s="2" t="n">
-        <v>608.6799999999999</v>
+        <v>15545.51</v>
       </c>
     </row>
     <row r="75">
@@ -5324,7 +5324,7 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>3378-5108-CM25</t>
+          <t>1157285-10-CM25</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -5344,17 +5344,17 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>61.101.030-3</t>
+          <t>62.000.860-5</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>DIVISION LOGISTICA DEL EJERCITO</t>
+          <t>SUBSECRETARIA PARA LAS FUERZAS ARMADAS</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
@@ -5383,13 +5383,13 @@
         </is>
       </c>
       <c r="M76" s="2" t="n">
-        <v>15869.12</v>
+        <v>45047.81</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>1157285-10-CM25</t>
+          <t>3378-5108-CM25</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -5409,17 +5409,17 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>62.000.860-5</t>
+          <t>61.101.030-3</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>SUBSECRETARIA PARA LAS FUERZAS ARMADAS</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
@@ -5448,13 +5448,13 @@
         </is>
       </c>
       <c r="M77" s="2" t="n">
-        <v>45047.81</v>
+        <v>15869.12</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>2667-315-CM25</t>
+          <t>1186801-6-CM25</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -5479,12 +5479,12 @@
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>69.255.600-3</t>
+          <t>60.930.000-0</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE VITACURA</t>
+          <t>CONSEJO NACIONAL DE EDUCACION</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
@@ -5513,13 +5513,13 @@
         </is>
       </c>
       <c r="M78" s="2" t="n">
-        <v>319155.93</v>
+        <v>1084.86</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>1186801-6-CM25</t>
+          <t>2667-315-CM25</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -5544,12 +5544,12 @@
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>60.930.000-0</t>
+          <t>69.255.600-3</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>CONSEJO NACIONAL DE EDUCACION</t>
+          <t>I MUNICIPALIDAD DE VITACURA</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
@@ -5578,7 +5578,7 @@
         </is>
       </c>
       <c r="M79" s="2" t="n">
-        <v>1084.86</v>
+        <v>319155.93</v>
       </c>
     </row>
     <row r="80">
@@ -6429,7 +6429,7 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>670784-7-CM25</t>
+          <t>3378-6239-CM25</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -6449,17 +6449,17 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>60.818.000-1</t>
+          <t>61.101.030-3</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>SUPERINTENDENCIA DE PENSIONES</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
@@ -6488,13 +6488,13 @@
         </is>
       </c>
       <c r="M93" s="2" t="n">
-        <v>8454.799999999999</v>
+        <v>14929.94</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>3378-6239-CM25</t>
+          <t>670784-7-CM25</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -6514,17 +6514,17 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>61.101.030-3</t>
+          <t>60.818.000-1</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>DIVISION LOGISTICA DEL EJERCITO</t>
+          <t>SUPERINTENDENCIA DE PENSIONES</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
@@ -6553,7 +6553,7 @@
         </is>
       </c>
       <c r="M94" s="2" t="n">
-        <v>14929.94</v>
+        <v>8454.799999999999</v>
       </c>
     </row>
     <row r="95">
@@ -6754,7 +6754,7 @@
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>1477-247-CM25</t>
+          <t>1186801-9-CM25</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -6779,12 +6779,12 @@
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>70.786.200-9</t>
+          <t>60.930.000-0</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Corporación de Asistencia Judicial RM</t>
+          <t>CONSEJO NACIONAL DE EDUCACION</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
@@ -6813,13 +6813,13 @@
         </is>
       </c>
       <c r="M98" s="2" t="n">
-        <v>30775.84</v>
+        <v>1104.29</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>1186801-9-CM25</t>
+          <t>1477-247-CM25</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -6844,12 +6844,12 @@
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>60.930.000-0</t>
+          <t>70.786.200-9</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>CONSEJO NACIONAL DE EDUCACION</t>
+          <t>Corporación de Asistencia Judicial RM</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
@@ -6878,7 +6878,7 @@
         </is>
       </c>
       <c r="M99" s="2" t="n">
-        <v>1104.29</v>
+        <v>30775.84</v>
       </c>
     </row>
     <row r="100">
@@ -7079,7 +7079,7 @@
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>2702-382-CM25</t>
+          <t>1373053-9-CM25</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -7104,12 +7104,12 @@
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>69.071.800-6</t>
+          <t>82.174.900-k</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE TALAGANTE</t>
+          <t>SERVICIO DE COOPERACION TECNICA</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
@@ -7138,13 +7138,13 @@
         </is>
       </c>
       <c r="M103" s="2" t="n">
-        <v>9183.23</v>
+        <v>7776.79</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>1373053-9-CM25</t>
+          <t>2702-382-CM25</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -7169,12 +7169,12 @@
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>82.174.900-k</t>
+          <t>69.071.800-6</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>SERVICIO DE COOPERACION TECNICA</t>
+          <t>I MUNICIPALIDAD DE TALAGANTE</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
@@ -7203,7 +7203,7 @@
         </is>
       </c>
       <c r="M104" s="2" t="n">
-        <v>7776.79</v>
+        <v>9183.23</v>
       </c>
     </row>
     <row r="105">
@@ -8054,7 +8054,7 @@
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>670784-10-CM25</t>
+          <t>1186801-12-CM25</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
@@ -8079,12 +8079,12 @@
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>60.818.000-1</t>
+          <t>60.930.000-0</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>SUPERINTENDENCIA DE PENSIONES</t>
+          <t>CONSEJO NACIONAL DE EDUCACION</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
@@ -8113,13 +8113,13 @@
         </is>
       </c>
       <c r="M118" s="2" t="n">
-        <v>8503.780000000001</v>
+        <v>1096.37</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>1186801-12-CM25</t>
+          <t>670784-10-CM25</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
@@ -8144,12 +8144,12 @@
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>60.930.000-0</t>
+          <t>60.818.000-1</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>CONSEJO NACIONAL DE EDUCACION</t>
+          <t>SUPERINTENDENCIA DE PENSIONES</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
@@ -8178,7 +8178,7 @@
         </is>
       </c>
       <c r="M119" s="2" t="n">
-        <v>1096.37</v>
+        <v>8503.780000000001</v>
       </c>
     </row>
     <row r="120">
@@ -8249,7 +8249,7 @@
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>1166422-4-CM25</t>
+          <t>2702-483-CM25</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
@@ -8274,12 +8274,12 @@
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>61.001.002-4</t>
+          <t>69.071.800-6</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>SUBSECRETARIA DEL MINISTERIO DE JUSTICIA</t>
+          <t>I MUNICIPALIDAD DE TALAGANTE</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
@@ -8308,13 +8308,13 @@
         </is>
       </c>
       <c r="M121" s="2" t="n">
-        <v>184748.34</v>
+        <v>9246.620000000001</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>2702-483-CM25</t>
+          <t>1166422-4-CM25</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
@@ -8339,12 +8339,12 @@
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>69.071.800-6</t>
+          <t>61.001.002-4</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE TALAGANTE</t>
+          <t>SUBSECRETARIA DEL MINISTERIO DE JUSTICIA</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
@@ -8373,7 +8373,7 @@
         </is>
       </c>
       <c r="M122" s="2" t="n">
-        <v>9246.620000000001</v>
+        <v>184748.34</v>
       </c>
     </row>
     <row r="123">
@@ -8444,7 +8444,7 @@
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>1373053-11-CM25</t>
+          <t>1373053-10-CM25</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
@@ -8503,13 +8503,13 @@
         </is>
       </c>
       <c r="M124" s="2" t="n">
-        <v>7926.61</v>
+        <v>7801.46</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>1373053-10-CM25</t>
+          <t>1373053-11-CM25</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
@@ -8568,7 +8568,7 @@
         </is>
       </c>
       <c r="M125" s="2" t="n">
-        <v>7801.46</v>
+        <v>7926.61</v>
       </c>
     </row>
     <row r="126">
@@ -8769,7 +8769,7 @@
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>670784-11-CM25</t>
+          <t>1186801-13-CM25</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
@@ -8794,12 +8794,12 @@
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>60.818.000-1</t>
+          <t>60.930.000-0</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>SUPERINTENDENCIA DE PENSIONES</t>
+          <t>CONSEJO NACIONAL DE EDUCACION</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
@@ -8828,13 +8828,13 @@
         </is>
       </c>
       <c r="M129" s="2" t="n">
-        <v>8683.26</v>
+        <v>1108.64</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>1186801-13-CM25</t>
+          <t>670784-11-CM25</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
@@ -8859,12 +8859,12 @@
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>60.930.000-0</t>
+          <t>60.818.000-1</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>CONSEJO NACIONAL DE EDUCACION</t>
+          <t>SUPERINTENDENCIA DE PENSIONES</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
@@ -8893,7 +8893,7 @@
         </is>
       </c>
       <c r="M130" s="2" t="n">
-        <v>1108.64</v>
+        <v>8683.26</v>
       </c>
     </row>
     <row r="131">
@@ -9809,7 +9809,7 @@
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>1186801-15-CM25</t>
+          <t>1186801-14-CM25</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
@@ -9868,13 +9868,13 @@
         </is>
       </c>
       <c r="M145" s="2" t="n">
-        <v>1104.53</v>
+        <v>1141.35</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>1186801-14-CM25</t>
+          <t>1186801-15-CM25</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
@@ -9933,7 +9933,7 @@
         </is>
       </c>
       <c r="M146" s="2" t="n">
-        <v>1141.35</v>
+        <v>1104.53</v>
       </c>
     </row>
     <row r="147">
@@ -10004,7 +10004,7 @@
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>1373053-13-CM25</t>
+          <t>307-102-CM25</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
@@ -10029,12 +10029,12 @@
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>82.174.900-k</t>
+          <t>60.919.000-0</t>
         </is>
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>SERVICIO DE COOPERACION TECNICA</t>
+          <t>Consejo de Rectores de las Universidades Chilenas</t>
         </is>
       </c>
       <c r="H148" t="inlineStr">
@@ -10063,7 +10063,7 @@
         </is>
       </c>
       <c r="M148" s="2" t="n">
-        <v>8444.09</v>
+        <v>623.76</v>
       </c>
     </row>
     <row r="149">
@@ -10134,7 +10134,7 @@
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>307-102-CM25</t>
+          <t>1373053-13-CM25</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
@@ -10159,12 +10159,12 @@
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>60.919.000-0</t>
+          <t>82.174.900-k</t>
         </is>
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>Consejo de Rectores de las Universidades Chilenas</t>
+          <t>SERVICIO DE COOPERACION TECNICA</t>
         </is>
       </c>
       <c r="H150" t="inlineStr">
@@ -10193,7 +10193,7 @@
         </is>
       </c>
       <c r="M150" s="2" t="n">
-        <v>623.76</v>
+        <v>8444.09</v>
       </c>
     </row>
     <row r="151">
@@ -10979,7 +10979,7 @@
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>2701-5-CM26</t>
+          <t>574800-1-CM26</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
@@ -11004,12 +11004,12 @@
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t>69.071.800-6</t>
+          <t>60.601.000-1</t>
         </is>
       </c>
       <c r="G163" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE TALAGANTE</t>
+          <t>SUBSECRETARIA DE RELACIONES EXTERIORES</t>
         </is>
       </c>
       <c r="H163" t="inlineStr">
@@ -11038,13 +11038,13 @@
         </is>
       </c>
       <c r="M163" s="2" t="n">
-        <v>7274.71</v>
+        <v>63593.52</v>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>574800-1-CM26</t>
+          <t>2701-5-CM26</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
@@ -11069,12 +11069,12 @@
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t>60.601.000-1</t>
+          <t>69.071.800-6</t>
         </is>
       </c>
       <c r="G164" t="inlineStr">
         <is>
-          <t>SUBSECRETARIA DE RELACIONES EXTERIORES</t>
+          <t>I MUNICIPALIDAD DE TALAGANTE</t>
         </is>
       </c>
       <c r="H164" t="inlineStr">
@@ -11103,7 +11103,7 @@
         </is>
       </c>
       <c r="M164" s="2" t="n">
-        <v>63593.52</v>
+        <v>7274.71</v>
       </c>
     </row>
     <row r="165">
@@ -11499,7 +11499,7 @@
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>1153625-3-CM26</t>
+          <t>786370-1-CM26</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
@@ -11519,17 +11519,17 @@
       </c>
       <c r="E171" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t>62.000.670-K</t>
+          <t>61.980.170-9</t>
         </is>
       </c>
       <c r="G171" t="inlineStr">
         <is>
-          <t>SUBSECRETARIA DE RELACIONES ECONOMICAS INTERNACIONALES</t>
+          <t>SERVICIO NACIONAL PARA LA PREVENCION Y REHABILITACION DEL CONSUMO DE D</t>
         </is>
       </c>
       <c r="H171" t="inlineStr">
@@ -11558,13 +11558,13 @@
         </is>
       </c>
       <c r="M171" s="2" t="n">
-        <v>66441.31</v>
+        <v>66147.32000000001</v>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>1111089-31-CM26</t>
+          <t>1157285-1-SE26</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
@@ -11589,12 +11589,12 @@
       </c>
       <c r="F172" t="inlineStr">
         <is>
-          <t>60.915.000-9</t>
+          <t>62.000.860-5</t>
         </is>
       </c>
       <c r="G172" t="inlineStr">
         <is>
-          <t>Comisión Nacional de Investigación Científica y Tecnológicas - CONICYT</t>
+          <t>SUBSECRETARIA PARA LAS FUERZAS ARMADAS</t>
         </is>
       </c>
       <c r="H172" t="inlineStr">
@@ -11623,13 +11623,13 @@
         </is>
       </c>
       <c r="M172" s="2" t="n">
-        <v>44161.73</v>
+        <v>50859.94</v>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>786370-1-CM26</t>
+          <t>1111089-31-CM26</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
@@ -11649,17 +11649,17 @@
       </c>
       <c r="E173" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F173" t="inlineStr">
         <is>
-          <t>61.980.170-9</t>
+          <t>60.915.000-9</t>
         </is>
       </c>
       <c r="G173" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL PARA LA PREVENCION Y REHABILITACION DEL CONSUMO DE D</t>
+          <t>Comisión Nacional de Investigación Científica y Tecnológicas - CONICYT</t>
         </is>
       </c>
       <c r="H173" t="inlineStr">
@@ -11688,13 +11688,13 @@
         </is>
       </c>
       <c r="M173" s="2" t="n">
-        <v>66147.32000000001</v>
+        <v>44161.73</v>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>1157285-1-SE26</t>
+          <t>1153625-3-CM26</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
@@ -11719,12 +11719,12 @@
       </c>
       <c r="F174" t="inlineStr">
         <is>
-          <t>62.000.860-5</t>
+          <t>62.000.670-K</t>
         </is>
       </c>
       <c r="G174" t="inlineStr">
         <is>
-          <t>SUBSECRETARIA PARA LAS FUERZAS ARMADAS</t>
+          <t>SUBSECRETARIA DE RELACIONES ECONOMICAS INTERNACIONALES</t>
         </is>
       </c>
       <c r="H174" t="inlineStr">
@@ -11753,7 +11753,7 @@
         </is>
       </c>
       <c r="M174" s="2" t="n">
-        <v>50859.94</v>
+        <v>66441.31</v>
       </c>
     </row>
     <row r="175">
@@ -12084,7 +12084,7 @@
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>543511-1-CM26</t>
+          <t>626802-3-CM26</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
@@ -12104,17 +12104,17 @@
       </c>
       <c r="E180" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F180" t="inlineStr">
         <is>
-          <t>61.706.000-0</t>
+          <t>65.034.169-4</t>
         </is>
       </c>
       <c r="G180" t="inlineStr">
         <is>
-          <t>Comisión Chilena del Cobre - COCHILCO</t>
+          <t>Consejo Resolutivo de Asignaciones Parlamentaria</t>
         </is>
       </c>
       <c r="H180" t="inlineStr">
@@ -12143,13 +12143,13 @@
         </is>
       </c>
       <c r="M180" s="2" t="n">
-        <v>9592.43</v>
+        <v>4695.24</v>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>626802-3-CM26</t>
+          <t>543511-1-CM26</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
@@ -12169,17 +12169,17 @@
       </c>
       <c r="E181" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F181" t="inlineStr">
         <is>
-          <t>65.034.169-4</t>
+          <t>61.706.000-0</t>
         </is>
       </c>
       <c r="G181" t="inlineStr">
         <is>
-          <t>Consejo Resolutivo de Asignaciones Parlamentaria</t>
+          <t>Comisión Chilena del Cobre - COCHILCO</t>
         </is>
       </c>
       <c r="H181" t="inlineStr">
@@ -12208,13 +12208,13 @@
         </is>
       </c>
       <c r="M181" s="2" t="n">
-        <v>4695.24</v>
+        <v>9592.43</v>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>550716-1-CM26</t>
+          <t>5134-2-CM26</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
@@ -12234,17 +12234,17 @@
       </c>
       <c r="E182" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F182" t="inlineStr">
         <is>
-          <t>65.961.370-0</t>
+          <t>61.005.000-k</t>
         </is>
       </c>
       <c r="G182" t="inlineStr">
         <is>
-          <t>GOBIERNO REGIONAL REGION METROPOLITANA</t>
+          <t>SUPERINTENDENCIA DE INSOLVENCIA Y REEMPRENDIMIENTO</t>
         </is>
       </c>
       <c r="H182" t="inlineStr">
@@ -12273,13 +12273,13 @@
         </is>
       </c>
       <c r="M182" s="2" t="n">
-        <v>7256.26</v>
+        <v>79768.07000000001</v>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>5134-2-CM26</t>
+          <t>1477-24-CM26</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
@@ -12304,12 +12304,12 @@
       </c>
       <c r="F183" t="inlineStr">
         <is>
-          <t>61.005.000-k</t>
+          <t>70.786.200-9</t>
         </is>
       </c>
       <c r="G183" t="inlineStr">
         <is>
-          <t>SUPERINTENDENCIA DE INSOLVENCIA Y REEMPRENDIMIENTO</t>
+          <t>Corporación de Asistencia Judicial RM</t>
         </is>
       </c>
       <c r="H183" t="inlineStr">
@@ -12338,13 +12338,13 @@
         </is>
       </c>
       <c r="M183" s="2" t="n">
-        <v>79768.07000000001</v>
+        <v>37905.05</v>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>1477-24-CM26</t>
+          <t>550716-1-CM26</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
@@ -12364,17 +12364,17 @@
       </c>
       <c r="E184" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F184" t="inlineStr">
         <is>
-          <t>70.786.200-9</t>
+          <t>65.961.370-0</t>
         </is>
       </c>
       <c r="G184" t="inlineStr">
         <is>
-          <t>Corporación de Asistencia Judicial RM</t>
+          <t>GOBIERNO REGIONAL REGION METROPOLITANA</t>
         </is>
       </c>
       <c r="H184" t="inlineStr">
@@ -12403,7 +12403,7 @@
         </is>
       </c>
       <c r="M184" s="2" t="n">
-        <v>37905.05</v>
+        <v>7256.26</v>
       </c>
     </row>
     <row r="185">
@@ -12539,7 +12539,7 @@
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>606591-4-CM26</t>
+          <t>606591-5-CM26</t>
         </is>
       </c>
       <c r="B187" t="inlineStr">
@@ -12598,13 +12598,13 @@
         </is>
       </c>
       <c r="M187" s="2" t="n">
-        <v>35616.04</v>
+        <v>32901.72</v>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>606591-5-CM26</t>
+          <t>606591-4-CM26</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
@@ -12663,7 +12663,7 @@
         </is>
       </c>
       <c r="M188" s="2" t="n">
-        <v>32901.72</v>
+        <v>35616.04</v>
       </c>
     </row>
     <row r="189">
@@ -12929,7 +12929,7 @@
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t>1211992-22-CM26</t>
+          <t>2701-85-CM26</t>
         </is>
       </c>
       <c r="B193" t="inlineStr">
@@ -12949,17 +12949,17 @@
       </c>
       <c r="E193" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F193" t="inlineStr">
         <is>
-          <t>65.192.585-1</t>
+          <t>69.071.800-6</t>
         </is>
       </c>
       <c r="G193" t="inlineStr">
         <is>
-          <t>CORPORACIÓN YUNUS</t>
+          <t>I MUNICIPALIDAD DE TALAGANTE</t>
         </is>
       </c>
       <c r="H193" t="inlineStr">
@@ -12988,13 +12988,13 @@
         </is>
       </c>
       <c r="M193" s="2" t="n">
-        <v>1565.68</v>
+        <v>8181.93</v>
       </c>
     </row>
     <row r="194">
       <c r="A194" t="inlineStr">
         <is>
-          <t>2701-85-CM26</t>
+          <t>1211992-22-CM26</t>
         </is>
       </c>
       <c r="B194" t="inlineStr">
@@ -13014,17 +13014,17 @@
       </c>
       <c r="E194" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F194" t="inlineStr">
         <is>
-          <t>69.071.800-6</t>
+          <t>65.192.585-1</t>
         </is>
       </c>
       <c r="G194" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE TALAGANTE</t>
+          <t>CORPORACIÓN YUNUS</t>
         </is>
       </c>
       <c r="H194" t="inlineStr">
@@ -13053,7 +13053,7 @@
         </is>
       </c>
       <c r="M194" s="2" t="n">
-        <v>8181.93</v>
+        <v>1565.68</v>
       </c>
     </row>
     <row r="195">
@@ -13189,7 +13189,7 @@
     <row r="197">
       <c r="A197" t="inlineStr">
         <is>
-          <t>1477-47-CM26</t>
+          <t>3378-1718-CM26</t>
         </is>
       </c>
       <c r="B197" t="inlineStr">
@@ -13209,17 +13209,17 @@
       </c>
       <c r="E197" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F197" t="inlineStr">
         <is>
-          <t>70.786.200-9</t>
+          <t>61.101.030-3</t>
         </is>
       </c>
       <c r="G197" t="inlineStr">
         <is>
-          <t>Corporación de Asistencia Judicial RM</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H197" t="inlineStr">
@@ -13248,13 +13248,13 @@
         </is>
       </c>
       <c r="M197" s="2" t="n">
-        <v>37714.34</v>
+        <v>17394.98</v>
       </c>
     </row>
     <row r="198">
       <c r="A198" t="inlineStr">
         <is>
-          <t>3378-1718-CM26</t>
+          <t>1477-47-CM26</t>
         </is>
       </c>
       <c r="B198" t="inlineStr">
@@ -13274,17 +13274,17 @@
       </c>
       <c r="E198" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F198" t="inlineStr">
         <is>
-          <t>61.101.030-3</t>
+          <t>70.786.200-9</t>
         </is>
       </c>
       <c r="G198" t="inlineStr">
         <is>
-          <t>DIVISION LOGISTICA DEL EJERCITO</t>
+          <t>Corporación de Asistencia Judicial RM</t>
         </is>
       </c>
       <c r="H198" t="inlineStr">
@@ -13313,7 +13313,7 @@
         </is>
       </c>
       <c r="M198" s="2" t="n">
-        <v>17394.98</v>
+        <v>37714.34</v>
       </c>
     </row>
     <row r="199">
@@ -14229,7 +14229,7 @@
     <row r="213">
       <c r="A213" t="inlineStr">
         <is>
-          <t>1149280-4-SE26</t>
+          <t>1186801-3-CM26</t>
         </is>
       </c>
       <c r="B213" t="inlineStr">
@@ -14254,12 +14254,12 @@
       </c>
       <c r="F213" t="inlineStr">
         <is>
-          <t>60.400.000-9</t>
+          <t>60.930.000-0</t>
         </is>
       </c>
       <c r="G213" t="inlineStr">
         <is>
-          <t>CONTRALORIA GENERAL DE LA REPUBLICA</t>
+          <t>CONSEJO NACIONAL DE EDUCACION</t>
         </is>
       </c>
       <c r="H213" t="inlineStr">
@@ -14288,7 +14288,7 @@
         </is>
       </c>
       <c r="M213" s="2" t="n">
-        <v>717480.3100000001</v>
+        <v>1205.28</v>
       </c>
     </row>
     <row r="214">
@@ -14359,7 +14359,7 @@
     <row r="215">
       <c r="A215" t="inlineStr">
         <is>
-          <t>1186801-3-CM26</t>
+          <t>1149280-4-SE26</t>
         </is>
       </c>
       <c r="B215" t="inlineStr">
@@ -14384,12 +14384,12 @@
       </c>
       <c r="F215" t="inlineStr">
         <is>
-          <t>60.930.000-0</t>
+          <t>60.400.000-9</t>
         </is>
       </c>
       <c r="G215" t="inlineStr">
         <is>
-          <t>CONSEJO NACIONAL DE EDUCACION</t>
+          <t>CONTRALORIA GENERAL DE LA REPUBLICA</t>
         </is>
       </c>
       <c r="H215" t="inlineStr">
@@ -14418,7 +14418,7 @@
         </is>
       </c>
       <c r="M215" s="2" t="n">
-        <v>1205.28</v>
+        <v>717480.3100000001</v>
       </c>
     </row>
     <row r="216">
@@ -14554,7 +14554,7 @@
     <row r="218">
       <c r="A218" t="inlineStr">
         <is>
-          <t>1373053-3-CM26</t>
+          <t>603663-54-CM26</t>
         </is>
       </c>
       <c r="B218" t="inlineStr">
@@ -14579,12 +14579,12 @@
       </c>
       <c r="F218" t="inlineStr">
         <is>
-          <t>82.174.900-k</t>
+          <t>65.028.707-K</t>
         </is>
       </c>
       <c r="G218" t="inlineStr">
         <is>
-          <t>SERVICIO DE COOPERACION TECNICA</t>
+          <t>INSTITUTO NACIONAL DE DERECHOS HUMANOS</t>
         </is>
       </c>
       <c r="H218" t="inlineStr">
@@ -14613,7 +14613,7 @@
         </is>
       </c>
       <c r="M218" s="2" t="n">
-        <v>9257.09</v>
+        <v>76156.3</v>
       </c>
     </row>
     <row r="219">
@@ -14684,7 +14684,7 @@
     <row r="220">
       <c r="A220" t="inlineStr">
         <is>
-          <t>603663-54-CM26</t>
+          <t>1373053-3-CM26</t>
         </is>
       </c>
       <c r="B220" t="inlineStr">
@@ -14709,12 +14709,12 @@
       </c>
       <c r="F220" t="inlineStr">
         <is>
-          <t>65.028.707-K</t>
+          <t>82.174.900-k</t>
         </is>
       </c>
       <c r="G220" t="inlineStr">
         <is>
-          <t>INSTITUTO NACIONAL DE DERECHOS HUMANOS</t>
+          <t>SERVICIO DE COOPERACION TECNICA</t>
         </is>
       </c>
       <c r="H220" t="inlineStr">
@@ -14743,7 +14743,7 @@
         </is>
       </c>
       <c r="M220" s="2" t="n">
-        <v>76156.3</v>
+        <v>9257.09</v>
       </c>
     </row>
     <row r="221">
@@ -14814,7 +14814,7 @@
     <row r="222">
       <c r="A222" t="inlineStr">
         <is>
-          <t>1211992-43-CM26</t>
+          <t>4973-40-SE26</t>
         </is>
       </c>
       <c r="B222" t="inlineStr">
@@ -14834,17 +14834,17 @@
       </c>
       <c r="E222" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F222" t="inlineStr">
         <is>
-          <t>65.192.585-1</t>
+          <t>61.202.016-7</t>
         </is>
       </c>
       <c r="G222" t="inlineStr">
         <is>
-          <t>CORPORACIÓN YUNUS</t>
+          <t>MINISTERIO DE OBRAS PUBLICAS DIREC CION GRAL DE OO PP DCYF</t>
         </is>
       </c>
       <c r="H222" t="inlineStr">
@@ -14873,13 +14873,13 @@
         </is>
       </c>
       <c r="M222" s="2" t="n">
-        <v>1242.65</v>
+        <v>1573308.56</v>
       </c>
     </row>
     <row r="223">
       <c r="A223" t="inlineStr">
         <is>
-          <t>4973-40-SE26</t>
+          <t>1211992-43-CM26</t>
         </is>
       </c>
       <c r="B223" t="inlineStr">
@@ -14899,17 +14899,17 @@
       </c>
       <c r="E223" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F223" t="inlineStr">
         <is>
-          <t>61.202.016-7</t>
+          <t>65.192.585-1</t>
         </is>
       </c>
       <c r="G223" t="inlineStr">
         <is>
-          <t>MINISTERIO DE OBRAS PUBLICAS DIREC CION GRAL DE OO PP DCYF</t>
+          <t>CORPORACIÓN YUNUS</t>
         </is>
       </c>
       <c r="H223" t="inlineStr">
@@ -14938,7 +14938,7 @@
         </is>
       </c>
       <c r="M223" s="2" t="n">
-        <v>1573308.56</v>
+        <v>1242.65</v>
       </c>
     </row>
     <row r="224">
@@ -15009,7 +15009,7 @@
     <row r="225">
       <c r="A225" t="inlineStr">
         <is>
-          <t>5482-80-CM26</t>
+          <t>5482-81-CM26</t>
         </is>
       </c>
       <c r="B225" t="inlineStr">
@@ -15074,7 +15074,7 @@
     <row r="226">
       <c r="A226" t="inlineStr">
         <is>
-          <t>5482-81-CM26</t>
+          <t>5482-80-CM26</t>
         </is>
       </c>
       <c r="B226" t="inlineStr">
@@ -15334,7 +15334,7 @@
     <row r="230">
       <c r="A230" t="inlineStr">
         <is>
-          <t>1495206-1-CM26</t>
+          <t>1477-108-CM26</t>
         </is>
       </c>
       <c r="B230" t="inlineStr">
@@ -15359,12 +15359,12 @@
       </c>
       <c r="F230" t="inlineStr">
         <is>
-          <t>61.981.340-5</t>
+          <t>70.786.200-9</t>
         </is>
       </c>
       <c r="G230" t="inlineStr">
         <is>
-          <t>SERVICIO DE BIODIVERSIDAD Y ÁREAS PROTEGIDAS</t>
+          <t>Corporación de Asistencia Judicial RM</t>
         </is>
       </c>
       <c r="H230" t="inlineStr">
@@ -15393,13 +15393,13 @@
         </is>
       </c>
       <c r="M230" s="2" t="n">
-        <v>3227.45</v>
+        <v>36973.69</v>
       </c>
     </row>
     <row r="231">
       <c r="A231" t="inlineStr">
         <is>
-          <t>1477-108-CM26</t>
+          <t>1495206-1-CM26</t>
         </is>
       </c>
       <c r="B231" t="inlineStr">
@@ -15424,12 +15424,12 @@
       </c>
       <c r="F231" t="inlineStr">
         <is>
-          <t>70.786.200-9</t>
+          <t>61.981.340-5</t>
         </is>
       </c>
       <c r="G231" t="inlineStr">
         <is>
-          <t>Corporación de Asistencia Judicial RM</t>
+          <t>SERVICIO DE BIODIVERSIDAD Y ÁREAS PROTEGIDAS</t>
         </is>
       </c>
       <c r="H231" t="inlineStr">
@@ -15458,7 +15458,7 @@
         </is>
       </c>
       <c r="M231" s="2" t="n">
-        <v>36973.69</v>
+        <v>3227.45</v>
       </c>
     </row>
     <row r="232">
@@ -15659,7 +15659,7 @@
     <row r="235">
       <c r="A235" t="inlineStr">
         <is>
-          <t>1373053-5-CM26</t>
+          <t>1211992-69-CM26</t>
         </is>
       </c>
       <c r="B235" t="inlineStr">
@@ -15679,17 +15679,17 @@
       </c>
       <c r="E235" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F235" t="inlineStr">
         <is>
-          <t>82.174.900-k</t>
+          <t>65.192.585-1</t>
         </is>
       </c>
       <c r="G235" t="inlineStr">
         <is>
-          <t>SERVICIO DE COOPERACION TECNICA</t>
+          <t>CORPORACIÓN YUNUS</t>
         </is>
       </c>
       <c r="H235" t="inlineStr">
@@ -15718,13 +15718,13 @@
         </is>
       </c>
       <c r="M235" s="2" t="n">
-        <v>9595.75</v>
+        <v>1266.44</v>
       </c>
     </row>
     <row r="236">
       <c r="A236" t="inlineStr">
         <is>
-          <t>1211992-69-CM26</t>
+          <t>1373053-5-CM26</t>
         </is>
       </c>
       <c r="B236" t="inlineStr">
@@ -15744,17 +15744,17 @@
       </c>
       <c r="E236" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F236" t="inlineStr">
         <is>
-          <t>65.192.585-1</t>
+          <t>82.174.900-k</t>
         </is>
       </c>
       <c r="G236" t="inlineStr">
         <is>
-          <t>CORPORACIÓN YUNUS</t>
+          <t>SERVICIO DE COOPERACION TECNICA</t>
         </is>
       </c>
       <c r="H236" t="inlineStr">
@@ -15783,7 +15783,7 @@
         </is>
       </c>
       <c r="M236" s="2" t="n">
-        <v>1266.44</v>
+        <v>9595.75</v>
       </c>
     </row>
     <row r="237">
@@ -16244,7 +16244,7 @@
     <row r="244">
       <c r="A244" t="inlineStr">
         <is>
-          <t>1395481-2-SE26</t>
+          <t>1395481-3-SE26</t>
         </is>
       </c>
       <c r="B244" t="inlineStr">
@@ -16303,13 +16303,13 @@
         </is>
       </c>
       <c r="M244" s="2" t="n">
-        <v>117272.9</v>
+        <v>257795.23</v>
       </c>
     </row>
     <row r="245">
       <c r="A245" t="inlineStr">
         <is>
-          <t>1395481-3-SE26</t>
+          <t>1395481-2-SE26</t>
         </is>
       </c>
       <c r="B245" t="inlineStr">
@@ -16368,7 +16368,7 @@
         </is>
       </c>
       <c r="M245" s="2" t="n">
-        <v>257795.23</v>
+        <v>117272.9</v>
       </c>
     </row>
     <row r="246">
@@ -17804,7 +17804,7 @@
     <row r="268">
       <c r="A268" t="inlineStr">
         <is>
-          <t>545927-3-SE26</t>
+          <t>550716-9-CM26</t>
         </is>
       </c>
       <c r="B268" t="inlineStr">
@@ -17829,12 +17829,12 @@
       </c>
       <c r="F268" t="inlineStr">
         <is>
-          <t>61.212.000-5</t>
+          <t>65.961.370-0</t>
         </is>
       </c>
       <c r="G268" t="inlineStr">
         <is>
-          <t>SUBSECRETARIA DE TRANSPORTES</t>
+          <t>GOBIERNO REGIONAL REGION METROPOLITANA</t>
         </is>
       </c>
       <c r="H268" t="inlineStr">
@@ -17863,7 +17863,7 @@
         </is>
       </c>
       <c r="M268" s="2" t="n">
-        <v>581414.84</v>
+        <v>7073.88</v>
       </c>
     </row>
     <row r="269">
@@ -17934,7 +17934,7 @@
     <row r="270">
       <c r="A270" t="inlineStr">
         <is>
-          <t>550716-9-CM26</t>
+          <t>545927-3-SE26</t>
         </is>
       </c>
       <c r="B270" t="inlineStr">
@@ -17959,12 +17959,12 @@
       </c>
       <c r="F270" t="inlineStr">
         <is>
-          <t>65.961.370-0</t>
+          <t>61.212.000-5</t>
         </is>
       </c>
       <c r="G270" t="inlineStr">
         <is>
-          <t>GOBIERNO REGIONAL REGION METROPOLITANA</t>
+          <t>SUBSECRETARIA DE TRANSPORTES</t>
         </is>
       </c>
       <c r="H270" t="inlineStr">
@@ -17993,7 +17993,7 @@
         </is>
       </c>
       <c r="M270" s="2" t="n">
-        <v>7073.88</v>
+        <v>581414.84</v>
       </c>
     </row>
     <row r="271">
@@ -18324,7 +18324,7 @@
     <row r="276">
       <c r="A276" t="inlineStr">
         <is>
-          <t>2701-496-CM26</t>
+          <t>1477-242-CM26</t>
         </is>
       </c>
       <c r="B276" t="inlineStr">
@@ -18349,12 +18349,12 @@
       </c>
       <c r="F276" t="inlineStr">
         <is>
-          <t>69.071.800-6</t>
+          <t>70.786.200-9</t>
         </is>
       </c>
       <c r="G276" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE TALAGANTE</t>
+          <t>Corporación de Asistencia Judicial RM</t>
         </is>
       </c>
       <c r="H276" t="inlineStr">
@@ -18383,13 +18383,13 @@
         </is>
       </c>
       <c r="M276" s="2" t="n">
-        <v>7849.1</v>
+        <v>36580.68</v>
       </c>
     </row>
     <row r="277">
       <c r="A277" t="inlineStr">
         <is>
-          <t>1477-242-CM26</t>
+          <t>2701-496-CM26</t>
         </is>
       </c>
       <c r="B277" t="inlineStr">
@@ -18414,12 +18414,12 @@
       </c>
       <c r="F277" t="inlineStr">
         <is>
-          <t>70.786.200-9</t>
+          <t>69.071.800-6</t>
         </is>
       </c>
       <c r="G277" t="inlineStr">
         <is>
-          <t>Corporación de Asistencia Judicial RM</t>
+          <t>I MUNICIPALIDAD DE TALAGANTE</t>
         </is>
       </c>
       <c r="H277" t="inlineStr">
@@ -18448,7 +18448,7 @@
         </is>
       </c>
       <c r="M277" s="2" t="n">
-        <v>36580.68</v>
+        <v>7849.1</v>
       </c>
     </row>
     <row r="278">
@@ -18584,7 +18584,7 @@
     <row r="280">
       <c r="A280" t="inlineStr">
         <is>
-          <t>1211992-168-CM26</t>
+          <t>626802-9-CM26</t>
         </is>
       </c>
       <c r="B280" t="inlineStr">
@@ -18604,17 +18604,17 @@
       </c>
       <c r="E280" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F280" t="inlineStr">
         <is>
-          <t>65.192.585-1</t>
+          <t>65.034.169-4</t>
         </is>
       </c>
       <c r="G280" t="inlineStr">
         <is>
-          <t>CORPORACIÓN YUNUS</t>
+          <t>Consejo Resolutivo de Asignaciones Parlamentaria</t>
         </is>
       </c>
       <c r="H280" t="inlineStr">
@@ -18643,13 +18643,13 @@
         </is>
       </c>
       <c r="M280" s="2" t="n">
-        <v>1622.04</v>
+        <v>2949.17</v>
       </c>
     </row>
     <row r="281">
       <c r="A281" t="inlineStr">
         <is>
-          <t>626802-9-CM26</t>
+          <t>1211992-168-CM26</t>
         </is>
       </c>
       <c r="B281" t="inlineStr">
@@ -18669,17 +18669,17 @@
       </c>
       <c r="E281" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F281" t="inlineStr">
         <is>
-          <t>65.034.169-4</t>
+          <t>65.192.585-1</t>
         </is>
       </c>
       <c r="G281" t="inlineStr">
         <is>
-          <t>Consejo Resolutivo de Asignaciones Parlamentaria</t>
+          <t>CORPORACIÓN YUNUS</t>
         </is>
       </c>
       <c r="H281" t="inlineStr">
@@ -18708,7 +18708,7 @@
         </is>
       </c>
       <c r="M281" s="2" t="n">
-        <v>2949.17</v>
+        <v>1622.04</v>
       </c>
     </row>
     <row r="282">
@@ -18909,7 +18909,7 @@
     <row r="285">
       <c r="A285" t="inlineStr">
         <is>
-          <t>2701-560-CM26</t>
+          <t>1500781-64-CM26</t>
         </is>
       </c>
       <c r="B285" t="inlineStr">
@@ -18934,12 +18934,12 @@
       </c>
       <c r="F285" t="inlineStr">
         <is>
-          <t>69.071.800-6</t>
+          <t>65.260.064-6</t>
         </is>
       </c>
       <c r="G285" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE TALAGANTE</t>
+          <t>CORPORACION MUNICIPAL DE DEPORTES, CULTURA, RECREACION Y FOMENTO DE HU</t>
         </is>
       </c>
       <c r="H285" t="inlineStr">
@@ -18968,13 +18968,13 @@
         </is>
       </c>
       <c r="M285" s="2" t="n">
-        <v>7874.28</v>
+        <v>46630.5</v>
       </c>
     </row>
     <row r="286">
       <c r="A286" t="inlineStr">
         <is>
-          <t>1500781-64-CM26</t>
+          <t>2701-560-CM26</t>
         </is>
       </c>
       <c r="B286" t="inlineStr">
@@ -18999,12 +18999,12 @@
       </c>
       <c r="F286" t="inlineStr">
         <is>
-          <t>65.260.064-6</t>
+          <t>69.071.800-6</t>
         </is>
       </c>
       <c r="G286" t="inlineStr">
         <is>
-          <t>CORPORACION MUNICIPAL DE DEPORTES, CULTURA, RECREACION Y FOMENTO DE HU</t>
+          <t>I MUNICIPALIDAD DE TALAGANTE</t>
         </is>
       </c>
       <c r="H286" t="inlineStr">
@@ -19033,7 +19033,7 @@
         </is>
       </c>
       <c r="M286" s="2" t="n">
-        <v>46630.5</v>
+        <v>7874.28</v>
       </c>
     </row>
     <row r="287">
@@ -19514,7 +19514,7 @@
       </c>
       <c r="E294" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F294" t="inlineStr">
@@ -19884,7 +19884,7 @@
     <row r="300">
       <c r="A300" t="inlineStr">
         <is>
-          <t>550716-12-CM26</t>
+          <t>558338-4-SE26</t>
         </is>
       </c>
       <c r="B300" t="inlineStr">
@@ -19909,12 +19909,12 @@
       </c>
       <c r="F300" t="inlineStr">
         <is>
-          <t>65.961.370-0</t>
+          <t>61.702.000-9</t>
         </is>
       </c>
       <c r="G300" t="inlineStr">
         <is>
-          <t>GOBIERNO REGIONAL REGION METROPOLITANA</t>
+          <t>SERVICIO NACIONAL DE GEOLOGIA Y MINERIA</t>
         </is>
       </c>
       <c r="H300" t="inlineStr">
@@ -19943,13 +19943,13 @@
         </is>
       </c>
       <c r="M300" s="2" t="n">
-        <v>6943.58</v>
+        <v>306084.36</v>
       </c>
     </row>
     <row r="301">
       <c r="A301" t="inlineStr">
         <is>
-          <t>558338-4-SE26</t>
+          <t>550716-12-CM26</t>
         </is>
       </c>
       <c r="B301" t="inlineStr">
@@ -19974,12 +19974,12 @@
       </c>
       <c r="F301" t="inlineStr">
         <is>
-          <t>61.702.000-9</t>
+          <t>65.961.370-0</t>
         </is>
       </c>
       <c r="G301" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE GEOLOGIA Y MINERIA</t>
+          <t>GOBIERNO REGIONAL REGION METROPOLITANA</t>
         </is>
       </c>
       <c r="H301" t="inlineStr">
@@ -20008,13 +20008,13 @@
         </is>
       </c>
       <c r="M301" s="2" t="n">
-        <v>306084.36</v>
+        <v>6943.58</v>
       </c>
     </row>
     <row r="302">
       <c r="A302" t="inlineStr">
         <is>
-          <t>2702-464-CM26</t>
+          <t>1186801-10-CM26</t>
         </is>
       </c>
       <c r="B302" t="inlineStr">
@@ -20039,12 +20039,12 @@
       </c>
       <c r="F302" t="inlineStr">
         <is>
-          <t>69.071.800-6</t>
+          <t>60.930.000-0</t>
         </is>
       </c>
       <c r="G302" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE TALAGANTE</t>
+          <t>CONSEJO NACIONAL DE EDUCACION</t>
         </is>
       </c>
       <c r="H302" t="inlineStr">
@@ -20073,13 +20073,13 @@
         </is>
       </c>
       <c r="M302" s="2" t="n">
-        <v>10413.64</v>
+        <v>4681.22</v>
       </c>
     </row>
     <row r="303">
       <c r="A303" t="inlineStr">
         <is>
-          <t>1186801-10-CM26</t>
+          <t>2702-464-CM26</t>
         </is>
       </c>
       <c r="B303" t="inlineStr">
@@ -20104,12 +20104,12 @@
       </c>
       <c r="F303" t="inlineStr">
         <is>
-          <t>60.930.000-0</t>
+          <t>69.071.800-6</t>
         </is>
       </c>
       <c r="G303" t="inlineStr">
         <is>
-          <t>CONSEJO NACIONAL DE EDUCACION</t>
+          <t>I MUNICIPALIDAD DE TALAGANTE</t>
         </is>
       </c>
       <c r="H303" t="inlineStr">
@@ -20138,13 +20138,13 @@
         </is>
       </c>
       <c r="M303" s="2" t="n">
-        <v>4681.22</v>
+        <v>10413.64</v>
       </c>
     </row>
     <row r="304">
       <c r="A304" t="inlineStr">
         <is>
-          <t>307-95-CM26</t>
+          <t>2701-677-CM26</t>
         </is>
       </c>
       <c r="B304" t="inlineStr">
@@ -20169,12 +20169,12 @@
       </c>
       <c r="F304" t="inlineStr">
         <is>
-          <t>60.919.000-0</t>
+          <t>69.071.800-6</t>
         </is>
       </c>
       <c r="G304" t="inlineStr">
         <is>
-          <t>Consejo de Rectores de las Universidades Chilenas</t>
+          <t>I MUNICIPALIDAD DE TALAGANTE</t>
         </is>
       </c>
       <c r="H304" t="inlineStr">
@@ -20203,13 +20203,13 @@
         </is>
       </c>
       <c r="M304" s="2" t="n">
-        <v>667.67</v>
+        <v>7594.58</v>
       </c>
     </row>
     <row r="305">
       <c r="A305" t="inlineStr">
         <is>
-          <t>307-96-CM26</t>
+          <t>2701-676-CM26</t>
         </is>
       </c>
       <c r="B305" t="inlineStr">
@@ -20234,12 +20234,12 @@
       </c>
       <c r="F305" t="inlineStr">
         <is>
-          <t>60.919.000-0</t>
+          <t>69.071.800-6</t>
         </is>
       </c>
       <c r="G305" t="inlineStr">
         <is>
-          <t>Consejo de Rectores de las Universidades Chilenas</t>
+          <t>I MUNICIPALIDAD DE TALAGANTE</t>
         </is>
       </c>
       <c r="H305" t="inlineStr">
@@ -20268,13 +20268,13 @@
         </is>
       </c>
       <c r="M305" s="2" t="n">
-        <v>667.67</v>
+        <v>7594.58</v>
       </c>
     </row>
     <row r="306">
       <c r="A306" t="inlineStr">
         <is>
-          <t>307-97-CM26</t>
+          <t>2701-675-CM26</t>
         </is>
       </c>
       <c r="B306" t="inlineStr">
@@ -20299,12 +20299,12 @@
       </c>
       <c r="F306" t="inlineStr">
         <is>
-          <t>60.919.000-0</t>
+          <t>69.071.800-6</t>
         </is>
       </c>
       <c r="G306" t="inlineStr">
         <is>
-          <t>Consejo de Rectores de las Universidades Chilenas</t>
+          <t>I MUNICIPALIDAD DE TALAGANTE</t>
         </is>
       </c>
       <c r="H306" t="inlineStr">
@@ -20333,7 +20333,7 @@
         </is>
       </c>
       <c r="M306" s="2" t="n">
-        <v>667.67</v>
+        <v>7594.58</v>
       </c>
     </row>
     <row r="307">
@@ -20404,7 +20404,7 @@
     <row r="308">
       <c r="A308" t="inlineStr">
         <is>
-          <t>2701-675-CM26</t>
+          <t>307-97-CM26</t>
         </is>
       </c>
       <c r="B308" t="inlineStr">
@@ -20429,12 +20429,12 @@
       </c>
       <c r="F308" t="inlineStr">
         <is>
-          <t>69.071.800-6</t>
+          <t>60.919.000-0</t>
         </is>
       </c>
       <c r="G308" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE TALAGANTE</t>
+          <t>Consejo de Rectores de las Universidades Chilenas</t>
         </is>
       </c>
       <c r="H308" t="inlineStr">
@@ -20463,13 +20463,13 @@
         </is>
       </c>
       <c r="M308" s="2" t="n">
-        <v>7594.58</v>
+        <v>667.67</v>
       </c>
     </row>
     <row r="309">
       <c r="A309" t="inlineStr">
         <is>
-          <t>2701-676-CM26</t>
+          <t>307-96-CM26</t>
         </is>
       </c>
       <c r="B309" t="inlineStr">
@@ -20494,12 +20494,12 @@
       </c>
       <c r="F309" t="inlineStr">
         <is>
-          <t>69.071.800-6</t>
+          <t>60.919.000-0</t>
         </is>
       </c>
       <c r="G309" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE TALAGANTE</t>
+          <t>Consejo de Rectores de las Universidades Chilenas</t>
         </is>
       </c>
       <c r="H309" t="inlineStr">
@@ -20528,13 +20528,13 @@
         </is>
       </c>
       <c r="M309" s="2" t="n">
-        <v>7594.58</v>
+        <v>667.67</v>
       </c>
     </row>
     <row r="310">
       <c r="A310" t="inlineStr">
         <is>
-          <t>2701-677-CM26</t>
+          <t>307-95-CM26</t>
         </is>
       </c>
       <c r="B310" t="inlineStr">
@@ -20559,12 +20559,12 @@
       </c>
       <c r="F310" t="inlineStr">
         <is>
-          <t>69.071.800-6</t>
+          <t>60.919.000-0</t>
         </is>
       </c>
       <c r="G310" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE TALAGANTE</t>
+          <t>Consejo de Rectores de las Universidades Chilenas</t>
         </is>
       </c>
       <c r="H310" t="inlineStr">
@@ -20593,7 +20593,7 @@
         </is>
       </c>
       <c r="M310" s="2" t="n">
-        <v>7594.58</v>
+        <v>667.67</v>
       </c>
     </row>
     <row r="311">
@@ -20724,6 +20724,721 @@
       </c>
       <c r="M312" s="2" t="n">
         <v>20926.2</v>
+      </c>
+    </row>
+    <row r="313">
+      <c r="A313" t="inlineStr">
+        <is>
+          <t>4722-5-CM26</t>
+        </is>
+      </c>
+      <c r="B313" t="inlineStr">
+        <is>
+          <t>2239-12-LR23</t>
+        </is>
+      </c>
+      <c r="C313" t="inlineStr">
+        <is>
+          <t>oct-2026</t>
+        </is>
+      </c>
+      <c r="D313" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="E313" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F313" t="inlineStr">
+        <is>
+          <t>65.138.650-0</t>
+        </is>
+      </c>
+      <c r="G313" t="inlineStr">
+        <is>
+          <t>DEFENSORIA PENAL PUBLICA</t>
+        </is>
+      </c>
+      <c r="H313" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="I313" t="inlineStr">
+        <is>
+          <t>BCI SEGUROS VIDA S A</t>
+        </is>
+      </c>
+      <c r="J313" t="inlineStr">
+        <is>
+          <t>96.573.600-K</t>
+        </is>
+      </c>
+      <c r="K313" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
+      <c r="L313" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M313" s="2" t="n">
+        <v>29037.1</v>
+      </c>
+    </row>
+    <row r="314">
+      <c r="A314" t="inlineStr">
+        <is>
+          <t>670784-12-CM26</t>
+        </is>
+      </c>
+      <c r="B314" t="inlineStr">
+        <is>
+          <t>2239-12-LR23</t>
+        </is>
+      </c>
+      <c r="C314" t="inlineStr">
+        <is>
+          <t>oct-2026</t>
+        </is>
+      </c>
+      <c r="D314" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="E314" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F314" t="inlineStr">
+        <is>
+          <t>60.818.000-1</t>
+        </is>
+      </c>
+      <c r="G314" t="inlineStr">
+        <is>
+          <t>SUPERINTENDENCIA DE PENSIONES</t>
+        </is>
+      </c>
+      <c r="H314" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="I314" t="inlineStr">
+        <is>
+          <t>BCI SEGUROS VIDA S A</t>
+        </is>
+      </c>
+      <c r="J314" t="inlineStr">
+        <is>
+          <t>96.573.600-K</t>
+        </is>
+      </c>
+      <c r="K314" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
+      <c r="L314" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M314" s="2" t="n">
+        <v>9567.940000000001</v>
+      </c>
+    </row>
+    <row r="315">
+      <c r="A315" t="inlineStr">
+        <is>
+          <t>1211992-203-CM26</t>
+        </is>
+      </c>
+      <c r="B315" t="inlineStr">
+        <is>
+          <t>2239-12-LR23</t>
+        </is>
+      </c>
+      <c r="C315" t="inlineStr">
+        <is>
+          <t>oct-2026</t>
+        </is>
+      </c>
+      <c r="D315" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="E315" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F315" t="inlineStr">
+        <is>
+          <t>65.192.585-1</t>
+        </is>
+      </c>
+      <c r="G315" t="inlineStr">
+        <is>
+          <t>CORPORACIÓN YUNUS</t>
+        </is>
+      </c>
+      <c r="H315" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="I315" t="inlineStr">
+        <is>
+          <t>BCI SEGUROS VIDA S A</t>
+        </is>
+      </c>
+      <c r="J315" t="inlineStr">
+        <is>
+          <t>96.573.600-K</t>
+        </is>
+      </c>
+      <c r="K315" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
+      <c r="L315" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M315" s="2" t="n">
+        <v>1107.44</v>
+      </c>
+    </row>
+    <row r="316">
+      <c r="A316" t="inlineStr">
+        <is>
+          <t>1166422-1-CM26</t>
+        </is>
+      </c>
+      <c r="B316" t="inlineStr">
+        <is>
+          <t>2239-12-LR23</t>
+        </is>
+      </c>
+      <c r="C316" t="inlineStr">
+        <is>
+          <t>oct-2026</t>
+        </is>
+      </c>
+      <c r="D316" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="E316" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F316" t="inlineStr">
+        <is>
+          <t>61.001.002-4</t>
+        </is>
+      </c>
+      <c r="G316" t="inlineStr">
+        <is>
+          <t>SUBSECRETARIA DEL MINISTERIO DE JUSTICIA</t>
+        </is>
+      </c>
+      <c r="H316" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="I316" t="inlineStr">
+        <is>
+          <t>BCI SEGUROS VIDA S A</t>
+        </is>
+      </c>
+      <c r="J316" t="inlineStr">
+        <is>
+          <t>96.573.600-K</t>
+        </is>
+      </c>
+      <c r="K316" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
+      <c r="L316" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M316" s="2" t="n">
+        <v>73328.53</v>
+      </c>
+    </row>
+    <row r="317">
+      <c r="A317" t="inlineStr">
+        <is>
+          <t>670784-13-CM26</t>
+        </is>
+      </c>
+      <c r="B317" t="inlineStr">
+        <is>
+          <t>2239-12-LR23</t>
+        </is>
+      </c>
+      <c r="C317" t="inlineStr">
+        <is>
+          <t>oct-2026</t>
+        </is>
+      </c>
+      <c r="D317" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="E317" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F317" t="inlineStr">
+        <is>
+          <t>60.818.000-1</t>
+        </is>
+      </c>
+      <c r="G317" t="inlineStr">
+        <is>
+          <t>SUPERINTENDENCIA DE PENSIONES</t>
+        </is>
+      </c>
+      <c r="H317" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="I317" t="inlineStr">
+        <is>
+          <t>BCI SEGUROS VIDA S A</t>
+        </is>
+      </c>
+      <c r="J317" t="inlineStr">
+        <is>
+          <t>96.573.600-K</t>
+        </is>
+      </c>
+      <c r="K317" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
+      <c r="L317" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M317" s="2" t="n">
+        <v>9756.940000000001</v>
+      </c>
+    </row>
+    <row r="318">
+      <c r="A318" t="inlineStr">
+        <is>
+          <t>670784-14-CM26</t>
+        </is>
+      </c>
+      <c r="B318" t="inlineStr">
+        <is>
+          <t>2239-12-LR23</t>
+        </is>
+      </c>
+      <c r="C318" t="inlineStr">
+        <is>
+          <t>oct-2026</t>
+        </is>
+      </c>
+      <c r="D318" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="E318" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F318" t="inlineStr">
+        <is>
+          <t>60.818.000-1</t>
+        </is>
+      </c>
+      <c r="G318" t="inlineStr">
+        <is>
+          <t>SUPERINTENDENCIA DE PENSIONES</t>
+        </is>
+      </c>
+      <c r="H318" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="I318" t="inlineStr">
+        <is>
+          <t>BCI SEGUROS VIDA S A</t>
+        </is>
+      </c>
+      <c r="J318" t="inlineStr">
+        <is>
+          <t>96.573.600-K</t>
+        </is>
+      </c>
+      <c r="K318" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
+      <c r="L318" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M318" s="2" t="n">
+        <v>9710.92</v>
+      </c>
+    </row>
+    <row r="319">
+      <c r="A319" t="inlineStr">
+        <is>
+          <t>670784-15-CM26</t>
+        </is>
+      </c>
+      <c r="B319" t="inlineStr">
+        <is>
+          <t>2239-12-LR23</t>
+        </is>
+      </c>
+      <c r="C319" t="inlineStr">
+        <is>
+          <t>oct-2026</t>
+        </is>
+      </c>
+      <c r="D319" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="E319" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F319" t="inlineStr">
+        <is>
+          <t>60.818.000-1</t>
+        </is>
+      </c>
+      <c r="G319" t="inlineStr">
+        <is>
+          <t>SUPERINTENDENCIA DE PENSIONES</t>
+        </is>
+      </c>
+      <c r="H319" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="I319" t="inlineStr">
+        <is>
+          <t>BCI SEGUROS VIDA S A</t>
+        </is>
+      </c>
+      <c r="J319" t="inlineStr">
+        <is>
+          <t>96.573.600-K</t>
+        </is>
+      </c>
+      <c r="K319" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
+      <c r="L319" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M319" s="2" t="n">
+        <v>9618.870000000001</v>
+      </c>
+    </row>
+    <row r="320">
+      <c r="A320" t="inlineStr">
+        <is>
+          <t>550716-13-CM26</t>
+        </is>
+      </c>
+      <c r="B320" t="inlineStr">
+        <is>
+          <t>2239-12-LR23</t>
+        </is>
+      </c>
+      <c r="C320" t="inlineStr">
+        <is>
+          <t>oct-2026</t>
+        </is>
+      </c>
+      <c r="D320" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="E320" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F320" t="inlineStr">
+        <is>
+          <t>65.961.370-0</t>
+        </is>
+      </c>
+      <c r="G320" t="inlineStr">
+        <is>
+          <t>GOBIERNO REGIONAL REGION METROPOLITANA</t>
+        </is>
+      </c>
+      <c r="H320" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="I320" t="inlineStr">
+        <is>
+          <t>BCI SEGUROS VIDA S A</t>
+        </is>
+      </c>
+      <c r="J320" t="inlineStr">
+        <is>
+          <t>96.573.600-K</t>
+        </is>
+      </c>
+      <c r="K320" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
+      <c r="L320" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M320" s="2" t="n">
+        <v>6673.38</v>
+      </c>
+    </row>
+    <row r="321">
+      <c r="A321" t="inlineStr">
+        <is>
+          <t>1477-321-CM26</t>
+        </is>
+      </c>
+      <c r="B321" t="inlineStr">
+        <is>
+          <t>2239-12-LR23</t>
+        </is>
+      </c>
+      <c r="C321" t="inlineStr">
+        <is>
+          <t>oct-2026</t>
+        </is>
+      </c>
+      <c r="D321" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="E321" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F321" t="inlineStr">
+        <is>
+          <t>70.786.200-9</t>
+        </is>
+      </c>
+      <c r="G321" t="inlineStr">
+        <is>
+          <t>Corporación de Asistencia Judicial RM</t>
+        </is>
+      </c>
+      <c r="H321" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="I321" t="inlineStr">
+        <is>
+          <t>BCI SEGUROS VIDA S A</t>
+        </is>
+      </c>
+      <c r="J321" t="inlineStr">
+        <is>
+          <t>96.573.600-K</t>
+        </is>
+      </c>
+      <c r="K321" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
+      <c r="L321" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M321" s="2" t="n">
+        <v>35235.75</v>
+      </c>
+    </row>
+    <row r="322">
+      <c r="A322" t="inlineStr">
+        <is>
+          <t>565314-5-SE26</t>
+        </is>
+      </c>
+      <c r="B322" t="inlineStr">
+        <is>
+          <t>2239-12-LR23</t>
+        </is>
+      </c>
+      <c r="C322" t="inlineStr">
+        <is>
+          <t>oct-2026</t>
+        </is>
+      </c>
+      <c r="D322" t="inlineStr">
+        <is>
+          <t>2026-10-23</t>
+        </is>
+      </c>
+      <c r="E322" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F322" t="inlineStr">
+        <is>
+          <t>61.979.620-9</t>
+        </is>
+      </c>
+      <c r="G322" t="inlineStr">
+        <is>
+          <t>INSTITUTO DE PREVISION SOCIAL</t>
+        </is>
+      </c>
+      <c r="H322" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="I322" t="inlineStr">
+        <is>
+          <t>BCI SEGUROS VIDA S A</t>
+        </is>
+      </c>
+      <c r="J322" t="inlineStr">
+        <is>
+          <t>96.573.600-K</t>
+        </is>
+      </c>
+      <c r="K322" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
+      <c r="L322" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M322" s="2" t="n">
+        <v>1222662.99</v>
+      </c>
+    </row>
+    <row r="323">
+      <c r="A323" t="inlineStr">
+        <is>
+          <t>559222-1-CM26</t>
+        </is>
+      </c>
+      <c r="B323" t="inlineStr">
+        <is>
+          <t>2239-12-LR23</t>
+        </is>
+      </c>
+      <c r="C323" t="inlineStr">
+        <is>
+          <t>oct-2026</t>
+        </is>
+      </c>
+      <c r="D323" t="inlineStr">
+        <is>
+          <t>2026-10-23</t>
+        </is>
+      </c>
+      <c r="E323" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F323" t="inlineStr">
+        <is>
+          <t>60.107.000-6</t>
+        </is>
+      </c>
+      <c r="G323" t="inlineStr">
+        <is>
+          <t>SERVICIO NACIONAL DE LA MUJER Y LA EQUIDAD DE GENERO</t>
+        </is>
+      </c>
+      <c r="H323" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="I323" t="inlineStr">
+        <is>
+          <t>BCI SEGUROS VIDA S A</t>
+        </is>
+      </c>
+      <c r="J323" t="inlineStr">
+        <is>
+          <t>96.573.600-K</t>
+        </is>
+      </c>
+      <c r="K323" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
+      <c r="L323" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M323" s="2" t="n">
+        <v>488295.71</v>
       </c>
     </row>
   </sheetData>
